--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -468,7 +468,7 @@
         <v>Gitai.xlsx</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-31T13:06:45.034Z</v>
+        <v>2026-07-31T13:53:14.710Z</v>
       </c>
       <c r="E2">
         <v>928</v>
@@ -8490,7 +8490,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="B230" t="str">
         <v>2023-11-03</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="B231" t="str">
         <v>2023-11-03</v>
@@ -8554,7 +8554,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="B232" t="str">
         <v>2023-11-03</v>
@@ -8586,7 +8586,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="B233" t="str">
         <v>2023-11-03</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="B234" t="str">
         <v>2023-11-03</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="B235" t="str">
         <v>2023-11-03</v>
@@ -8682,7 +8682,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B236" t="str">
         <v>2023-12-01</v>
@@ -8714,7 +8714,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="B237" t="str">
         <v>2023-12-01</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="B238" t="str">
         <v>2023-12-02</v>
@@ -8778,7 +8778,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>796</v>
+        <v>816</v>
       </c>
       <c r="B239" t="str">
         <v>2023-12-02</v>
@@ -8810,7 +8810,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B240" t="str">
         <v>2023-12-05</v>
@@ -8842,7 +8842,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="B241" t="str">
         <v>2023-12-06</v>
@@ -8874,7 +8874,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="B242" t="str">
         <v>2023-12-07</v>
@@ -8906,7 +8906,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="B243" t="str">
         <v>2023-12-07</v>
@@ -8938,7 +8938,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B244" t="str">
         <v>2023-12-08</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>802</v>
+        <v>826</v>
       </c>
       <c r="B245" t="str">
         <v>2023-12-09</v>
@@ -9002,7 +9002,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="B246" t="str">
         <v>2023-12-11</v>
@@ -9034,7 +9034,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="B247" t="str">
         <v>2023-12-11</v>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="B248" t="str">
         <v>2023-12-11</v>
@@ -9098,7 +9098,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="B249" t="str">
         <v>2023-12-12</v>
@@ -9130,7 +9130,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>807</v>
+        <v>901</v>
       </c>
       <c r="B250" t="str">
         <v>2024-02-06</v>
@@ -9162,7 +9162,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>808</v>
+        <v>902</v>
       </c>
       <c r="B251" t="str">
         <v>2024-02-06</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>809</v>
+        <v>903</v>
       </c>
       <c r="B252" t="str">
         <v>2024-02-06</v>
@@ -9226,7 +9226,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>810</v>
+        <v>904</v>
       </c>
       <c r="B253" t="str">
         <v>2024-02-06</v>
@@ -9258,7 +9258,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>811</v>
+        <v>980</v>
       </c>
       <c r="B254" t="str">
         <v>2024-03-07</v>
@@ -9290,7 +9290,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>812</v>
+        <v>981</v>
       </c>
       <c r="B255" t="str">
         <v>2024-03-07</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>813</v>
+        <v>982</v>
       </c>
       <c r="B256" t="str">
         <v>2024-03-07</v>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>814</v>
+        <v>983</v>
       </c>
       <c r="B257" t="str">
         <v>2024-03-07</v>
@@ -9386,7 +9386,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>815</v>
+        <v>984</v>
       </c>
       <c r="B258" t="str">
         <v>2024-03-08</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>816</v>
+        <v>985</v>
       </c>
       <c r="B259" t="str">
         <v>2024-03-08</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>817</v>
+        <v>986</v>
       </c>
       <c r="B260" t="str">
         <v>2024-03-09</v>
@@ -9482,7 +9482,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>818</v>
+        <v>987</v>
       </c>
       <c r="B261" t="str">
         <v>2024-03-09</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>819</v>
+        <v>988</v>
       </c>
       <c r="B262" t="str">
         <v>2024-03-10</v>
@@ -9546,7 +9546,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>820</v>
+        <v>989</v>
       </c>
       <c r="B263" t="str">
         <v>2024-03-10</v>
@@ -9578,7 +9578,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>821</v>
+        <v>990</v>
       </c>
       <c r="B264" t="str">
         <v>2024-03-11</v>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>822</v>
+        <v>991</v>
       </c>
       <c r="B265" t="str">
         <v>2024-03-13</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>823</v>
+        <v>992</v>
       </c>
       <c r="B266" t="str">
         <v>2024-03-13</v>
@@ -9674,7 +9674,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>824</v>
+        <v>993</v>
       </c>
       <c r="B267" t="str">
         <v>2024-03-13</v>
@@ -9706,7 +9706,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>825</v>
+        <v>1011</v>
       </c>
       <c r="B268" t="str">
         <v>2024-03-14</v>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>826</v>
+        <v>1012</v>
       </c>
       <c r="B269" t="str">
         <v>2024-03-14</v>
@@ -9770,7 +9770,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>827</v>
+        <v>1013</v>
       </c>
       <c r="B270" t="str">
         <v>2024-03-14</v>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>828</v>
+        <v>1014</v>
       </c>
       <c r="B271" t="str">
         <v>2024-03-14</v>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>829</v>
+        <v>1015</v>
       </c>
       <c r="B272" t="str">
         <v>2024-03-14</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>830</v>
+        <v>1016</v>
       </c>
       <c r="B273" t="str">
         <v>2024-03-14</v>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>831</v>
+        <v>1017</v>
       </c>
       <c r="B274" t="str">
         <v>2024-03-14</v>
@@ -9930,7 +9930,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>832</v>
+        <v>1018</v>
       </c>
       <c r="B275" t="str">
         <v>2024-03-14</v>
@@ -9962,7 +9962,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>833</v>
+        <v>1019</v>
       </c>
       <c r="B276" t="str">
         <v>2024-03-14</v>
@@ -9994,7 +9994,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>834</v>
+        <v>1020</v>
       </c>
       <c r="B277" t="str">
         <v>2024-03-14</v>
@@ -10026,7 +10026,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>835</v>
+        <v>1021</v>
       </c>
       <c r="B278" t="str">
         <v>2024-03-14</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>836</v>
+        <v>1022</v>
       </c>
       <c r="B279" t="str">
         <v>2024-03-14</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>837</v>
+        <v>1023</v>
       </c>
       <c r="B280" t="str">
         <v>2024-03-14</v>
@@ -10122,7 +10122,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>838</v>
+        <v>1024</v>
       </c>
       <c r="B281" t="str">
         <v>2024-03-14</v>
@@ -10154,7 +10154,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>839</v>
+        <v>1025</v>
       </c>
       <c r="B282" t="str">
         <v>2024-03-14</v>
@@ -10186,7 +10186,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>840</v>
+        <v>1026</v>
       </c>
       <c r="B283" t="str">
         <v>2024-03-14</v>
@@ -10218,7 +10218,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>841</v>
+        <v>1027</v>
       </c>
       <c r="B284" t="str">
         <v>2024-03-14</v>
@@ -10250,7 +10250,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>842</v>
+        <v>1028</v>
       </c>
       <c r="B285" t="str">
         <v>2024-03-14</v>
@@ -10282,7 +10282,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>843</v>
+        <v>1029</v>
       </c>
       <c r="B286" t="str">
         <v>2024-03-14</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>844</v>
+        <v>1030</v>
       </c>
       <c r="B287" t="str">
         <v>2024-03-14</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>845</v>
+        <v>1031</v>
       </c>
       <c r="B288" t="str">
         <v>2024-03-14</v>
@@ -10378,7 +10378,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>846</v>
+        <v>1032</v>
       </c>
       <c r="B289" t="str">
         <v>2024-03-14</v>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>847</v>
+        <v>1033</v>
       </c>
       <c r="B290" t="str">
         <v>2024-03-14</v>
@@ -10442,7 +10442,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>848</v>
+        <v>1034</v>
       </c>
       <c r="B291" t="str">
         <v>2024-03-14</v>
@@ -10474,7 +10474,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>849</v>
+        <v>1035</v>
       </c>
       <c r="B292" t="str">
         <v>2024-03-14</v>
@@ -10506,7 +10506,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>850</v>
+        <v>1036</v>
       </c>
       <c r="B293" t="str">
         <v>2024-03-14</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>851</v>
+        <v>1037</v>
       </c>
       <c r="B294" t="str">
         <v>2024-03-14</v>
@@ -10570,7 +10570,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>852</v>
+        <v>1038</v>
       </c>
       <c r="B295" t="str">
         <v>2024-03-14</v>
@@ -10602,7 +10602,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>853</v>
+        <v>1039</v>
       </c>
       <c r="B296" t="str">
         <v>2024-03-14</v>
@@ -10634,7 +10634,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>854</v>
+        <v>1040</v>
       </c>
       <c r="B297" t="str">
         <v>2024-03-14</v>
@@ -10666,7 +10666,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>855</v>
+        <v>1041</v>
       </c>
       <c r="B298" t="str">
         <v>2024-03-14</v>
@@ -10698,7 +10698,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>856</v>
+        <v>1042</v>
       </c>
       <c r="B299" t="str">
         <v>2024-03-14</v>
@@ -10730,7 +10730,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>857</v>
+        <v>1043</v>
       </c>
       <c r="B300" t="str">
         <v>2024-03-14</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>858</v>
+        <v>1044</v>
       </c>
       <c r="B301" t="str">
         <v>2024-03-14</v>
@@ -10794,7 +10794,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>859</v>
+        <v>1045</v>
       </c>
       <c r="B302" t="str">
         <v>2024-03-14</v>
@@ -10826,7 +10826,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>860</v>
+        <v>1046</v>
       </c>
       <c r="B303" t="str">
         <v>2024-03-14</v>
@@ -10858,7 +10858,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>861</v>
+        <v>1047</v>
       </c>
       <c r="B304" t="str">
         <v>2024-03-14</v>
@@ -10890,7 +10890,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>862</v>
+        <v>1048</v>
       </c>
       <c r="B305" t="str">
         <v>2024-03-14</v>
@@ -10922,7 +10922,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>863</v>
+        <v>1049</v>
       </c>
       <c r="B306" t="str">
         <v>2024-03-14</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="B307" t="str">
         <v>2024-03-15</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>865</v>
+        <v>1051</v>
       </c>
       <c r="B308" t="str">
         <v>2024-03-15</v>
@@ -11018,7 +11018,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>866</v>
+        <v>1052</v>
       </c>
       <c r="B309" t="str">
         <v>2024-03-15</v>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>867</v>
+        <v>1053</v>
       </c>
       <c r="B310" t="str">
         <v>2024-03-15</v>
@@ -11082,7 +11082,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>868</v>
+        <v>1054</v>
       </c>
       <c r="B311" t="str">
         <v>2024-03-16</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>869</v>
+        <v>1055</v>
       </c>
       <c r="B312" t="str">
         <v>2024-03-16</v>
@@ -11146,7 +11146,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>870</v>
+        <v>1056</v>
       </c>
       <c r="B313" t="str">
         <v>2024-03-17</v>
@@ -11178,7 +11178,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>871</v>
+        <v>1057</v>
       </c>
       <c r="B314" t="str">
         <v>2024-03-17</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>872</v>
+        <v>1058</v>
       </c>
       <c r="B315" t="str">
         <v>2024-03-17</v>
@@ -11242,7 +11242,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>873</v>
+        <v>1059</v>
       </c>
       <c r="B316" t="str">
         <v>2024-03-17</v>
@@ -11274,7 +11274,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>874</v>
+        <v>1060</v>
       </c>
       <c r="B317" t="str">
         <v>2024-03-23</v>
@@ -11306,7 +11306,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>875</v>
+        <v>1061</v>
       </c>
       <c r="B318" t="str">
         <v>2024-03-24</v>
@@ -11338,7 +11338,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>876</v>
+        <v>1062</v>
       </c>
       <c r="B319" t="str">
         <v>2024-03-24</v>
@@ -11370,7 +11370,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>877</v>
+        <v>1063</v>
       </c>
       <c r="B320" t="str">
         <v>2024-03-24</v>
@@ -11402,7 +11402,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>878</v>
+        <v>1064</v>
       </c>
       <c r="B321" t="str">
         <v>2024-03-28</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>879</v>
+        <v>1088</v>
       </c>
       <c r="B322" t="str">
         <v>2024-04-15</v>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>880</v>
+        <v>1089</v>
       </c>
       <c r="B323" t="str">
         <v>2024-04-15</v>
@@ -11498,7 +11498,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>881</v>
+        <v>1090</v>
       </c>
       <c r="B324" t="str">
         <v>2024-04-15</v>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>882</v>
+        <v>1091</v>
       </c>
       <c r="B325" t="str">
         <v>2024-04-16</v>
@@ -11562,7 +11562,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>883</v>
+        <v>1092</v>
       </c>
       <c r="B326" t="str">
         <v>2024-04-16</v>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>884</v>
+        <v>1093</v>
       </c>
       <c r="B327" t="str">
         <v>2024-04-16</v>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>885</v>
+        <v>1094</v>
       </c>
       <c r="B328" t="str">
         <v>2024-04-16</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>886</v>
+        <v>1095</v>
       </c>
       <c r="B329" t="str">
         <v>2024-04-16</v>
@@ -11690,7 +11690,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>887</v>
+        <v>1096</v>
       </c>
       <c r="B330" t="str">
         <v>2024-04-16</v>
@@ -11722,7 +11722,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>888</v>
+        <v>1097</v>
       </c>
       <c r="B331" t="str">
         <v>2024-04-16</v>
@@ -11754,7 +11754,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>889</v>
+        <v>1098</v>
       </c>
       <c r="B332" t="str">
         <v>2024-04-16</v>
@@ -11786,7 +11786,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>890</v>
+        <v>1099</v>
       </c>
       <c r="B333" t="str">
         <v>2024-04-16</v>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>891</v>
+        <v>1100</v>
       </c>
       <c r="B334" t="str">
         <v>2024-04-16</v>
@@ -11850,7 +11850,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>892</v>
+        <v>1101</v>
       </c>
       <c r="B335" t="str">
         <v>2024-04-16</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>893</v>
+        <v>1102</v>
       </c>
       <c r="B336" t="str">
         <v>2024-04-18</v>
@@ -11914,7 +11914,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>894</v>
+        <v>1103</v>
       </c>
       <c r="B337" t="str">
         <v>2024-04-18</v>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>895</v>
+        <v>1104</v>
       </c>
       <c r="B338" t="str">
         <v>2024-04-19</v>
@@ -11978,7 +11978,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>896</v>
+        <v>1105</v>
       </c>
       <c r="B339" t="str">
         <v>2024-04-19</v>
@@ -12010,7 +12010,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>897</v>
+        <v>1106</v>
       </c>
       <c r="B340" t="str">
         <v>2024-04-19</v>
@@ -12042,7 +12042,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>898</v>
+        <v>1117</v>
       </c>
       <c r="B341" t="str">
         <v>2024-04-21</v>
@@ -12074,7 +12074,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>899</v>
+        <v>1118</v>
       </c>
       <c r="B342" t="str">
         <v>2024-04-21</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>900</v>
+        <v>1119</v>
       </c>
       <c r="B343" t="str">
         <v>2024-04-22</v>
@@ -12138,7 +12138,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>901</v>
+        <v>1120</v>
       </c>
       <c r="B344" t="str">
         <v>2024-04-22</v>
@@ -12170,7 +12170,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>902</v>
+        <v>1165</v>
       </c>
       <c r="B345" t="str">
         <v>2024-05-07</v>
@@ -12202,7 +12202,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>903</v>
+        <v>1166</v>
       </c>
       <c r="B346" t="str">
         <v>2024-05-07</v>
@@ -12234,7 +12234,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>904</v>
+        <v>1167</v>
       </c>
       <c r="B347" t="str">
         <v>2024-05-07</v>
@@ -12266,7 +12266,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>905</v>
+        <v>1168</v>
       </c>
       <c r="B348" t="str">
         <v>2024-05-07</v>
@@ -12298,7 +12298,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>906</v>
+        <v>1169</v>
       </c>
       <c r="B349" t="str">
         <v>2024-05-07</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>907</v>
+        <v>1170</v>
       </c>
       <c r="B350" t="str">
         <v>2024-05-07</v>
@@ -12362,7 +12362,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>908</v>
+        <v>1171</v>
       </c>
       <c r="B351" t="str">
         <v>2024-05-07</v>
@@ -12394,7 +12394,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>909</v>
+        <v>1172</v>
       </c>
       <c r="B352" t="str">
         <v>2024-05-07</v>
@@ -12426,7 +12426,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>910</v>
+        <v>1173</v>
       </c>
       <c r="B353" t="str">
         <v>2024-05-07</v>
@@ -12458,7 +12458,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>911</v>
+        <v>1174</v>
       </c>
       <c r="B354" t="str">
         <v>2024-05-07</v>
@@ -12490,7 +12490,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>912</v>
+        <v>1175</v>
       </c>
       <c r="B355" t="str">
         <v>2024-05-07</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>913</v>
+        <v>1176</v>
       </c>
       <c r="B356" t="str">
         <v>2024-05-07</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>914</v>
+        <v>1177</v>
       </c>
       <c r="B357" t="str">
         <v>2024-05-07</v>
@@ -12586,7 +12586,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>915</v>
+        <v>1178</v>
       </c>
       <c r="B358" t="str">
         <v>2024-05-07</v>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>916</v>
+        <v>1179</v>
       </c>
       <c r="B359" t="str">
         <v>2024-05-07</v>
@@ -12650,7 +12650,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>917</v>
+        <v>1180</v>
       </c>
       <c r="B360" t="str">
         <v>2024-05-08</v>
@@ -12682,7 +12682,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>918</v>
+        <v>1181</v>
       </c>
       <c r="B361" t="str">
         <v>2024-05-08</v>
@@ -12714,7 +12714,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>919</v>
+        <v>1182</v>
       </c>
       <c r="B362" t="str">
         <v>2024-05-08</v>
@@ -12746,7 +12746,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>920</v>
+        <v>1183</v>
       </c>
       <c r="B363" t="str">
         <v>2024-05-08</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>921</v>
+        <v>1184</v>
       </c>
       <c r="B364" t="str">
         <v>2024-05-08</v>
@@ -12810,7 +12810,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>922</v>
+        <v>1185</v>
       </c>
       <c r="B365" t="str">
         <v>2024-05-08</v>
@@ -12842,7 +12842,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>923</v>
+        <v>1186</v>
       </c>
       <c r="B366" t="str">
         <v>2024-05-08</v>
@@ -12874,7 +12874,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>924</v>
+        <v>1187</v>
       </c>
       <c r="B367" t="str">
         <v>2024-05-08</v>
@@ -12906,7 +12906,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>925</v>
+        <v>1188</v>
       </c>
       <c r="B368" t="str">
         <v>2024-05-08</v>
@@ -12938,7 +12938,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>926</v>
+        <v>1189</v>
       </c>
       <c r="B369" t="str">
         <v>2024-05-08</v>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>927</v>
+        <v>1190</v>
       </c>
       <c r="B370" t="str">
         <v>2024-05-08</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>928</v>
+        <v>1191</v>
       </c>
       <c r="B371" t="str">
         <v>2024-05-08</v>
@@ -13034,7 +13034,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>929</v>
+        <v>1192</v>
       </c>
       <c r="B372" t="str">
         <v>2024-05-08</v>
@@ -13066,7 +13066,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>930</v>
+        <v>1193</v>
       </c>
       <c r="B373" t="str">
         <v>2024-05-08</v>
@@ -13098,7 +13098,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>931</v>
+        <v>1194</v>
       </c>
       <c r="B374" t="str">
         <v>2024-05-08</v>
@@ -13130,7 +13130,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>932</v>
+        <v>1195</v>
       </c>
       <c r="B375" t="str">
         <v>2024-05-09</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>933</v>
+        <v>1196</v>
       </c>
       <c r="B376" t="str">
         <v>2024-05-09</v>
@@ -13194,7 +13194,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>934</v>
+        <v>1197</v>
       </c>
       <c r="B377" t="str">
         <v>2024-05-09</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>935</v>
+        <v>1198</v>
       </c>
       <c r="B378" t="str">
         <v>2024-05-09</v>
@@ -13258,7 +13258,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>936</v>
+        <v>1199</v>
       </c>
       <c r="B379" t="str">
         <v>2024-05-09</v>
@@ -13290,7 +13290,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>937</v>
+        <v>1200</v>
       </c>
       <c r="B380" t="str">
         <v>2024-05-09</v>
@@ -13322,7 +13322,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>938</v>
+        <v>1201</v>
       </c>
       <c r="B381" t="str">
         <v>2024-05-09</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>939</v>
+        <v>1202</v>
       </c>
       <c r="B382" t="str">
         <v>2024-05-09</v>
@@ -13386,7 +13386,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>940</v>
+        <v>1203</v>
       </c>
       <c r="B383" t="str">
         <v>2024-05-09</v>
@@ -13418,7 +13418,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>941</v>
+        <v>1204</v>
       </c>
       <c r="B384" t="str">
         <v>2024-05-09</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>942</v>
+        <v>1205</v>
       </c>
       <c r="B385" t="str">
         <v>2024-05-09</v>
@@ -13482,7 +13482,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>943</v>
+        <v>1206</v>
       </c>
       <c r="B386" t="str">
         <v>2024-05-09</v>
@@ -13514,7 +13514,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>944</v>
+        <v>1207</v>
       </c>
       <c r="B387" t="str">
         <v>2024-05-09</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>945</v>
+        <v>1208</v>
       </c>
       <c r="B388" t="str">
         <v>2024-05-09</v>
@@ -13578,7 +13578,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>946</v>
+        <v>1209</v>
       </c>
       <c r="B389" t="str">
         <v>2024-05-09</v>
@@ -13610,7 +13610,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>947</v>
+        <v>1210</v>
       </c>
       <c r="B390" t="str">
         <v>2024-05-10</v>
@@ -13642,7 +13642,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>948</v>
+        <v>1211</v>
       </c>
       <c r="B391" t="str">
         <v>2024-05-10</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>949</v>
+        <v>1212</v>
       </c>
       <c r="B392" t="str">
         <v>2024-05-10</v>
@@ -13706,7 +13706,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>950</v>
+        <v>1213</v>
       </c>
       <c r="B393" t="str">
         <v>2024-05-10</v>
@@ -13738,7 +13738,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>951</v>
+        <v>1214</v>
       </c>
       <c r="B394" t="str">
         <v>2024-05-10</v>
@@ -13770,7 +13770,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>952</v>
+        <v>1215</v>
       </c>
       <c r="B395" t="str">
         <v>2024-05-10</v>
@@ -13802,7 +13802,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>953</v>
+        <v>1216</v>
       </c>
       <c r="B396" t="str">
         <v>2024-05-10</v>
@@ -13834,7 +13834,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>954</v>
+        <v>1217</v>
       </c>
       <c r="B397" t="str">
         <v>2024-05-10</v>
@@ -13866,7 +13866,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>955</v>
+        <v>1218</v>
       </c>
       <c r="B398" t="str">
         <v>2024-05-10</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>956</v>
+        <v>1219</v>
       </c>
       <c r="B399" t="str">
         <v>2024-05-10</v>
@@ -13930,7 +13930,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>957</v>
+        <v>1220</v>
       </c>
       <c r="B400" t="str">
         <v>2024-05-10</v>
@@ -13962,7 +13962,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>958</v>
+        <v>1221</v>
       </c>
       <c r="B401" t="str">
         <v>2024-05-10</v>
@@ -13994,7 +13994,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>959</v>
+        <v>1222</v>
       </c>
       <c r="B402" t="str">
         <v>2024-05-10</v>
@@ -14026,7 +14026,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>960</v>
+        <v>1223</v>
       </c>
       <c r="B403" t="str">
         <v>2024-05-10</v>
@@ -14058,7 +14058,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>961</v>
+        <v>1224</v>
       </c>
       <c r="B404" t="str">
         <v>2024-05-10</v>
@@ -14090,7 +14090,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>962</v>
+        <v>1240</v>
       </c>
       <c r="B405" t="str">
         <v>2024-05-11</v>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>963</v>
+        <v>1241</v>
       </c>
       <c r="B406" t="str">
         <v>2024-05-11</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>964</v>
+        <v>1242</v>
       </c>
       <c r="B407" t="str">
         <v>2024-05-11</v>
@@ -14186,7 +14186,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>965</v>
+        <v>1243</v>
       </c>
       <c r="B408" t="str">
         <v>2024-05-11</v>
@@ -14218,7 +14218,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>966</v>
+        <v>1244</v>
       </c>
       <c r="B409" t="str">
         <v>2024-05-11</v>
@@ -14250,7 +14250,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>967</v>
+        <v>1245</v>
       </c>
       <c r="B410" t="str">
         <v>2024-05-11</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>968</v>
+        <v>1246</v>
       </c>
       <c r="B411" t="str">
         <v>2024-05-11</v>
@@ -14314,7 +14314,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>969</v>
+        <v>1247</v>
       </c>
       <c r="B412" t="str">
         <v>2024-05-11</v>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>970</v>
+        <v>1248</v>
       </c>
       <c r="B413" t="str">
         <v>2024-05-11</v>
@@ -14378,7 +14378,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>971</v>
+        <v>1249</v>
       </c>
       <c r="B414" t="str">
         <v>2024-05-11</v>
@@ -14410,7 +14410,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>972</v>
+        <v>1250</v>
       </c>
       <c r="B415" t="str">
         <v>2024-05-11</v>
@@ -14442,7 +14442,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>973</v>
+        <v>1251</v>
       </c>
       <c r="B416" t="str">
         <v>2024-05-11</v>
@@ -14474,7 +14474,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>974</v>
+        <v>1252</v>
       </c>
       <c r="B417" t="str">
         <v>2024-05-11</v>
@@ -14506,7 +14506,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>975</v>
+        <v>1253</v>
       </c>
       <c r="B418" t="str">
         <v>2024-05-11</v>
@@ -14538,7 +14538,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>976</v>
+        <v>1254</v>
       </c>
       <c r="B419" t="str">
         <v>2024-05-11</v>
@@ -14570,7 +14570,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>977</v>
+        <v>1255</v>
       </c>
       <c r="B420" t="str">
         <v>2024-05-11</v>
@@ -14602,7 +14602,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>978</v>
+        <v>1256</v>
       </c>
       <c r="B421" t="str">
         <v>2024-05-11</v>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>979</v>
+        <v>1257</v>
       </c>
       <c r="B422" t="str">
         <v>2024-05-12</v>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>980</v>
+        <v>1258</v>
       </c>
       <c r="B423" t="str">
         <v>2024-05-12</v>
@@ -14698,7 +14698,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>981</v>
+        <v>1259</v>
       </c>
       <c r="B424" t="str">
         <v>2024-05-12</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>982</v>
+        <v>1260</v>
       </c>
       <c r="B425" t="str">
         <v>2024-05-12</v>
@@ -14762,7 +14762,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>983</v>
+        <v>1261</v>
       </c>
       <c r="B426" t="str">
         <v>2024-05-12</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>984</v>
+        <v>1262</v>
       </c>
       <c r="B427" t="str">
         <v>2024-05-12</v>
@@ -14826,7 +14826,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>985</v>
+        <v>1263</v>
       </c>
       <c r="B428" t="str">
         <v>2024-05-12</v>
@@ -14858,7 +14858,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>986</v>
+        <v>1264</v>
       </c>
       <c r="B429" t="str">
         <v>2024-05-12</v>
@@ -14890,7 +14890,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>987</v>
+        <v>1265</v>
       </c>
       <c r="B430" t="str">
         <v>2024-05-12</v>
@@ -14922,7 +14922,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>988</v>
+        <v>1266</v>
       </c>
       <c r="B431" t="str">
         <v>2024-05-12</v>
@@ -14954,7 +14954,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>989</v>
+        <v>1267</v>
       </c>
       <c r="B432" t="str">
         <v>2024-05-12</v>
@@ -14986,7 +14986,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>990</v>
+        <v>1268</v>
       </c>
       <c r="B433" t="str">
         <v>2024-05-12</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>991</v>
+        <v>1269</v>
       </c>
       <c r="B434" t="str">
         <v>2024-05-12</v>
@@ -15050,7 +15050,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>992</v>
+        <v>1270</v>
       </c>
       <c r="B435" t="str">
         <v>2024-05-12</v>
@@ -15082,7 +15082,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>993</v>
+        <v>1271</v>
       </c>
       <c r="B436" t="str">
         <v>2024-05-12</v>
@@ -15114,7 +15114,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>994</v>
+        <v>1272</v>
       </c>
       <c r="B437" t="str">
         <v>2024-05-12</v>
@@ -15146,7 +15146,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>995</v>
+        <v>1273</v>
       </c>
       <c r="B438" t="str">
         <v>2024-05-13</v>
@@ -15178,7 +15178,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>996</v>
+        <v>1274</v>
       </c>
       <c r="B439" t="str">
         <v>2024-05-13</v>
@@ -15210,7 +15210,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>997</v>
+        <v>1275</v>
       </c>
       <c r="B440" t="str">
         <v>2024-05-13</v>
@@ -15242,7 +15242,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>998</v>
+        <v>1276</v>
       </c>
       <c r="B441" t="str">
         <v>2024-05-13</v>
@@ -15274,7 +15274,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>999</v>
+        <v>1277</v>
       </c>
       <c r="B442" t="str">
         <v>2024-05-13</v>
@@ -15306,7 +15306,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>1000</v>
+        <v>1278</v>
       </c>
       <c r="B443" t="str">
         <v>2024-05-13</v>
@@ -15338,7 +15338,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>1001</v>
+        <v>1279</v>
       </c>
       <c r="B444" t="str">
         <v>2024-05-13</v>
@@ -15370,7 +15370,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>1002</v>
+        <v>1280</v>
       </c>
       <c r="B445" t="str">
         <v>2024-05-13</v>
@@ -15402,7 +15402,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>1003</v>
+        <v>1281</v>
       </c>
       <c r="B446" t="str">
         <v>2024-05-13</v>
@@ -15434,7 +15434,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>1004</v>
+        <v>1282</v>
       </c>
       <c r="B447" t="str">
         <v>2024-05-13</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>1005</v>
+        <v>1283</v>
       </c>
       <c r="B448" t="str">
         <v>2024-05-13</v>
@@ -15498,7 +15498,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>1006</v>
+        <v>1284</v>
       </c>
       <c r="B449" t="str">
         <v>2024-05-13</v>
@@ -15530,7 +15530,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>1007</v>
+        <v>1285</v>
       </c>
       <c r="B450" t="str">
         <v>2024-05-13</v>
@@ -15562,7 +15562,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>1008</v>
+        <v>1286</v>
       </c>
       <c r="B451" t="str">
         <v>2024-05-13</v>
@@ -15594,7 +15594,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>1009</v>
+        <v>1287</v>
       </c>
       <c r="B452" t="str">
         <v>2024-05-13</v>
@@ -15626,7 +15626,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>1010</v>
+        <v>1288</v>
       </c>
       <c r="B453" t="str">
         <v>2024-05-13</v>
@@ -15658,7 +15658,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>1011</v>
+        <v>1289</v>
       </c>
       <c r="B454" t="str">
         <v>2024-05-14</v>
@@ -15690,7 +15690,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>1012</v>
+        <v>1290</v>
       </c>
       <c r="B455" t="str">
         <v>2024-05-14</v>
@@ -15722,7 +15722,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>1013</v>
+        <v>1291</v>
       </c>
       <c r="B456" t="str">
         <v>2024-05-14</v>
@@ -15754,7 +15754,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>1014</v>
+        <v>1292</v>
       </c>
       <c r="B457" t="str">
         <v>2024-05-14</v>
@@ -15786,7 +15786,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>1015</v>
+        <v>1293</v>
       </c>
       <c r="B458" t="str">
         <v>2024-05-14</v>
@@ -15818,7 +15818,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>1016</v>
+        <v>1294</v>
       </c>
       <c r="B459" t="str">
         <v>2024-05-14</v>
@@ -15850,7 +15850,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>1017</v>
+        <v>1295</v>
       </c>
       <c r="B460" t="str">
         <v>2024-05-14</v>
@@ -15882,7 +15882,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>1018</v>
+        <v>1296</v>
       </c>
       <c r="B461" t="str">
         <v>2024-05-14</v>
@@ -15914,7 +15914,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>1019</v>
+        <v>1297</v>
       </c>
       <c r="B462" t="str">
         <v>2024-05-14</v>
@@ -15946,7 +15946,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>1020</v>
+        <v>1298</v>
       </c>
       <c r="B463" t="str">
         <v>2024-05-14</v>
@@ -15978,7 +15978,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>1021</v>
+        <v>1299</v>
       </c>
       <c r="B464" t="str">
         <v>2024-05-14</v>
@@ -16010,7 +16010,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>1022</v>
+        <v>1300</v>
       </c>
       <c r="B465" t="str">
         <v>2024-05-14</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>1023</v>
+        <v>1301</v>
       </c>
       <c r="B466" t="str">
         <v>2024-05-14</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>1024</v>
+        <v>1302</v>
       </c>
       <c r="B467" t="str">
         <v>2024-05-14</v>
@@ -16106,7 +16106,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>1025</v>
+        <v>1303</v>
       </c>
       <c r="B468" t="str">
         <v>2024-05-14</v>
@@ -16138,7 +16138,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>1026</v>
+        <v>1304</v>
       </c>
       <c r="B469" t="str">
         <v>2024-05-14</v>
@@ -16170,7 +16170,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>1027</v>
+        <v>1305</v>
       </c>
       <c r="B470" t="str">
         <v>2024-05-15</v>
@@ -16202,7 +16202,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>1028</v>
+        <v>1306</v>
       </c>
       <c r="B471" t="str">
         <v>2024-05-15</v>
@@ -16234,7 +16234,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>1029</v>
+        <v>1307</v>
       </c>
       <c r="B472" t="str">
         <v>2024-05-15</v>
@@ -16266,7 +16266,7 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>1030</v>
+        <v>1308</v>
       </c>
       <c r="B473" t="str">
         <v>2024-05-15</v>
@@ -16298,7 +16298,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>1031</v>
+        <v>1309</v>
       </c>
       <c r="B474" t="str">
         <v>2024-05-15</v>
@@ -16330,7 +16330,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>1032</v>
+        <v>1310</v>
       </c>
       <c r="B475" t="str">
         <v>2024-05-15</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>1033</v>
+        <v>1311</v>
       </c>
       <c r="B476" t="str">
         <v>2024-05-15</v>
@@ -16394,7 +16394,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>1034</v>
+        <v>1312</v>
       </c>
       <c r="B477" t="str">
         <v>2024-05-15</v>
@@ -16426,7 +16426,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>1035</v>
+        <v>1313</v>
       </c>
       <c r="B478" t="str">
         <v>2024-05-15</v>
@@ -16458,7 +16458,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>1036</v>
+        <v>1314</v>
       </c>
       <c r="B479" t="str">
         <v>2024-05-15</v>
@@ -16490,7 +16490,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>1037</v>
+        <v>1315</v>
       </c>
       <c r="B480" t="str">
         <v>2024-05-15</v>
@@ -16522,7 +16522,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>1038</v>
+        <v>1316</v>
       </c>
       <c r="B481" t="str">
         <v>2024-05-15</v>
@@ -16554,7 +16554,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>1039</v>
+        <v>1317</v>
       </c>
       <c r="B482" t="str">
         <v>2024-05-15</v>
@@ -16586,7 +16586,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>1040</v>
+        <v>1318</v>
       </c>
       <c r="B483" t="str">
         <v>2024-05-15</v>
@@ -16618,7 +16618,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>1041</v>
+        <v>1319</v>
       </c>
       <c r="B484" t="str">
         <v>2024-05-15</v>
@@ -16650,7 +16650,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="B485" t="str">
         <v>2024-05-15</v>
@@ -16682,7 +16682,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1043</v>
+        <v>1321</v>
       </c>
       <c r="B486" t="str">
         <v>2024-05-15</v>
@@ -16714,7 +16714,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1044</v>
+        <v>1322</v>
       </c>
       <c r="B487" t="str">
         <v>2024-05-16</v>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>1045</v>
+        <v>1323</v>
       </c>
       <c r="B488" t="str">
         <v>2024-05-16</v>
@@ -16778,7 +16778,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>1046</v>
+        <v>1324</v>
       </c>
       <c r="B489" t="str">
         <v>2024-05-16</v>
@@ -16810,7 +16810,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>1047</v>
+        <v>1325</v>
       </c>
       <c r="B490" t="str">
         <v>2024-05-16</v>
@@ -16842,7 +16842,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>1048</v>
+        <v>1326</v>
       </c>
       <c r="B491" t="str">
         <v>2024-05-16</v>
@@ -16874,7 +16874,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1049</v>
+        <v>1327</v>
       </c>
       <c r="B492" t="str">
         <v>2024-05-16</v>
@@ -16906,7 +16906,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>1050</v>
+        <v>1328</v>
       </c>
       <c r="B493" t="str">
         <v>2024-05-16</v>
@@ -16938,7 +16938,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>1051</v>
+        <v>1329</v>
       </c>
       <c r="B494" t="str">
         <v>2024-05-16</v>
@@ -16970,7 +16970,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>1052</v>
+        <v>1330</v>
       </c>
       <c r="B495" t="str">
         <v>2024-05-16</v>
@@ -17002,7 +17002,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>1053</v>
+        <v>1331</v>
       </c>
       <c r="B496" t="str">
         <v>2024-05-16</v>
@@ -17034,7 +17034,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>1054</v>
+        <v>1332</v>
       </c>
       <c r="B497" t="str">
         <v>2024-05-16</v>
@@ -17066,7 +17066,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>1055</v>
+        <v>1333</v>
       </c>
       <c r="B498" t="str">
         <v>2024-05-16</v>
@@ -17098,7 +17098,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>1056</v>
+        <v>1334</v>
       </c>
       <c r="B499" t="str">
         <v>2024-05-16</v>
@@ -17130,7 +17130,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>1057</v>
+        <v>1335</v>
       </c>
       <c r="B500" t="str">
         <v>2024-05-16</v>
@@ -17162,7 +17162,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>1058</v>
+        <v>1336</v>
       </c>
       <c r="B501" t="str">
         <v>2024-05-16</v>
@@ -17194,7 +17194,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>1059</v>
+        <v>1337</v>
       </c>
       <c r="B502" t="str">
         <v>2024-05-16</v>
@@ -17226,7 +17226,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>1060</v>
+        <v>1338</v>
       </c>
       <c r="B503" t="str">
         <v>2024-05-16</v>
@@ -17258,7 +17258,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>1061</v>
+        <v>1339</v>
       </c>
       <c r="B504" t="str">
         <v>2024-05-16</v>
@@ -17290,7 +17290,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>1062</v>
+        <v>1340</v>
       </c>
       <c r="B505" t="str">
         <v>2024-05-16</v>
@@ -17322,7 +17322,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>1063</v>
+        <v>1341</v>
       </c>
       <c r="B506" t="str">
         <v>2024-05-17</v>
@@ -17354,7 +17354,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>1064</v>
+        <v>1342</v>
       </c>
       <c r="B507" t="str">
         <v>2024-05-17</v>
@@ -17386,7 +17386,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>1065</v>
+        <v>1343</v>
       </c>
       <c r="B508" t="str">
         <v>2024-05-17</v>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>1066</v>
+        <v>1344</v>
       </c>
       <c r="B509" t="str">
         <v>2024-05-17</v>
@@ -17450,7 +17450,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>1067</v>
+        <v>1345</v>
       </c>
       <c r="B510" t="str">
         <v>2024-05-17</v>
@@ -17482,7 +17482,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>1068</v>
+        <v>1346</v>
       </c>
       <c r="B511" t="str">
         <v>2024-05-17</v>
@@ -17514,7 +17514,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>1069</v>
+        <v>1347</v>
       </c>
       <c r="B512" t="str">
         <v>2024-05-17</v>
@@ -17546,7 +17546,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>1070</v>
+        <v>1348</v>
       </c>
       <c r="B513" t="str">
         <v>2024-05-17</v>
@@ -17578,7 +17578,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>1071</v>
+        <v>1349</v>
       </c>
       <c r="B514" t="str">
         <v>2024-05-17</v>
@@ -17610,7 +17610,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>1072</v>
+        <v>1350</v>
       </c>
       <c r="B515" t="str">
         <v>2024-05-17</v>
@@ -17642,7 +17642,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>1073</v>
+        <v>1351</v>
       </c>
       <c r="B516" t="str">
         <v>2024-05-18</v>
@@ -17674,7 +17674,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>1074</v>
+        <v>1352</v>
       </c>
       <c r="B517" t="str">
         <v>2024-05-18</v>
@@ -17706,7 +17706,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>1075</v>
+        <v>1353</v>
       </c>
       <c r="B518" t="str">
         <v>2024-05-18</v>
@@ -17738,7 +17738,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>1076</v>
+        <v>1354</v>
       </c>
       <c r="B519" t="str">
         <v>2024-05-18</v>
@@ -17770,7 +17770,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>1077</v>
+        <v>1355</v>
       </c>
       <c r="B520" t="str">
         <v>2024-05-18</v>
@@ -17802,7 +17802,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>1078</v>
+        <v>1356</v>
       </c>
       <c r="B521" t="str">
         <v>2024-05-18</v>
@@ -17834,7 +17834,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>1079</v>
+        <v>1357</v>
       </c>
       <c r="B522" t="str">
         <v>2024-05-18</v>
@@ -17866,7 +17866,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>1080</v>
+        <v>1358</v>
       </c>
       <c r="B523" t="str">
         <v>2024-05-18</v>
@@ -17898,7 +17898,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>1081</v>
+        <v>1359</v>
       </c>
       <c r="B524" t="str">
         <v>2024-05-18</v>
@@ -17930,7 +17930,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>1082</v>
+        <v>1360</v>
       </c>
       <c r="B525" t="str">
         <v>2024-05-18</v>
@@ -17962,7 +17962,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>1083</v>
+        <v>1396</v>
       </c>
       <c r="B526" t="str">
         <v>2024-05-19</v>
@@ -17994,7 +17994,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>1084</v>
+        <v>1397</v>
       </c>
       <c r="B527" t="str">
         <v>2024-05-19</v>
@@ -18026,7 +18026,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>1085</v>
+        <v>1398</v>
       </c>
       <c r="B528" t="str">
         <v>2024-05-19</v>
@@ -18058,7 +18058,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>1086</v>
+        <v>1399</v>
       </c>
       <c r="B529" t="str">
         <v>2024-05-19</v>
@@ -18090,7 +18090,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>1087</v>
+        <v>1400</v>
       </c>
       <c r="B530" t="str">
         <v>2024-05-19</v>
@@ -18122,7 +18122,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>1088</v>
+        <v>1401</v>
       </c>
       <c r="B531" t="str">
         <v>2024-05-19</v>
@@ -18154,7 +18154,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>1089</v>
+        <v>1402</v>
       </c>
       <c r="B532" t="str">
         <v>2024-05-19</v>
@@ -18186,7 +18186,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>1090</v>
+        <v>1403</v>
       </c>
       <c r="B533" t="str">
         <v>2024-05-19</v>
@@ -18218,7 +18218,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>1091</v>
+        <v>1404</v>
       </c>
       <c r="B534" t="str">
         <v>2024-05-19</v>
@@ -18250,7 +18250,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>1092</v>
+        <v>1405</v>
       </c>
       <c r="B535" t="str">
         <v>2024-05-19</v>
@@ -18282,7 +18282,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>1093</v>
+        <v>1442</v>
       </c>
       <c r="B536" t="str">
         <v>2024-05-20</v>
@@ -18314,7 +18314,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>1094</v>
+        <v>1443</v>
       </c>
       <c r="B537" t="str">
         <v>2024-05-20</v>
@@ -18346,7 +18346,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>1095</v>
+        <v>1444</v>
       </c>
       <c r="B538" t="str">
         <v>2024-05-20</v>
@@ -18378,7 +18378,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>1096</v>
+        <v>1445</v>
       </c>
       <c r="B539" t="str">
         <v>2024-05-20</v>
@@ -18410,7 +18410,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>1097</v>
+        <v>1446</v>
       </c>
       <c r="B540" t="str">
         <v>2024-05-20</v>
@@ -18442,7 +18442,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>1098</v>
+        <v>1447</v>
       </c>
       <c r="B541" t="str">
         <v>2024-05-20</v>
@@ -18474,7 +18474,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>1099</v>
+        <v>1448</v>
       </c>
       <c r="B542" t="str">
         <v>2024-05-20</v>
@@ -18506,7 +18506,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>1100</v>
+        <v>1449</v>
       </c>
       <c r="B543" t="str">
         <v>2024-05-20</v>
@@ -18538,7 +18538,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>1101</v>
+        <v>1450</v>
       </c>
       <c r="B544" t="str">
         <v>2024-05-20</v>
@@ -18570,7 +18570,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>1102</v>
+        <v>1451</v>
       </c>
       <c r="B545" t="str">
         <v>2024-05-20</v>
@@ -18602,7 +18602,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>1103</v>
+        <v>1452</v>
       </c>
       <c r="B546" t="str">
         <v>2024-05-20</v>
@@ -18634,7 +18634,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>1104</v>
+        <v>1471</v>
       </c>
       <c r="B547" t="str">
         <v>2024-05-21</v>
@@ -18666,7 +18666,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>1105</v>
+        <v>1472</v>
       </c>
       <c r="B548" t="str">
         <v>2024-05-21</v>
@@ -18698,7 +18698,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>1106</v>
+        <v>1473</v>
       </c>
       <c r="B549" t="str">
         <v>2024-05-21</v>
@@ -18730,7 +18730,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>1107</v>
+        <v>1474</v>
       </c>
       <c r="B550" t="str">
         <v>2024-05-21</v>
@@ -18762,7 +18762,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>1108</v>
+        <v>1475</v>
       </c>
       <c r="B551" t="str">
         <v>2024-05-21</v>
@@ -18794,7 +18794,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>1109</v>
+        <v>1476</v>
       </c>
       <c r="B552" t="str">
         <v>2024-05-21</v>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>1110</v>
+        <v>1477</v>
       </c>
       <c r="B553" t="str">
         <v>2024-05-21</v>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>1111</v>
+        <v>1478</v>
       </c>
       <c r="B554" t="str">
         <v>2024-05-21</v>
@@ -18890,7 +18890,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>1112</v>
+        <v>1479</v>
       </c>
       <c r="B555" t="str">
         <v>2024-05-21</v>
@@ -18922,7 +18922,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>1113</v>
+        <v>1480</v>
       </c>
       <c r="B556" t="str">
         <v>2024-05-21</v>
@@ -18954,7 +18954,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>1114</v>
+        <v>1481</v>
       </c>
       <c r="B557" t="str">
         <v>2024-05-21</v>
@@ -18986,7 +18986,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>1115</v>
+        <v>1482</v>
       </c>
       <c r="B558" t="str">
         <v>2024-05-22</v>
@@ -19018,7 +19018,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>1116</v>
+        <v>1483</v>
       </c>
       <c r="B559" t="str">
         <v>2024-05-22</v>
@@ -19050,7 +19050,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>1117</v>
+        <v>1484</v>
       </c>
       <c r="B560" t="str">
         <v>2024-05-22</v>
@@ -19082,7 +19082,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>1118</v>
+        <v>1485</v>
       </c>
       <c r="B561" t="str">
         <v>2024-05-22</v>
@@ -19114,7 +19114,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>1119</v>
+        <v>1486</v>
       </c>
       <c r="B562" t="str">
         <v>2024-05-22</v>
@@ -19146,7 +19146,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>1120</v>
+        <v>1487</v>
       </c>
       <c r="B563" t="str">
         <v>2024-05-22</v>
@@ -19178,7 +19178,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>1121</v>
+        <v>1488</v>
       </c>
       <c r="B564" t="str">
         <v>2024-05-22</v>
@@ -19210,7 +19210,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>1122</v>
+        <v>1489</v>
       </c>
       <c r="B565" t="str">
         <v>2024-05-22</v>
@@ -19242,7 +19242,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>1123</v>
+        <v>1490</v>
       </c>
       <c r="B566" t="str">
         <v>2024-05-22</v>
@@ -19274,7 +19274,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>1124</v>
+        <v>1491</v>
       </c>
       <c r="B567" t="str">
         <v>2024-05-22</v>
@@ -19306,7 +19306,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>1125</v>
+        <v>1492</v>
       </c>
       <c r="B568" t="str">
         <v>2024-05-22</v>
@@ -19338,7 +19338,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>1126</v>
+        <v>1493</v>
       </c>
       <c r="B569" t="str">
         <v>2024-05-23</v>
@@ -19370,7 +19370,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>1127</v>
+        <v>1494</v>
       </c>
       <c r="B570" t="str">
         <v>2024-05-23</v>
@@ -19402,7 +19402,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>1128</v>
+        <v>1495</v>
       </c>
       <c r="B571" t="str">
         <v>2024-05-23</v>
@@ -19434,7 +19434,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>1129</v>
+        <v>1496</v>
       </c>
       <c r="B572" t="str">
         <v>2024-05-23</v>
@@ -19466,7 +19466,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>1130</v>
+        <v>1497</v>
       </c>
       <c r="B573" t="str">
         <v>2024-05-23</v>
@@ -19498,7 +19498,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>1131</v>
+        <v>1498</v>
       </c>
       <c r="B574" t="str">
         <v>2024-05-23</v>
@@ -19530,7 +19530,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>1132</v>
+        <v>1499</v>
       </c>
       <c r="B575" t="str">
         <v>2024-05-24</v>
@@ -19562,7 +19562,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>1133</v>
+        <v>1500</v>
       </c>
       <c r="B576" t="str">
         <v>2024-05-25</v>
@@ -19594,7 +19594,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>1134</v>
+        <v>1501</v>
       </c>
       <c r="B577" t="str">
         <v>2024-05-27</v>
@@ -19626,7 +19626,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>1135</v>
+        <v>1502</v>
       </c>
       <c r="B578" t="str">
         <v>2024-05-28</v>
@@ -19658,7 +19658,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>1136</v>
+        <v>1503</v>
       </c>
       <c r="B579" t="str">
         <v>2024-05-29</v>
@@ -19690,7 +19690,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>1137</v>
+        <v>1504</v>
       </c>
       <c r="B580" t="str">
         <v>2024-05-30</v>
@@ -19722,7 +19722,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>1138</v>
+        <v>1505</v>
       </c>
       <c r="B581" t="str">
         <v>2024-05-30</v>
@@ -19754,7 +19754,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>1139</v>
+        <v>1539</v>
       </c>
       <c r="B582" t="str">
         <v>2024-06-01</v>
@@ -19786,7 +19786,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>1140</v>
+        <v>1540</v>
       </c>
       <c r="B583" t="str">
         <v>2024-06-01</v>
@@ -19818,7 +19818,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>1141</v>
+        <v>1541</v>
       </c>
       <c r="B584" t="str">
         <v>2024-06-01</v>
@@ -19850,7 +19850,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>1142</v>
+        <v>1542</v>
       </c>
       <c r="B585" t="str">
         <v>2024-06-02</v>
@@ -19882,7 +19882,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>1143</v>
+        <v>1543</v>
       </c>
       <c r="B586" t="str">
         <v>2024-06-02</v>
@@ -19914,7 +19914,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>1144</v>
+        <v>1544</v>
       </c>
       <c r="B587" t="str">
         <v>2024-06-07</v>
@@ -19946,7 +19946,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>1145</v>
+        <v>1565</v>
       </c>
       <c r="B588" t="str">
         <v>2024-06-17</v>
@@ -19978,7 +19978,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>1146</v>
+        <v>1566</v>
       </c>
       <c r="B589" t="str">
         <v>2024-06-17</v>
@@ -20010,7 +20010,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>1147</v>
+        <v>1567</v>
       </c>
       <c r="B590" t="str">
         <v>2024-06-17</v>
@@ -20042,7 +20042,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>1148</v>
+        <v>1568</v>
       </c>
       <c r="B591" t="str">
         <v>2024-06-17</v>
@@ -20074,7 +20074,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>1149</v>
+        <v>1569</v>
       </c>
       <c r="B592" t="str">
         <v>2024-06-18</v>
@@ -20106,7 +20106,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1150</v>
+        <v>1570</v>
       </c>
       <c r="B593" t="str">
         <v>2024-06-18</v>
@@ -20138,7 +20138,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1151</v>
+        <v>1571</v>
       </c>
       <c r="B594" t="str">
         <v>2024-06-18</v>
@@ -20170,7 +20170,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>1152</v>
+        <v>1572</v>
       </c>
       <c r="B595" t="str">
         <v>2024-06-19</v>
@@ -20202,7 +20202,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>1153</v>
+        <v>1573</v>
       </c>
       <c r="B596" t="str">
         <v>2024-06-19</v>
@@ -20234,7 +20234,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>1154</v>
+        <v>1574</v>
       </c>
       <c r="B597" t="str">
         <v>2024-06-19</v>
@@ -20266,7 +20266,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>1155</v>
+        <v>1575</v>
       </c>
       <c r="B598" t="str">
         <v>2024-06-20</v>
@@ -20298,7 +20298,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>1156</v>
+        <v>1576</v>
       </c>
       <c r="B599" t="str">
         <v>2024-06-23</v>
@@ -20330,7 +20330,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>1157</v>
+        <v>1577</v>
       </c>
       <c r="B600" t="str">
         <v>2024-06-23</v>
@@ -20362,7 +20362,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>1158</v>
+        <v>1578</v>
       </c>
       <c r="B601" t="str">
         <v>2024-06-23</v>
@@ -20394,7 +20394,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>1159</v>
+        <v>1579</v>
       </c>
       <c r="B602" t="str">
         <v>2024-06-24</v>
@@ -20426,7 +20426,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>1160</v>
+        <v>1580</v>
       </c>
       <c r="B603" t="str">
         <v>2024-06-24</v>
@@ -20458,7 +20458,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>1161</v>
+        <v>1581</v>
       </c>
       <c r="B604" t="str">
         <v>2024-06-24</v>
@@ -20490,7 +20490,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>1162</v>
+        <v>1582</v>
       </c>
       <c r="B605" t="str">
         <v>2024-06-24</v>
@@ -20522,7 +20522,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>1163</v>
+        <v>1583</v>
       </c>
       <c r="B606" t="str">
         <v>2024-06-25</v>
@@ -20554,7 +20554,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>1164</v>
+        <v>1584</v>
       </c>
       <c r="B607" t="str">
         <v>2024-06-25</v>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>1165</v>
+        <v>1585</v>
       </c>
       <c r="B608" t="str">
         <v>2024-06-25</v>
@@ -20618,7 +20618,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>1166</v>
+        <v>1586</v>
       </c>
       <c r="B609" t="str">
         <v>2024-06-26</v>
@@ -20650,7 +20650,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>1167</v>
+        <v>1587</v>
       </c>
       <c r="B610" t="str">
         <v>2024-06-26</v>
@@ -20682,7 +20682,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>1168</v>
+        <v>1588</v>
       </c>
       <c r="B611" t="str">
         <v>2024-06-26</v>
@@ -20714,7 +20714,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>1169</v>
+        <v>1589</v>
       </c>
       <c r="B612" t="str">
         <v>2024-06-27</v>
@@ -20746,7 +20746,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>1170</v>
+        <v>1590</v>
       </c>
       <c r="B613" t="str">
         <v>2024-06-28</v>
@@ -20778,7 +20778,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>1171</v>
+        <v>1591</v>
       </c>
       <c r="B614" t="str">
         <v>2024-06-29</v>
@@ -20810,7 +20810,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>1172</v>
+        <v>1592</v>
       </c>
       <c r="B615" t="str">
         <v>2024-06-29</v>
@@ -20842,7 +20842,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>1173</v>
+        <v>1593</v>
       </c>
       <c r="B616" t="str">
         <v>2024-06-29</v>
@@ -20874,7 +20874,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>1174</v>
+        <v>1594</v>
       </c>
       <c r="B617" t="str">
         <v>2024-06-30</v>
@@ -20906,7 +20906,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>1175</v>
+        <v>1595</v>
       </c>
       <c r="B618" t="str">
         <v>2024-06-30</v>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>1176</v>
+        <v>1600</v>
       </c>
       <c r="B619" t="str">
         <v>2024-07-01</v>
@@ -20970,7 +20970,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>1177</v>
+        <v>1601</v>
       </c>
       <c r="B620" t="str">
         <v>2024-07-02</v>
@@ -21002,7 +21002,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>1178</v>
+        <v>1602</v>
       </c>
       <c r="B621" t="str">
         <v>2024-07-03</v>
@@ -21034,7 +21034,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>1179</v>
+        <v>1603</v>
       </c>
       <c r="B622" t="str">
         <v>2024-07-04</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>1180</v>
+        <v>1604</v>
       </c>
       <c r="B623" t="str">
         <v>2024-07-04</v>
@@ -21098,7 +21098,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>1181</v>
+        <v>1605</v>
       </c>
       <c r="B624" t="str">
         <v>2024-07-04</v>
@@ -21130,7 +21130,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>1182</v>
+        <v>1606</v>
       </c>
       <c r="B625" t="str">
         <v>2024-07-27</v>
@@ -21162,7 +21162,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>1183</v>
+        <v>1621</v>
       </c>
       <c r="B626" t="str">
         <v>2024-10-12</v>
@@ -21194,7 +21194,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>1184</v>
+        <v>1622</v>
       </c>
       <c r="B627" t="str">
         <v>2024-10-13</v>
@@ -21226,7 +21226,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>1185</v>
+        <v>1623</v>
       </c>
       <c r="B628" t="str">
         <v>2024-10-13</v>
@@ -21258,7 +21258,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>1186</v>
+        <v>1624</v>
       </c>
       <c r="B629" t="str">
         <v>2024-10-14</v>
@@ -21290,7 +21290,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>1187</v>
+        <v>1625</v>
       </c>
       <c r="B630" t="str">
         <v>2024-10-17</v>
@@ -21322,7 +21322,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>1188</v>
+        <v>1626</v>
       </c>
       <c r="B631" t="str">
         <v>2024-10-17</v>
@@ -21354,7 +21354,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>1189</v>
+        <v>1627</v>
       </c>
       <c r="B632" t="str">
         <v>2024-10-17</v>
@@ -21386,7 +21386,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>1190</v>
+        <v>1628</v>
       </c>
       <c r="B633" t="str">
         <v>2024-10-17</v>
@@ -21418,7 +21418,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>1191</v>
+        <v>1629</v>
       </c>
       <c r="B634" t="str">
         <v>2024-10-25</v>
@@ -21450,7 +21450,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>1192</v>
+        <v>1630</v>
       </c>
       <c r="B635" t="str">
         <v>2024-10-25</v>
@@ -21482,7 +21482,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>1193</v>
+        <v>1631</v>
       </c>
       <c r="B636" t="str">
         <v>2024-10-25</v>
@@ -21514,7 +21514,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>1194</v>
+        <v>1632</v>
       </c>
       <c r="B637" t="str">
         <v>2024-10-25</v>
@@ -21546,7 +21546,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>1195</v>
+        <v>1633</v>
       </c>
       <c r="B638" t="str">
         <v>2024-10-25</v>
@@ -21578,7 +21578,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>1196</v>
+        <v>1634</v>
       </c>
       <c r="B639" t="str">
         <v>2024-10-25</v>
@@ -21610,7 +21610,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>1197</v>
+        <v>1635</v>
       </c>
       <c r="B640" t="str">
         <v>2024-10-25</v>
@@ -21642,7 +21642,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>1198</v>
+        <v>1636</v>
       </c>
       <c r="B641" t="str">
         <v>2024-10-25</v>
@@ -21674,7 +21674,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>1199</v>
+        <v>1637</v>
       </c>
       <c r="B642" t="str">
         <v>2024-10-25</v>
@@ -21706,7 +21706,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>1201</v>
+        <v>1639</v>
       </c>
       <c r="B643" t="str">
         <v>2024-11-03</v>
@@ -21738,7 +21738,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>1202</v>
+        <v>1640</v>
       </c>
       <c r="B644" t="str">
         <v>2024-11-03</v>
@@ -21770,7 +21770,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>1203</v>
+        <v>1641</v>
       </c>
       <c r="B645" t="str">
         <v>2024-11-13</v>
@@ -21802,7 +21802,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>1204</v>
+        <v>1642</v>
       </c>
       <c r="B646" t="str">
         <v>2024-11-13</v>
@@ -21834,7 +21834,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>1205</v>
+        <v>1643</v>
       </c>
       <c r="B647" t="str">
         <v>2024-11-13</v>
@@ -21866,7 +21866,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>1206</v>
+        <v>1644</v>
       </c>
       <c r="B648" t="str">
         <v>2024-11-14</v>
@@ -21898,7 +21898,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>1207</v>
+        <v>1645</v>
       </c>
       <c r="B649" t="str">
         <v>2024-11-28</v>
@@ -21930,7 +21930,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>1208</v>
+        <v>1646</v>
       </c>
       <c r="B650" t="str">
         <v>2024-11-29</v>
@@ -21962,7 +21962,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>1209</v>
+        <v>1647</v>
       </c>
       <c r="B651" t="str">
         <v>2024-11-29</v>
@@ -21994,7 +21994,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>1210</v>
+        <v>1648</v>
       </c>
       <c r="B652" t="str">
         <v>2024-11-30</v>
@@ -22026,7 +22026,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>1211</v>
+        <v>1649</v>
       </c>
       <c r="B653" t="str">
         <v>2024-12-01</v>
@@ -22058,7 +22058,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>1212</v>
+        <v>1650</v>
       </c>
       <c r="B654" t="str">
         <v>2024-12-07</v>
@@ -22090,7 +22090,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>1213</v>
+        <v>1651</v>
       </c>
       <c r="B655" t="str">
         <v>2024-12-10</v>
@@ -22122,7 +22122,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>1214</v>
+        <v>1652</v>
       </c>
       <c r="B656" t="str">
         <v>2024-12-10</v>
@@ -22154,7 +22154,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>1215</v>
+        <v>1653</v>
       </c>
       <c r="B657" t="str">
         <v>2024-12-10</v>
@@ -22186,7 +22186,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>1216</v>
+        <v>1654</v>
       </c>
       <c r="B658" t="str">
         <v>2024-12-10</v>
@@ -22218,7 +22218,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>1217</v>
+        <v>1655</v>
       </c>
       <c r="B659" t="str">
         <v>2024-12-10</v>
@@ -22250,7 +22250,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>1218</v>
+        <v>1656</v>
       </c>
       <c r="B660" t="str">
         <v>2024-12-10</v>
@@ -22282,7 +22282,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>1219</v>
+        <v>1657</v>
       </c>
       <c r="B661" t="str">
         <v>2024-12-15</v>
@@ -22314,7 +22314,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>1220</v>
+        <v>1658</v>
       </c>
       <c r="B662" t="str">
         <v>2024-12-15</v>
@@ -22346,7 +22346,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>1221</v>
+        <v>1659</v>
       </c>
       <c r="B663" t="str">
         <v>2024-12-15</v>
@@ -22378,7 +22378,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>1222</v>
+        <v>1660</v>
       </c>
       <c r="B664" t="str">
         <v>2024-12-17</v>
@@ -22410,7 +22410,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>1223</v>
+        <v>1661</v>
       </c>
       <c r="B665" t="str">
         <v>2024-12-17</v>
@@ -22442,7 +22442,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>1224</v>
+        <v>1662</v>
       </c>
       <c r="B666" t="str">
         <v>2024-12-19</v>
@@ -22474,7 +22474,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>1225</v>
+        <v>1663</v>
       </c>
       <c r="B667" t="str">
         <v>2024-12-19</v>
@@ -22506,7 +22506,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>1226</v>
+        <v>1664</v>
       </c>
       <c r="B668" t="str">
         <v>2024-12-20</v>
@@ -22538,7 +22538,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>1227</v>
+        <v>1665</v>
       </c>
       <c r="B669" t="str">
         <v>2024-12-21</v>
@@ -22570,7 +22570,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>1228</v>
+        <v>1666</v>
       </c>
       <c r="B670" t="str">
         <v>2024-12-24</v>
@@ -22602,7 +22602,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>1229</v>
+        <v>1667</v>
       </c>
       <c r="B671" t="str">
         <v>2024-12-24</v>
@@ -22634,7 +22634,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>1230</v>
+        <v>1668</v>
       </c>
       <c r="B672" t="str">
         <v>2024-12-25</v>
@@ -22666,7 +22666,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>1231</v>
+        <v>1669</v>
       </c>
       <c r="B673" t="str">
         <v>2024-12-25</v>
@@ -22698,7 +22698,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>1232</v>
+        <v>1670</v>
       </c>
       <c r="B674" t="str">
         <v>2024-12-25</v>
@@ -22730,7 +22730,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>1233</v>
+        <v>1671</v>
       </c>
       <c r="B675" t="str">
         <v>2024-12-25</v>
@@ -22762,7 +22762,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>1234</v>
+        <v>1672</v>
       </c>
       <c r="B676" t="str">
         <v>2024-12-25</v>
@@ -22794,7 +22794,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>1235</v>
+        <v>1673</v>
       </c>
       <c r="B677" t="str">
         <v>2024-12-26</v>
@@ -22826,7 +22826,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>1236</v>
+        <v>1674</v>
       </c>
       <c r="B678" t="str">
         <v>2024-12-26</v>
@@ -22858,7 +22858,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>1237</v>
+        <v>1675</v>
       </c>
       <c r="B679" t="str">
         <v>2024-12-26</v>
@@ -22890,7 +22890,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>1238</v>
+        <v>1676</v>
       </c>
       <c r="B680" t="str">
         <v>2024-12-27</v>
@@ -22922,7 +22922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>1239</v>
+        <v>1677</v>
       </c>
       <c r="B681" t="str">
         <v>2024-12-30</v>
@@ -22954,7 +22954,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>1240</v>
+        <v>1678</v>
       </c>
       <c r="B682" t="str">
         <v>2024-12-30</v>
@@ -22986,7 +22986,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>1241</v>
+        <v>1679</v>
       </c>
       <c r="B683" t="str">
         <v>2024-12-30</v>
@@ -23018,7 +23018,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>1242</v>
+        <v>1680</v>
       </c>
       <c r="B684" t="str">
         <v>2024-12-30</v>
@@ -23050,7 +23050,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>1243</v>
+        <v>1681</v>
       </c>
       <c r="B685" t="str">
         <v>2024-12-30</v>
@@ -23082,7 +23082,7 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>1244</v>
+        <v>1682</v>
       </c>
       <c r="B686" t="str">
         <v>2025-01-01</v>
@@ -23114,7 +23114,7 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>1245</v>
+        <v>1683</v>
       </c>
       <c r="B687" t="str">
         <v>2025-01-01</v>
@@ -23146,7 +23146,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>1246</v>
+        <v>1684</v>
       </c>
       <c r="B688" t="str">
         <v>2025-01-01</v>
@@ -23178,7 +23178,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>1247</v>
+        <v>1685</v>
       </c>
       <c r="B689" t="str">
         <v>2025-01-01</v>
@@ -23210,7 +23210,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>1248</v>
+        <v>1686</v>
       </c>
       <c r="B690" t="str">
         <v>2025-01-01</v>
@@ -23242,7 +23242,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>1249</v>
+        <v>1699</v>
       </c>
       <c r="B691" t="str">
         <v>2025-01-05</v>
@@ -23274,7 +23274,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>1250</v>
+        <v>1700</v>
       </c>
       <c r="B692" t="str">
         <v>2025-01-08</v>
@@ -23306,7 +23306,7 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>1251</v>
+        <v>1701</v>
       </c>
       <c r="B693" t="str">
         <v>2025-01-08</v>
@@ -23338,7 +23338,7 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>1252</v>
+        <v>1702</v>
       </c>
       <c r="B694" t="str">
         <v>2025-01-08</v>
@@ -23370,7 +23370,7 @@
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>1253</v>
+        <v>1703</v>
       </c>
       <c r="B695" t="str">
         <v>2025-01-08</v>
@@ -23402,7 +23402,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>1254</v>
+        <v>1704</v>
       </c>
       <c r="B696" t="str">
         <v>2025-01-09</v>
@@ -23434,7 +23434,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>1255</v>
+        <v>1705</v>
       </c>
       <c r="B697" t="str">
         <v>2025-01-11</v>
@@ -23466,7 +23466,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>1256</v>
+        <v>1706</v>
       </c>
       <c r="B698" t="str">
         <v>2025-01-11</v>
@@ -23498,7 +23498,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>1257</v>
+        <v>1707</v>
       </c>
       <c r="B699" t="str">
         <v>2025-01-12</v>
@@ -23530,7 +23530,7 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>1258</v>
+        <v>1708</v>
       </c>
       <c r="B700" t="str">
         <v>2025-01-12</v>
@@ -23562,7 +23562,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>1259</v>
+        <v>1709</v>
       </c>
       <c r="B701" t="str">
         <v>2025-01-16</v>
@@ -23594,7 +23594,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>1260</v>
+        <v>1710</v>
       </c>
       <c r="B702" t="str">
         <v>2025-01-17</v>
@@ -23626,7 +23626,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>1261</v>
+        <v>1711</v>
       </c>
       <c r="B703" t="str">
         <v>2025-01-17</v>
@@ -23658,7 +23658,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>1262</v>
+        <v>1712</v>
       </c>
       <c r="B704" t="str">
         <v>2025-01-17</v>
@@ -23690,7 +23690,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>1263</v>
+        <v>1713</v>
       </c>
       <c r="B705" t="str">
         <v>2025-01-17</v>
@@ -23722,7 +23722,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>1264</v>
+        <v>1714</v>
       </c>
       <c r="B706" t="str">
         <v>2025-01-17</v>
@@ -23754,7 +23754,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>1265</v>
+        <v>1715</v>
       </c>
       <c r="B707" t="str">
         <v>2025-01-17</v>
@@ -23786,7 +23786,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>1266</v>
+        <v>1716</v>
       </c>
       <c r="B708" t="str">
         <v>2025-01-18</v>
@@ -23818,7 +23818,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>1267</v>
+        <v>1717</v>
       </c>
       <c r="B709" t="str">
         <v>2025-01-18</v>
@@ -23850,7 +23850,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>1268</v>
+        <v>1718</v>
       </c>
       <c r="B710" t="str">
         <v>2025-01-20</v>
@@ -23882,7 +23882,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>1269</v>
+        <v>1719</v>
       </c>
       <c r="B711" t="str">
         <v>2025-01-20</v>
@@ -23914,7 +23914,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>1270</v>
+        <v>1720</v>
       </c>
       <c r="B712" t="str">
         <v>2025-01-20</v>
@@ -23946,7 +23946,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>1271</v>
+        <v>1721</v>
       </c>
       <c r="B713" t="str">
         <v>2025-01-20</v>
@@ -23978,7 +23978,7 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>1272</v>
+        <v>1722</v>
       </c>
       <c r="B714" t="str">
         <v>2025-01-20</v>
@@ -24010,7 +24010,7 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>1273</v>
+        <v>1723</v>
       </c>
       <c r="B715" t="str">
         <v>2025-01-20</v>
@@ -24042,7 +24042,7 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>1274</v>
+        <v>1724</v>
       </c>
       <c r="B716" t="str">
         <v>2025-01-20</v>
@@ -24074,7 +24074,7 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>1275</v>
+        <v>1725</v>
       </c>
       <c r="B717" t="str">
         <v>2025-01-21</v>
@@ -24106,7 +24106,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>1276</v>
+        <v>1726</v>
       </c>
       <c r="B718" t="str">
         <v>2025-01-22</v>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>1277</v>
+        <v>1727</v>
       </c>
       <c r="B719" t="str">
         <v>2025-01-22</v>
@@ -24170,7 +24170,7 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>1278</v>
+        <v>1728</v>
       </c>
       <c r="B720" t="str">
         <v>2025-01-22</v>
@@ -24202,7 +24202,7 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>1279</v>
+        <v>1729</v>
       </c>
       <c r="B721" t="str">
         <v>2025-01-23</v>
@@ -24234,7 +24234,7 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>1280</v>
+        <v>1730</v>
       </c>
       <c r="B722" t="str">
         <v>2025-01-23</v>
@@ -24266,7 +24266,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>1281</v>
+        <v>1731</v>
       </c>
       <c r="B723" t="str">
         <v>2025-01-25</v>
@@ -24298,7 +24298,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>1282</v>
+        <v>1732</v>
       </c>
       <c r="B724" t="str">
         <v>2025-01-25</v>
@@ -24330,7 +24330,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>1283</v>
+        <v>1733</v>
       </c>
       <c r="B725" t="str">
         <v>2025-01-25</v>
@@ -24362,7 +24362,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>1284</v>
+        <v>1734</v>
       </c>
       <c r="B726" t="str">
         <v>2025-01-25</v>
@@ -24394,7 +24394,7 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>1285</v>
+        <v>1735</v>
       </c>
       <c r="B727" t="str">
         <v>2025-01-26</v>
@@ -24426,7 +24426,7 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>1286</v>
+        <v>1736</v>
       </c>
       <c r="B728" t="str">
         <v>2025-01-26</v>
@@ -24458,7 +24458,7 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>1287</v>
+        <v>1737</v>
       </c>
       <c r="B729" t="str">
         <v>2025-01-26</v>
@@ -24490,7 +24490,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>1288</v>
+        <v>1738</v>
       </c>
       <c r="B730" t="str">
         <v>2025-01-27</v>
@@ -24522,7 +24522,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>1289</v>
+        <v>1739</v>
       </c>
       <c r="B731" t="str">
         <v>2025-01-27</v>
@@ -24554,7 +24554,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>1290</v>
+        <v>1740</v>
       </c>
       <c r="B732" t="str">
         <v>2025-01-27</v>
@@ -24586,7 +24586,7 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>1291</v>
+        <v>1741</v>
       </c>
       <c r="B733" t="str">
         <v>2025-01-28</v>
@@ -24618,7 +24618,7 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>1292</v>
+        <v>1742</v>
       </c>
       <c r="B734" t="str">
         <v>2025-01-28</v>
@@ -24650,7 +24650,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>1293</v>
+        <v>1743</v>
       </c>
       <c r="B735" t="str">
         <v>2025-01-28</v>
@@ -24682,7 +24682,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>1294</v>
+        <v>1744</v>
       </c>
       <c r="B736" t="str">
         <v>2025-01-28</v>
@@ -24714,7 +24714,7 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>1295</v>
+        <v>1745</v>
       </c>
       <c r="B737" t="str">
         <v>2025-01-29</v>
@@ -24746,7 +24746,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>1296</v>
+        <v>1746</v>
       </c>
       <c r="B738" t="str">
         <v>2025-01-29</v>
@@ -24778,7 +24778,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>1297</v>
+        <v>1747</v>
       </c>
       <c r="B739" t="str">
         <v>2025-01-29</v>
@@ -24810,7 +24810,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>1298</v>
+        <v>1748</v>
       </c>
       <c r="B740" t="str">
         <v>2025-01-29</v>
@@ -24842,7 +24842,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>1299</v>
+        <v>1749</v>
       </c>
       <c r="B741" t="str">
         <v>2025-01-29</v>
@@ -24874,7 +24874,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="B742" t="str">
         <v>2025-01-29</v>
@@ -24906,7 +24906,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>1301</v>
+        <v>1751</v>
       </c>
       <c r="B743" t="str">
         <v>2025-01-29</v>
@@ -24938,7 +24938,7 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>1302</v>
+        <v>1752</v>
       </c>
       <c r="B744" t="str">
         <v>2025-02-01</v>
@@ -24970,7 +24970,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>1303</v>
+        <v>1753</v>
       </c>
       <c r="B745" t="str">
         <v>2025-02-01</v>
@@ -25002,7 +25002,7 @@
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>1304</v>
+        <v>1754</v>
       </c>
       <c r="B746" t="str">
         <v>2025-02-01</v>
@@ -25034,7 +25034,7 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>1305</v>
+        <v>1755</v>
       </c>
       <c r="B747" t="str">
         <v>2025-02-12</v>
@@ -25066,7 +25066,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>1306</v>
+        <v>1756</v>
       </c>
       <c r="B748" t="str">
         <v>2025-02-12</v>
@@ -25098,7 +25098,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>1307</v>
+        <v>1757</v>
       </c>
       <c r="B749" t="str">
         <v>2025-02-22</v>
@@ -25130,7 +25130,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>1308</v>
+        <v>1758</v>
       </c>
       <c r="B750" t="str">
         <v>2025-02-22</v>
@@ -25162,7 +25162,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>1309</v>
+        <v>1759</v>
       </c>
       <c r="B751" t="str">
         <v>2025-02-22</v>
@@ -25194,7 +25194,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>1310</v>
+        <v>1844</v>
       </c>
       <c r="B752" t="str">
         <v>2025-04-22</v>
@@ -25226,7 +25226,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>1311</v>
+        <v>1845</v>
       </c>
       <c r="B753" t="str">
         <v>2025-04-23</v>
@@ -25258,7 +25258,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>1312</v>
+        <v>1846</v>
       </c>
       <c r="B754" t="str">
         <v>2025-04-25</v>
@@ -25290,7 +25290,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>1313</v>
+        <v>1847</v>
       </c>
       <c r="B755" t="str">
         <v>2025-04-25</v>
@@ -25322,7 +25322,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>1314</v>
+        <v>1848</v>
       </c>
       <c r="B756" t="str">
         <v>2025-04-25</v>
@@ -25354,7 +25354,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>1315</v>
+        <v>1849</v>
       </c>
       <c r="B757" t="str">
         <v>2025-04-26</v>
@@ -25386,7 +25386,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>1316</v>
+        <v>1850</v>
       </c>
       <c r="B758" t="str">
         <v>2025-04-27</v>
@@ -25418,7 +25418,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>1317</v>
+        <v>1851</v>
       </c>
       <c r="B759" t="str">
         <v>2025-04-27</v>
@@ -25450,7 +25450,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>1318</v>
+        <v>1852</v>
       </c>
       <c r="B760" t="str">
         <v>2025-04-29</v>
@@ -25482,7 +25482,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>1319</v>
+        <v>1853</v>
       </c>
       <c r="B761" t="str">
         <v>2025-04-29</v>
@@ -25514,7 +25514,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>1320</v>
+        <v>1854</v>
       </c>
       <c r="B762" t="str">
         <v>2025-04-29</v>
@@ -25546,7 +25546,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>1321</v>
+        <v>1855</v>
       </c>
       <c r="B763" t="str">
         <v>2025-04-29</v>
@@ -25578,7 +25578,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>1322</v>
+        <v>1856</v>
       </c>
       <c r="B764" t="str">
         <v>2025-04-29</v>
@@ -25610,7 +25610,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>1323</v>
+        <v>1857</v>
       </c>
       <c r="B765" t="str">
         <v>2025-04-30</v>
@@ -25642,7 +25642,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>1324</v>
+        <v>1873</v>
       </c>
       <c r="B766" t="str">
         <v>2025-05-06</v>
@@ -25674,7 +25674,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>1325</v>
+        <v>1874</v>
       </c>
       <c r="B767" t="str">
         <v>2025-05-06</v>
@@ -25706,7 +25706,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>1326</v>
+        <v>1875</v>
       </c>
       <c r="B768" t="str">
         <v>2025-05-07</v>
@@ -25738,7 +25738,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>1327</v>
+        <v>1876</v>
       </c>
       <c r="B769" t="str">
         <v>2025-05-08</v>
@@ -25770,7 +25770,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>1328</v>
+        <v>1877</v>
       </c>
       <c r="B770" t="str">
         <v>2025-05-12</v>
@@ -25802,7 +25802,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>1329</v>
+        <v>1878</v>
       </c>
       <c r="B771" t="str">
         <v>2025-05-12</v>
@@ -25834,7 +25834,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>1330</v>
+        <v>1879</v>
       </c>
       <c r="B772" t="str">
         <v>2025-05-12</v>
@@ -25866,7 +25866,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>1331</v>
+        <v>1880</v>
       </c>
       <c r="B773" t="str">
         <v>2025-05-12</v>
@@ -25898,7 +25898,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>1332</v>
+        <v>1881</v>
       </c>
       <c r="B774" t="str">
         <v>2025-05-12</v>
@@ -25930,7 +25930,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>1333</v>
+        <v>1882</v>
       </c>
       <c r="B775" t="str">
         <v>2025-05-12</v>
@@ -25962,7 +25962,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>1334</v>
+        <v>1883</v>
       </c>
       <c r="B776" t="str">
         <v>2025-05-12</v>
@@ -25994,7 +25994,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>1335</v>
+        <v>1884</v>
       </c>
       <c r="B777" t="str">
         <v>2025-05-13</v>
@@ -26026,7 +26026,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>1336</v>
+        <v>1885</v>
       </c>
       <c r="B778" t="str">
         <v>2025-05-13</v>
@@ -26058,7 +26058,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>1337</v>
+        <v>1886</v>
       </c>
       <c r="B779" t="str">
         <v>2025-05-13</v>
@@ -26090,7 +26090,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>1338</v>
+        <v>1887</v>
       </c>
       <c r="B780" t="str">
         <v>2025-05-13</v>
@@ -26122,7 +26122,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>1339</v>
+        <v>1888</v>
       </c>
       <c r="B781" t="str">
         <v>2025-05-14</v>
@@ -26154,7 +26154,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>1340</v>
+        <v>1889</v>
       </c>
       <c r="B782" t="str">
         <v>2025-05-14</v>
@@ -26186,7 +26186,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>1341</v>
+        <v>1890</v>
       </c>
       <c r="B783" t="str">
         <v>2025-05-14</v>
@@ -26218,7 +26218,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>1342</v>
+        <v>1891</v>
       </c>
       <c r="B784" t="str">
         <v>2025-05-14</v>
@@ -26250,7 +26250,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>1343</v>
+        <v>1892</v>
       </c>
       <c r="B785" t="str">
         <v>2025-05-14</v>
@@ -26282,7 +26282,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>1344</v>
+        <v>1893</v>
       </c>
       <c r="B786" t="str">
         <v>2025-05-14</v>
@@ -26314,7 +26314,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>1345</v>
+        <v>1894</v>
       </c>
       <c r="B787" t="str">
         <v>2025-05-15</v>
@@ -26346,7 +26346,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>1346</v>
+        <v>1895</v>
       </c>
       <c r="B788" t="str">
         <v>2025-05-15</v>
@@ -26378,7 +26378,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>1347</v>
+        <v>1896</v>
       </c>
       <c r="B789" t="str">
         <v>2025-05-15</v>
@@ -26410,7 +26410,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>1348</v>
+        <v>1897</v>
       </c>
       <c r="B790" t="str">
         <v>2025-05-15</v>
@@ -26442,7 +26442,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>1349</v>
+        <v>1898</v>
       </c>
       <c r="B791" t="str">
         <v>2025-05-15</v>
@@ -26474,7 +26474,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>1350</v>
+        <v>1899</v>
       </c>
       <c r="B792" t="str">
         <v>2025-05-16</v>
@@ -26506,7 +26506,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>1351</v>
+        <v>1900</v>
       </c>
       <c r="B793" t="str">
         <v>2025-05-16</v>
@@ -26538,7 +26538,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>1352</v>
+        <v>1901</v>
       </c>
       <c r="B794" t="str">
         <v>2025-05-16</v>
@@ -26570,7 +26570,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>1353</v>
+        <v>1902</v>
       </c>
       <c r="B795" t="str">
         <v>2025-05-16</v>
@@ -26602,7 +26602,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>1354</v>
+        <v>1903</v>
       </c>
       <c r="B796" t="str">
         <v>2025-05-16</v>
@@ -26634,7 +26634,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>1355</v>
+        <v>1904</v>
       </c>
       <c r="B797" t="str">
         <v>2025-05-16</v>
@@ -26666,7 +26666,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>1356</v>
+        <v>1905</v>
       </c>
       <c r="B798" t="str">
         <v>2025-05-16</v>
@@ -26698,7 +26698,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>1357</v>
+        <v>1906</v>
       </c>
       <c r="B799" t="str">
         <v>2025-05-16</v>
@@ -26730,7 +26730,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>1358</v>
+        <v>1907</v>
       </c>
       <c r="B800" t="str">
         <v>2025-05-21</v>
@@ -26762,7 +26762,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>1359</v>
+        <v>1908</v>
       </c>
       <c r="B801" t="str">
         <v>2025-05-21</v>
@@ -26794,7 +26794,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>1360</v>
+        <v>1909</v>
       </c>
       <c r="B802" t="str">
         <v>2025-05-21</v>
@@ -26826,7 +26826,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>1361</v>
+        <v>1910</v>
       </c>
       <c r="B803" t="str">
         <v>2025-05-25</v>
@@ -26858,7 +26858,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>1362</v>
+        <v>1928</v>
       </c>
       <c r="B804" t="str">
         <v>2025-05-31</v>
@@ -26890,7 +26890,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>1363</v>
+        <v>1929</v>
       </c>
       <c r="B805" t="str">
         <v>2025-05-31</v>
@@ -26922,7 +26922,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>1364</v>
+        <v>1930</v>
       </c>
       <c r="B806" t="str">
         <v>2025-05-31</v>
@@ -26954,7 +26954,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>1365</v>
+        <v>1931</v>
       </c>
       <c r="B807" t="str">
         <v>2025-05-31</v>
@@ -26986,7 +26986,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>1366</v>
+        <v>1932</v>
       </c>
       <c r="B808" t="str">
         <v>2025-05-31</v>
@@ -27018,7 +27018,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>1367</v>
+        <v>1933</v>
       </c>
       <c r="B809" t="str">
         <v>2025-06-02</v>
@@ -27050,7 +27050,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>1368</v>
+        <v>1934</v>
       </c>
       <c r="B810" t="str">
         <v>2025-06-03</v>
@@ -27082,7 +27082,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>1369</v>
+        <v>1935</v>
       </c>
       <c r="B811" t="str">
         <v>2025-06-05</v>
@@ -27114,7 +27114,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>1370</v>
+        <v>1936</v>
       </c>
       <c r="B812" t="str">
         <v>2025-06-05</v>
@@ -27146,7 +27146,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>1371</v>
+        <v>1937</v>
       </c>
       <c r="B813" t="str">
         <v>2025-06-05</v>
@@ -27178,7 +27178,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>1372</v>
+        <v>1938</v>
       </c>
       <c r="B814" t="str">
         <v>2025-06-05</v>
@@ -27210,7 +27210,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>1373</v>
+        <v>1939</v>
       </c>
       <c r="B815" t="str">
         <v>2025-06-05</v>
@@ -27242,7 +27242,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>1374</v>
+        <v>1989</v>
       </c>
       <c r="B816" t="str">
         <v>2025-06-11</v>
@@ -27274,7 +27274,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>1375</v>
+        <v>1990</v>
       </c>
       <c r="B817" t="str">
         <v>2025-06-11</v>
@@ -27306,7 +27306,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>1376</v>
+        <v>1991</v>
       </c>
       <c r="B818" t="str">
         <v>2025-06-11</v>
@@ -27338,7 +27338,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>1377</v>
+        <v>1992</v>
       </c>
       <c r="B819" t="str">
         <v>2025-06-11</v>
@@ -27370,7 +27370,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>1378</v>
+        <v>1993</v>
       </c>
       <c r="B820" t="str">
         <v>2025-06-17</v>
@@ -27402,7 +27402,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>1379</v>
+        <v>1994</v>
       </c>
       <c r="B821" t="str">
         <v>2025-06-19</v>
@@ -27434,7 +27434,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>1380</v>
+        <v>1995</v>
       </c>
       <c r="B822" t="str">
         <v>2025-06-19</v>
@@ -27466,7 +27466,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>1381</v>
+        <v>1996</v>
       </c>
       <c r="B823" t="str">
         <v>2025-06-19</v>
@@ -27498,7 +27498,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>1382</v>
+        <v>1997</v>
       </c>
       <c r="B824" t="str">
         <v>2025-06-19</v>
@@ -27530,7 +27530,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>1383</v>
+        <v>1998</v>
       </c>
       <c r="B825" t="str">
         <v>2025-06-19</v>
@@ -27562,7 +27562,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>1384</v>
+        <v>1999</v>
       </c>
       <c r="B826" t="str">
         <v>2025-06-19</v>
@@ -27594,7 +27594,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>1385</v>
+        <v>2000</v>
       </c>
       <c r="B827" t="str">
         <v>2025-06-19</v>
@@ -27626,7 +27626,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>1386</v>
+        <v>2001</v>
       </c>
       <c r="B828" t="str">
         <v>2025-06-19</v>
@@ -27658,7 +27658,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>1387</v>
+        <v>2002</v>
       </c>
       <c r="B829" t="str">
         <v>2025-06-19</v>
@@ -27690,7 +27690,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>1388</v>
+        <v>2003</v>
       </c>
       <c r="B830" t="str">
         <v>2025-06-19</v>
@@ -27722,7 +27722,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>1389</v>
+        <v>2004</v>
       </c>
       <c r="B831" t="str">
         <v>2025-06-19</v>
@@ -27754,7 +27754,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>1390</v>
+        <v>2005</v>
       </c>
       <c r="B832" t="str">
         <v>2025-06-19</v>
@@ -27786,7 +27786,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>1391</v>
+        <v>2006</v>
       </c>
       <c r="B833" t="str">
         <v>2025-06-19</v>
@@ -27818,7 +27818,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>1392</v>
+        <v>2007</v>
       </c>
       <c r="B834" t="str">
         <v>2025-06-19</v>
@@ -27850,7 +27850,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>1393</v>
+        <v>2008</v>
       </c>
       <c r="B835" t="str">
         <v>2025-06-20</v>
@@ -27882,7 +27882,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>1394</v>
+        <v>2009</v>
       </c>
       <c r="B836" t="str">
         <v>2025-06-21</v>
@@ -27914,7 +27914,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>1395</v>
+        <v>2010</v>
       </c>
       <c r="B837" t="str">
         <v>2025-06-21</v>
@@ -27946,7 +27946,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>1396</v>
+        <v>2011</v>
       </c>
       <c r="B838" t="str">
         <v>2025-06-30</v>
@@ -27978,7 +27978,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>1397</v>
+        <v>2012</v>
       </c>
       <c r="B839" t="str">
         <v>2025-06-30</v>
@@ -28010,7 +28010,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>1398</v>
+        <v>2013</v>
       </c>
       <c r="B840" t="str">
         <v>2025-06-30</v>
@@ -28042,7 +28042,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>1399</v>
+        <v>2014</v>
       </c>
       <c r="B841" t="str">
         <v>2025-06-30</v>
@@ -28074,7 +28074,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>1400</v>
+        <v>2015</v>
       </c>
       <c r="B842" t="str">
         <v>2025-06-30</v>
@@ -28106,7 +28106,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>1401</v>
+        <v>2016</v>
       </c>
       <c r="B843" t="str">
         <v>2025-06-30</v>
@@ -28138,7 +28138,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>1402</v>
+        <v>2017</v>
       </c>
       <c r="B844" t="str">
         <v>2025-06-30</v>
@@ -28170,7 +28170,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>1403</v>
+        <v>2018</v>
       </c>
       <c r="B845" t="str">
         <v>2025-06-30</v>
@@ -28202,7 +28202,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>1404</v>
+        <v>2019</v>
       </c>
       <c r="B846" t="str">
         <v>2025-06-30</v>
@@ -28234,7 +28234,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>1405</v>
+        <v>2020</v>
       </c>
       <c r="B847" t="str">
         <v>2025-11-10</v>
@@ -28266,7 +28266,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>1406</v>
+        <v>2021</v>
       </c>
       <c r="B848" t="str">
         <v>2025-11-15</v>
@@ -28298,7 +28298,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>1407</v>
+        <v>2022</v>
       </c>
       <c r="B849" t="str">
         <v>2025-11-16</v>
@@ -28330,7 +28330,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>1408</v>
+        <v>2023</v>
       </c>
       <c r="B850" t="str">
         <v>2025-11-17</v>
@@ -28362,7 +28362,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>1409</v>
+        <v>2024</v>
       </c>
       <c r="B851" t="str">
         <v>2025-11-18</v>
@@ -28394,7 +28394,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>1410</v>
+        <v>2025</v>
       </c>
       <c r="B852" t="str">
         <v>2025-11-18</v>
@@ -28426,7 +28426,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>1411</v>
+        <v>2026</v>
       </c>
       <c r="B853" t="str">
         <v>2025-11-26</v>
@@ -28458,7 +28458,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>1412</v>
+        <v>2027</v>
       </c>
       <c r="B854" t="str">
         <v>2025-11-26</v>
@@ -28490,7 +28490,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>1413</v>
+        <v>2028</v>
       </c>
       <c r="B855" t="str">
         <v>2025-11-26</v>
@@ -28522,7 +28522,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>1414</v>
+        <v>2029</v>
       </c>
       <c r="B856" t="str">
         <v>2025-11-26</v>
@@ -28554,7 +28554,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>1415</v>
+        <v>2030</v>
       </c>
       <c r="B857" t="str">
         <v>2025-11-26</v>
@@ -28586,7 +28586,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>1416</v>
+        <v>2031</v>
       </c>
       <c r="B858" t="str">
         <v>2025-11-26</v>
@@ -28618,7 +28618,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>1417</v>
+        <v>2032</v>
       </c>
       <c r="B859" t="str">
         <v>2025-11-26</v>
@@ -28650,7 +28650,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>1418</v>
+        <v>2033</v>
       </c>
       <c r="B860" t="str">
         <v>2025-11-26</v>
@@ -28682,7 +28682,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>1419</v>
+        <v>2034</v>
       </c>
       <c r="B861" t="str">
         <v>2025-11-26</v>
@@ -28714,7 +28714,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>1420</v>
+        <v>2035</v>
       </c>
       <c r="B862" t="str">
         <v>2025-11-26</v>
@@ -28746,7 +28746,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>1421</v>
+        <v>2036</v>
       </c>
       <c r="B863" t="str">
         <v>2025-11-26</v>
@@ -28778,7 +28778,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>1422</v>
+        <v>2037</v>
       </c>
       <c r="B864" t="str">
         <v>2025-11-26</v>
@@ -28810,7 +28810,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>1423</v>
+        <v>2038</v>
       </c>
       <c r="B865" t="str">
         <v>2025-11-26</v>
@@ -28842,7 +28842,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>1424</v>
+        <v>2039</v>
       </c>
       <c r="B866" t="str">
         <v>2025-11-26</v>
@@ -28874,7 +28874,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>1425</v>
+        <v>2040</v>
       </c>
       <c r="B867" t="str">
         <v>2025-11-26</v>
@@ -28906,7 +28906,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>1426</v>
+        <v>2041</v>
       </c>
       <c r="B868" t="str">
         <v>2025-11-27</v>
@@ -28938,7 +28938,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>1427</v>
+        <v>2042</v>
       </c>
       <c r="B869" t="str">
         <v>2025-11-27</v>
@@ -28970,7 +28970,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>1428</v>
+        <v>2043</v>
       </c>
       <c r="B870" t="str">
         <v>2025-11-27</v>
@@ -29002,7 +29002,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>1429</v>
+        <v>2044</v>
       </c>
       <c r="B871" t="str">
         <v>2025-11-27</v>
@@ -29034,7 +29034,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>1430</v>
+        <v>2045</v>
       </c>
       <c r="B872" t="str">
         <v>2025-11-27</v>
@@ -29066,7 +29066,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>1431</v>
+        <v>2046</v>
       </c>
       <c r="B873" t="str">
         <v>2025-11-27</v>
@@ -29098,7 +29098,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>1432</v>
+        <v>2047</v>
       </c>
       <c r="B874" t="str">
         <v>2025-11-27</v>
@@ -29130,7 +29130,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>1433</v>
+        <v>2048</v>
       </c>
       <c r="B875" t="str">
         <v>2025-11-27</v>
@@ -29162,7 +29162,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>1434</v>
+        <v>2049</v>
       </c>
       <c r="B876" t="str">
         <v>2025-11-27</v>
@@ -29194,7 +29194,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>1435</v>
+        <v>2050</v>
       </c>
       <c r="B877" t="str">
         <v>2025-11-27</v>
@@ -29226,7 +29226,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>1436</v>
+        <v>2051</v>
       </c>
       <c r="B878" t="str">
         <v>2025-11-27</v>
@@ -29258,7 +29258,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>1437</v>
+        <v>2052</v>
       </c>
       <c r="B879" t="str">
         <v>2025-11-27</v>
@@ -29290,7 +29290,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>1438</v>
+        <v>2053</v>
       </c>
       <c r="B880" t="str">
         <v>2025-11-27</v>
@@ -29322,7 +29322,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>1439</v>
+        <v>2054</v>
       </c>
       <c r="B881" t="str">
         <v>2025-11-27</v>
@@ -29354,7 +29354,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>1440</v>
+        <v>2055</v>
       </c>
       <c r="B882" t="str">
         <v>2025-11-27</v>
@@ -29386,7 +29386,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>1441</v>
+        <v>2056</v>
       </c>
       <c r="B883" t="str">
         <v>2025-11-28</v>
@@ -29418,7 +29418,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>1442</v>
+        <v>2057</v>
       </c>
       <c r="B884" t="str">
         <v>2025-11-28</v>
@@ -29450,7 +29450,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>1443</v>
+        <v>2058</v>
       </c>
       <c r="B885" t="str">
         <v>2025-11-28</v>
@@ -29482,7 +29482,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>1444</v>
+        <v>2059</v>
       </c>
       <c r="B886" t="str">
         <v>2025-11-28</v>
@@ -29514,7 +29514,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>1445</v>
+        <v>2060</v>
       </c>
       <c r="B887" t="str">
         <v>2025-11-28</v>
@@ -29546,7 +29546,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>1446</v>
+        <v>2061</v>
       </c>
       <c r="B888" t="str">
         <v>2025-11-28</v>
@@ -29578,7 +29578,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>1447</v>
+        <v>2062</v>
       </c>
       <c r="B889" t="str">
         <v>2025-11-28</v>
@@ -29610,7 +29610,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>1448</v>
+        <v>2063</v>
       </c>
       <c r="B890" t="str">
         <v>2025-11-28</v>
@@ -29642,7 +29642,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>1449</v>
+        <v>2064</v>
       </c>
       <c r="B891" t="str">
         <v>2025-11-28</v>
@@ -29674,7 +29674,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>1450</v>
+        <v>2065</v>
       </c>
       <c r="B892" t="str">
         <v>2025-11-28</v>
@@ -29706,7 +29706,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>1451</v>
+        <v>2066</v>
       </c>
       <c r="B893" t="str">
         <v>2025-11-28</v>
@@ -29738,7 +29738,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>1452</v>
+        <v>2067</v>
       </c>
       <c r="B894" t="str">
         <v>2025-11-28</v>
@@ -29770,7 +29770,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>1453</v>
+        <v>2068</v>
       </c>
       <c r="B895" t="str">
         <v>2025-11-28</v>
@@ -29802,7 +29802,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>1454</v>
+        <v>2069</v>
       </c>
       <c r="B896" t="str">
         <v>2025-11-28</v>
@@ -29834,7 +29834,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>1455</v>
+        <v>2070</v>
       </c>
       <c r="B897" t="str">
         <v>2025-11-28</v>
@@ -29866,7 +29866,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>1456</v>
+        <v>2071</v>
       </c>
       <c r="B898" t="str">
         <v>2025-11-28</v>
@@ -29898,7 +29898,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>1457</v>
+        <v>2072</v>
       </c>
       <c r="B899" t="str">
         <v>2025-11-29</v>
@@ -29930,7 +29930,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>1458</v>
+        <v>2073</v>
       </c>
       <c r="B900" t="str">
         <v>2025-11-29</v>
@@ -29962,7 +29962,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>1459</v>
+        <v>2074</v>
       </c>
       <c r="B901" t="str">
         <v>2025-11-29</v>
@@ -29994,7 +29994,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>1460</v>
+        <v>2075</v>
       </c>
       <c r="B902" t="str">
         <v>2025-11-29</v>
@@ -30026,7 +30026,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>1461</v>
+        <v>2076</v>
       </c>
       <c r="B903" t="str">
         <v>2025-11-29</v>
@@ -30058,7 +30058,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>1462</v>
+        <v>2077</v>
       </c>
       <c r="B904" t="str">
         <v>2025-11-29</v>
@@ -30090,7 +30090,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>1463</v>
+        <v>2078</v>
       </c>
       <c r="B905" t="str">
         <v>2025-11-29</v>
@@ -30122,7 +30122,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>1464</v>
+        <v>2079</v>
       </c>
       <c r="B906" t="str">
         <v>2025-11-29</v>
@@ -30154,7 +30154,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>1465</v>
+        <v>2080</v>
       </c>
       <c r="B907" t="str">
         <v>2025-11-29</v>
@@ -30186,7 +30186,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>1466</v>
+        <v>2081</v>
       </c>
       <c r="B908" t="str">
         <v>2025-11-29</v>
@@ -30218,7 +30218,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>1467</v>
+        <v>2082</v>
       </c>
       <c r="B909" t="str">
         <v>2025-11-29</v>
@@ -30250,7 +30250,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>1468</v>
+        <v>2083</v>
       </c>
       <c r="B910" t="str">
         <v>2025-11-29</v>
@@ -30282,7 +30282,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>1469</v>
+        <v>2084</v>
       </c>
       <c r="B911" t="str">
         <v>2025-11-29</v>
@@ -30314,7 +30314,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>1470</v>
+        <v>2085</v>
       </c>
       <c r="B912" t="str">
         <v>2025-11-29</v>
@@ -30346,7 +30346,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>1471</v>
+        <v>2086</v>
       </c>
       <c r="B913" t="str">
         <v>2025-11-29</v>
@@ -30378,7 +30378,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>1472</v>
+        <v>2087</v>
       </c>
       <c r="B914" t="str">
         <v>2025-11-29</v>
@@ -30410,7 +30410,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>1473</v>
+        <v>2088</v>
       </c>
       <c r="B915" t="str">
         <v>2025-11-30</v>
@@ -30442,7 +30442,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>1474</v>
+        <v>2089</v>
       </c>
       <c r="B916" t="str">
         <v>2025-11-30</v>
@@ -30474,7 +30474,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>1475</v>
+        <v>2090</v>
       </c>
       <c r="B917" t="str">
         <v>2025-11-30</v>
@@ -30506,7 +30506,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>1476</v>
+        <v>2091</v>
       </c>
       <c r="B918" t="str">
         <v>2025-11-30</v>
@@ -30538,7 +30538,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>1477</v>
+        <v>2092</v>
       </c>
       <c r="B919" t="str">
         <v>2025-11-30</v>
@@ -30570,7 +30570,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>1478</v>
+        <v>2093</v>
       </c>
       <c r="B920" t="str">
         <v>2025-11-30</v>
@@ -30602,7 +30602,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>1479</v>
+        <v>2094</v>
       </c>
       <c r="B921" t="str">
         <v>2025-11-30</v>
@@ -30634,7 +30634,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>1480</v>
+        <v>2095</v>
       </c>
       <c r="B922" t="str">
         <v>2025-11-30</v>
@@ -30666,7 +30666,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>1481</v>
+        <v>2096</v>
       </c>
       <c r="B923" t="str">
         <v>2025-11-30</v>
@@ -30698,7 +30698,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>1482</v>
+        <v>2097</v>
       </c>
       <c r="B924" t="str">
         <v>2025-11-30</v>
@@ -30730,7 +30730,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>1483</v>
+        <v>2098</v>
       </c>
       <c r="B925" t="str">
         <v>2025-11-30</v>
@@ -30762,7 +30762,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>1484</v>
+        <v>2099</v>
       </c>
       <c r="B926" t="str">
         <v>2025-11-30</v>
@@ -30794,7 +30794,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>1485</v>
+        <v>2100</v>
       </c>
       <c r="B927" t="str">
         <v>2025-11-30</v>
@@ -30826,7 +30826,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>1486</v>
+        <v>2101</v>
       </c>
       <c r="B928" t="str">
         <v>2025-11-30</v>
@@ -30858,7 +30858,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>1487</v>
+        <v>2102</v>
       </c>
       <c r="B929" t="str">
         <v>2025-11-30</v>

--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -468,7 +468,7 @@
         <v>Gitai.xlsx</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-31T13:53:14.710Z</v>
+        <v>2026-07-31T14:05:49.559Z</v>
       </c>
       <c r="E2">
         <v>928</v>
@@ -477,10 +477,10 @@
         <v>5008700</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1053910</v>
       </c>
       <c r="I2">
         <v>60</v>
@@ -30897,7 +30897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -30922,9 +30922,2585 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>43</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2022-03-13</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D2" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E2" t="str">
+        <v>1050</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>73</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2022-04-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D3" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E3" t="str">
+        <v>4680</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>शोरूम | p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>74</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2022-04-23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D4" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2829</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>105</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2022-05-15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D5" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E5" t="str">
+        <v>26304</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>119</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2022-05-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D6" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E6" t="str">
+        <v>1048</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>135</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2022-06-18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D7" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E7" t="str">
+        <v>8770</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2023-02-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D8" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E8" t="str">
+        <v>650</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>195</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2023-04-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D9" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E9" t="str">
+        <v>3440</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>199</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2023-05-15</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D10" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E10" t="str">
+        <v>4975</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>200</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2023-05-30</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D11" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E11" t="str">
+        <v>7975</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>201</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2023-06-18</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D12" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E12" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>202</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2023-06-21</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D13" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E13" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>209</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2023-10-03</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D14" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E14" t="str">
+        <v>4500</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>212</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2023-10-17</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D15" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E15" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>213</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2023-10-25</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D16" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E16" t="str">
+        <v>4950</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>214</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2023-10-26</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D17" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E17" t="str">
+        <v>4950</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>215</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2023-10-29</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D18" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E18" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>216</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2023-10-30</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D19" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1048</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>217</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2023-11-02</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D20" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E20" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>218</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2023-11-03</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D21" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E21" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>219</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2023-11-11</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D22" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E22" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>221</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2023-11-25</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D23" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E23" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>223</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2023-11-28</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D24" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E24" t="str">
+        <v>4950</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>233</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2023-12-10</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D25" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E25" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>245</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2023-12-19</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D26" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E26" t="str">
+        <v>13036</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>246</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2023-12-20</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D27" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E27" t="str">
+        <v>3259</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>247</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2023-12-21</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D28" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2900</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>248</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2023-12-22</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D29" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E29" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>249</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2023-12-22</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D30" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E30" t="str">
+        <v>3200</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>263</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2024-01-12</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D31" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E31" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>264</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D32" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E32" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>265</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2024-01-16</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D33" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E33" t="str">
+        <v>3200</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>293</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2024-02-12</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D34" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E34" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>301</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2024-02-18</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D35" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E35" t="str">
+        <v>3460</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>303</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2024-02-24</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D36" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E36" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>306</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2024-02-26</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D37" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E37" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>307</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2024-02-27</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D38" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2400</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>310</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2024-02-29</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D39" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E39" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>312</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D40" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E40" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>320</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D41" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E41" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>322</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2024-03-12</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D42" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E42" t="str">
+        <v>5323</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>323</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D43" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E43" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>324</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D44" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E44" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>333</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2024-03-17</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D45" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E45" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>334</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2024-03-18</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D46" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E46" t="str">
+        <v>14500</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>335</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2024-03-23</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D47" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E47" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>336</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2024-03-24</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D48" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E48" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>337</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2024-03-25</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D49" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E49" t="str">
+        <v>15300</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>338</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2024-03-28</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D50" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E50" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>339</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2024-03-28</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D51" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E51" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>341</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2024-04-01</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D52" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E52" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>345</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2024-04-02</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D53" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E53" t="str">
+        <v>17000</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>346</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2024-04-02</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D54" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E54" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>348</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2024-04-04</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D55" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E55" t="str">
+        <v>19700</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>corrected from struck 19/5/24 | p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>352</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2024-04-06</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D56" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E56" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>358</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2024-04-09</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D57" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E57" t="str">
+        <v>37600</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>बकीट आणली | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>361</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2024-04-10</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D58" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E58" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>363</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2024-04-12</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D59" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E59" t="str">
+        <v>19700</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>364</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2024-04-13</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D60" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E60" t="str">
+        <v>15000</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>366</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2024-04-17</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D61" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E61" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>368</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2024-04-19</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D62" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E62" t="str">
+        <v>17300</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>378</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2024-04-24</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D63" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E63" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>392</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2024-05-04</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D64" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E64" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>397</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2024-05-08</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D65" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E65" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>411</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2024-05-14</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D66" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E66" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>426</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2024-05-20</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D67" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E67" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>454</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2024-05-31</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D68" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E68" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>465</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2024-06-02</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D69" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E69" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>468</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2024-06-04</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D70" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E70" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>492</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2024-06-24</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D71" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E71" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>496</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2024-09-13</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D72" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E72" t="str">
+        <v>6200</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>बॅटरी मशीन | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>504</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2024-10-08</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D73" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E73" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>505</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2024-10-10</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D74" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E74" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>506</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2024-10-10</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D75" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E75" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>507</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2024-10-11</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D76" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E76" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>date corrected (struck first digit of day) | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>508</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2024-10-23</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D77" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E77" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>509</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2024-10-23</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D78" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E78" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>510</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2024-11-11</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D79" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E79" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>513</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2024-11-27</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D80" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2000</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>514</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2024-11-30</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D81" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E81" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>515</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2024-12-01</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D82" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E82" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>527</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2024-12-29</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D83" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E83" t="str">
+        <v>3459</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>538</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-02-21</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D84" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2930</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>539</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-02-22</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D85" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E85" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>540</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D86" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E86" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>546</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025-03-10</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D87" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E87" t="str">
+        <v>5400</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>580</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025-04-01</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D88" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E88" t="str">
+        <v>7000</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>date corrected (month digit overwritten) | p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>602</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025-04-24</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D89" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E89" t="str">
+        <v>3600</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>603</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025-04-26</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D90" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E90" t="str">
+        <v>3400</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>607</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025-04-29</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D91" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E91" t="str">
+        <v>720</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>612</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2025-05-01</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D92" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E92" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>615</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D93" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E93" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>616</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D94" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E94" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>617</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D95" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E95" t="str">
+        <v>7200</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>620</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025-05-08</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D96" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E96" t="str">
+        <v>3050</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>621</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-05-09</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D97" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E97" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>date corrected (day 4 struck, written as 9) | p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>622</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-05-10</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D98" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E98" t="str">
+        <v>5400</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>625</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-05-13</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D99" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E99" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>655</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-07-04</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D100" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E100" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>656</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D101" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E101" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>657</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-09-28</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D102" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E102" t="str">
+        <v>3600</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>658</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-11-15</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D103" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E103" t="str">
+        <v>10419</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>659</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-11-17</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D104" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E104" t="str">
+        <v>3550</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>660</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D105" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E105" t="str">
+        <v>40000</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>661</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D106" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E106" t="str">
+        <v>60000</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>662</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D107" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E107" t="str">
+        <v>34700</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>663</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D108" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E108" t="str">
+        <v>30000</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>664</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D109" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E109" t="str">
+        <v>3559</v>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>665</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D110" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E110" t="str">
+        <v>5426</v>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>666</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D111" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E111" t="str">
+        <v>8000</v>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>667</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D112" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E112" t="str">
+        <v>90000</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>668</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D113" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E113" t="str">
+        <v>12000</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G113"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -468,7 +468,7 @@
         <v>Gitai.xlsx</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-31T14:05:49.559Z</v>
+        <v>2026-07-31T17:48:11.991Z</v>
       </c>
       <c r="E2">
         <v>928</v>
@@ -30924,7 +30924,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="B2" t="str">
         <v>2022-03-13</v>
@@ -30947,7 +30947,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="B3" t="str">
         <v>2022-04-23</v>
@@ -30970,7 +30970,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="B4" t="str">
         <v>2022-04-23</v>
@@ -30993,7 +30993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="B5" t="str">
         <v>2022-05-15</v>
@@ -31016,7 +31016,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>119</v>
+        <v>241</v>
       </c>
       <c r="B6" t="str">
         <v>2022-05-28</v>
@@ -31039,7 +31039,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="B7" t="str">
         <v>2022-06-18</v>
@@ -31062,7 +31062,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>181</v>
+        <v>373</v>
       </c>
       <c r="B8" t="str">
         <v>2023-02-26</v>
@@ -31085,7 +31085,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="B9" t="str">
         <v>2023-04-12</v>
@@ -31108,7 +31108,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>199</v>
+        <v>419</v>
       </c>
       <c r="B10" t="str">
         <v>2023-05-15</v>
@@ -31131,7 +31131,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="B11" t="str">
         <v>2023-05-30</v>
@@ -31154,7 +31154,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>201</v>
+        <v>421</v>
       </c>
       <c r="B12" t="str">
         <v>2023-06-18</v>
@@ -31177,7 +31177,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>202</v>
+        <v>422</v>
       </c>
       <c r="B13" t="str">
         <v>2023-06-21</v>
@@ -31200,7 +31200,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>209</v>
+        <v>429</v>
       </c>
       <c r="B14" t="str">
         <v>2023-10-03</v>
@@ -31223,7 +31223,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>212</v>
+        <v>432</v>
       </c>
       <c r="B15" t="str">
         <v>2023-10-17</v>
@@ -31246,7 +31246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>213</v>
+        <v>433</v>
       </c>
       <c r="B16" t="str">
         <v>2023-10-25</v>
@@ -31269,7 +31269,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>214</v>
+        <v>434</v>
       </c>
       <c r="B17" t="str">
         <v>2023-10-26</v>
@@ -31292,7 +31292,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>215</v>
+        <v>435</v>
       </c>
       <c r="B18" t="str">
         <v>2023-10-29</v>
@@ -31315,7 +31315,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>216</v>
+        <v>436</v>
       </c>
       <c r="B19" t="str">
         <v>2023-10-30</v>
@@ -31338,7 +31338,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>217</v>
+        <v>438</v>
       </c>
       <c r="B20" t="str">
         <v>2023-11-02</v>
@@ -31361,7 +31361,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="B21" t="str">
         <v>2023-11-03</v>
@@ -31384,7 +31384,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>219</v>
+        <v>440</v>
       </c>
       <c r="B22" t="str">
         <v>2023-11-11</v>
@@ -31407,7 +31407,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>221</v>
+        <v>442</v>
       </c>
       <c r="B23" t="str">
         <v>2023-11-25</v>
@@ -31430,7 +31430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>223</v>
+        <v>444</v>
       </c>
       <c r="B24" t="str">
         <v>2023-11-28</v>
@@ -31453,7 +31453,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>233</v>
+        <v>454</v>
       </c>
       <c r="B25" t="str">
         <v>2023-12-10</v>
@@ -31476,7 +31476,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>245</v>
+        <v>466</v>
       </c>
       <c r="B26" t="str">
         <v>2023-12-19</v>
@@ -31499,7 +31499,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>246</v>
+        <v>467</v>
       </c>
       <c r="B27" t="str">
         <v>2023-12-20</v>
@@ -31522,7 +31522,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>247</v>
+        <v>468</v>
       </c>
       <c r="B28" t="str">
         <v>2023-12-21</v>
@@ -31545,7 +31545,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>248</v>
+        <v>469</v>
       </c>
       <c r="B29" t="str">
         <v>2023-12-22</v>
@@ -31568,7 +31568,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>249</v>
+        <v>470</v>
       </c>
       <c r="B30" t="str">
         <v>2023-12-22</v>
@@ -31591,7 +31591,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>263</v>
+        <v>484</v>
       </c>
       <c r="B31" t="str">
         <v>2024-01-12</v>
@@ -31614,7 +31614,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>264</v>
+        <v>485</v>
       </c>
       <c r="B32" t="str">
         <v>2024-01-15</v>
@@ -31637,7 +31637,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="B33" t="str">
         <v>2024-01-16</v>
@@ -31660,7 +31660,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>293</v>
+        <v>514</v>
       </c>
       <c r="B34" t="str">
         <v>2024-02-12</v>
@@ -31683,7 +31683,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>301</v>
+        <v>522</v>
       </c>
       <c r="B35" t="str">
         <v>2024-02-18</v>
@@ -31706,7 +31706,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>303</v>
+        <v>524</v>
       </c>
       <c r="B36" t="str">
         <v>2024-02-24</v>
@@ -31729,7 +31729,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>306</v>
+        <v>527</v>
       </c>
       <c r="B37" t="str">
         <v>2024-02-26</v>
@@ -31752,7 +31752,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>307</v>
+        <v>528</v>
       </c>
       <c r="B38" t="str">
         <v>2024-02-27</v>
@@ -31775,7 +31775,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>310</v>
+        <v>531</v>
       </c>
       <c r="B39" t="str">
         <v>2024-02-29</v>
@@ -31798,7 +31798,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>312</v>
+        <v>533</v>
       </c>
       <c r="B40" t="str">
         <v>2024-03-01</v>
@@ -31821,7 +31821,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>320</v>
+        <v>541</v>
       </c>
       <c r="B41" t="str">
         <v>2024-03-06</v>
@@ -31844,7 +31844,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>322</v>
+        <v>543</v>
       </c>
       <c r="B42" t="str">
         <v>2024-03-12</v>
@@ -31867,7 +31867,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>323</v>
+        <v>544</v>
       </c>
       <c r="B43" t="str">
         <v>2024-03-13</v>
@@ -31890,7 +31890,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>324</v>
+        <v>545</v>
       </c>
       <c r="B44" t="str">
         <v>2024-03-13</v>
@@ -31913,7 +31913,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>333</v>
+        <v>554</v>
       </c>
       <c r="B45" t="str">
         <v>2024-03-17</v>
@@ -31936,7 +31936,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>334</v>
+        <v>555</v>
       </c>
       <c r="B46" t="str">
         <v>2024-03-18</v>
@@ -31959,7 +31959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>335</v>
+        <v>556</v>
       </c>
       <c r="B47" t="str">
         <v>2024-03-23</v>
@@ -31982,7 +31982,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>336</v>
+        <v>557</v>
       </c>
       <c r="B48" t="str">
         <v>2024-03-24</v>
@@ -32005,7 +32005,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>337</v>
+        <v>558</v>
       </c>
       <c r="B49" t="str">
         <v>2024-03-25</v>
@@ -32028,7 +32028,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>338</v>
+        <v>559</v>
       </c>
       <c r="B50" t="str">
         <v>2024-03-28</v>
@@ -32051,7 +32051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>339</v>
+        <v>560</v>
       </c>
       <c r="B51" t="str">
         <v>2024-03-28</v>
@@ -32074,7 +32074,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>341</v>
+        <v>562</v>
       </c>
       <c r="B52" t="str">
         <v>2024-04-01</v>
@@ -32097,7 +32097,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>345</v>
+        <v>566</v>
       </c>
       <c r="B53" t="str">
         <v>2024-04-02</v>
@@ -32120,7 +32120,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>346</v>
+        <v>567</v>
       </c>
       <c r="B54" t="str">
         <v>2024-04-02</v>
@@ -32143,7 +32143,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>348</v>
+        <v>569</v>
       </c>
       <c r="B55" t="str">
         <v>2024-04-04</v>
@@ -32166,7 +32166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>352</v>
+        <v>573</v>
       </c>
       <c r="B56" t="str">
         <v>2024-04-06</v>
@@ -32189,7 +32189,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>358</v>
+        <v>579</v>
       </c>
       <c r="B57" t="str">
         <v>2024-04-09</v>
@@ -32212,7 +32212,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>361</v>
+        <v>582</v>
       </c>
       <c r="B58" t="str">
         <v>2024-04-10</v>
@@ -32235,7 +32235,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>363</v>
+        <v>584</v>
       </c>
       <c r="B59" t="str">
         <v>2024-04-12</v>
@@ -32258,7 +32258,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>364</v>
+        <v>585</v>
       </c>
       <c r="B60" t="str">
         <v>2024-04-13</v>
@@ -32281,7 +32281,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>366</v>
+        <v>587</v>
       </c>
       <c r="B61" t="str">
         <v>2024-04-17</v>
@@ -32304,7 +32304,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>368</v>
+        <v>589</v>
       </c>
       <c r="B62" t="str">
         <v>2024-04-19</v>
@@ -32327,7 +32327,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>378</v>
+        <v>599</v>
       </c>
       <c r="B63" t="str">
         <v>2024-04-24</v>
@@ -32350,7 +32350,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>392</v>
+        <v>613</v>
       </c>
       <c r="B64" t="str">
         <v>2024-05-04</v>
@@ -32373,7 +32373,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>397</v>
+        <v>618</v>
       </c>
       <c r="B65" t="str">
         <v>2024-05-08</v>
@@ -32396,7 +32396,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>411</v>
+        <v>632</v>
       </c>
       <c r="B66" t="str">
         <v>2024-05-14</v>
@@ -32419,7 +32419,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>426</v>
+        <v>648</v>
       </c>
       <c r="B67" t="str">
         <v>2024-05-20</v>
@@ -32442,7 +32442,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>454</v>
+        <v>676</v>
       </c>
       <c r="B68" t="str">
         <v>2024-05-31</v>
@@ -32465,7 +32465,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>465</v>
+        <v>687</v>
       </c>
       <c r="B69" t="str">
         <v>2024-06-02</v>
@@ -32488,7 +32488,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>468</v>
+        <v>690</v>
       </c>
       <c r="B70" t="str">
         <v>2024-06-04</v>
@@ -32511,7 +32511,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>492</v>
+        <v>721</v>
       </c>
       <c r="B71" t="str">
         <v>2024-06-24</v>
@@ -32534,7 +32534,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>496</v>
+        <v>730</v>
       </c>
       <c r="B72" t="str">
         <v>2024-09-13</v>
@@ -32557,7 +32557,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>504</v>
+        <v>738</v>
       </c>
       <c r="B73" t="str">
         <v>2024-10-08</v>
@@ -32580,7 +32580,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>505</v>
+        <v>739</v>
       </c>
       <c r="B74" t="str">
         <v>2024-10-10</v>
@@ -32603,7 +32603,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>506</v>
+        <v>740</v>
       </c>
       <c r="B75" t="str">
         <v>2024-10-10</v>
@@ -32626,7 +32626,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>507</v>
+        <v>741</v>
       </c>
       <c r="B76" t="str">
         <v>2024-10-11</v>
@@ -32649,7 +32649,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>508</v>
+        <v>742</v>
       </c>
       <c r="B77" t="str">
         <v>2024-10-23</v>
@@ -32672,7 +32672,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>509</v>
+        <v>743</v>
       </c>
       <c r="B78" t="str">
         <v>2024-10-23</v>
@@ -32695,7 +32695,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>510</v>
+        <v>744</v>
       </c>
       <c r="B79" t="str">
         <v>2024-11-11</v>
@@ -32718,7 +32718,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>513</v>
+        <v>747</v>
       </c>
       <c r="B80" t="str">
         <v>2024-11-27</v>
@@ -32741,7 +32741,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>514</v>
+        <v>748</v>
       </c>
       <c r="B81" t="str">
         <v>2024-11-30</v>
@@ -32764,7 +32764,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>515</v>
+        <v>749</v>
       </c>
       <c r="B82" t="str">
         <v>2024-12-01</v>
@@ -32787,7 +32787,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>527</v>
+        <v>761</v>
       </c>
       <c r="B83" t="str">
         <v>2024-12-29</v>
@@ -32810,7 +32810,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>538</v>
+        <v>772</v>
       </c>
       <c r="B84" t="str">
         <v>2025-02-21</v>
@@ -32833,7 +32833,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>539</v>
+        <v>773</v>
       </c>
       <c r="B85" t="str">
         <v>2025-02-22</v>
@@ -32856,7 +32856,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>540</v>
+        <v>774</v>
       </c>
       <c r="B86" t="str">
         <v>2025-03-01</v>
@@ -32879,7 +32879,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>546</v>
+        <v>780</v>
       </c>
       <c r="B87" t="str">
         <v>2025-03-10</v>
@@ -32902,7 +32902,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>580</v>
+        <v>814</v>
       </c>
       <c r="B88" t="str">
         <v>2025-04-01</v>
@@ -32925,7 +32925,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>602</v>
+        <v>836</v>
       </c>
       <c r="B89" t="str">
         <v>2025-04-24</v>
@@ -32948,7 +32948,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>603</v>
+        <v>837</v>
       </c>
       <c r="B90" t="str">
         <v>2025-04-26</v>
@@ -32971,7 +32971,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>607</v>
+        <v>841</v>
       </c>
       <c r="B91" t="str">
         <v>2025-04-29</v>
@@ -32994,7 +32994,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>612</v>
+        <v>846</v>
       </c>
       <c r="B92" t="str">
         <v>2025-05-01</v>
@@ -33017,7 +33017,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>615</v>
+        <v>849</v>
       </c>
       <c r="B93" t="str">
         <v>2025-05-05</v>
@@ -33040,7 +33040,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>616</v>
+        <v>850</v>
       </c>
       <c r="B94" t="str">
         <v>2025-05-05</v>
@@ -33063,7 +33063,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>617</v>
+        <v>851</v>
       </c>
       <c r="B95" t="str">
         <v>2025-05-05</v>
@@ -33086,7 +33086,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>620</v>
+        <v>854</v>
       </c>
       <c r="B96" t="str">
         <v>2025-05-08</v>
@@ -33109,7 +33109,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>621</v>
+        <v>855</v>
       </c>
       <c r="B97" t="str">
         <v>2025-05-09</v>
@@ -33132,7 +33132,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>622</v>
+        <v>856</v>
       </c>
       <c r="B98" t="str">
         <v>2025-05-10</v>
@@ -33155,7 +33155,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>625</v>
+        <v>859</v>
       </c>
       <c r="B99" t="str">
         <v>2025-05-13</v>
@@ -33178,7 +33178,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>655</v>
+        <v>889</v>
       </c>
       <c r="B100" t="str">
         <v>2025-07-04</v>
@@ -33201,7 +33201,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>656</v>
+        <v>890</v>
       </c>
       <c r="B101" t="str">
         <v>2025-09-01</v>
@@ -33224,7 +33224,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>657</v>
+        <v>891</v>
       </c>
       <c r="B102" t="str">
         <v>2025-09-28</v>
@@ -33247,7 +33247,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>658</v>
+        <v>892</v>
       </c>
       <c r="B103" t="str">
         <v>2025-11-15</v>
@@ -33270,7 +33270,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>659</v>
+        <v>893</v>
       </c>
       <c r="B104" t="str">
         <v>2025-11-17</v>
@@ -33293,7 +33293,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>660</v>
+        <v>894</v>
       </c>
       <c r="B105" t="str">
         <v>2026-02-16</v>
@@ -33316,7 +33316,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>661</v>
+        <v>895</v>
       </c>
       <c r="B106" t="str">
         <v>2026-02-16</v>
@@ -33339,7 +33339,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>662</v>
+        <v>896</v>
       </c>
       <c r="B107" t="str">
         <v>2026-03-25</v>
@@ -33362,7 +33362,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>663</v>
+        <v>897</v>
       </c>
       <c r="B108" t="str">
         <v>2026-05-03</v>
@@ -33385,7 +33385,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>664</v>
+        <v>898</v>
       </c>
       <c r="B109" t="str">
         <v>2026-05-06</v>
@@ -33408,7 +33408,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>665</v>
+        <v>899</v>
       </c>
       <c r="B110" t="str">
         <v>2026-05-06</v>
@@ -33431,7 +33431,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>666</v>
+        <v>900</v>
       </c>
       <c r="B111" t="str">
         <v>2026-05-23</v>
@@ -33454,7 +33454,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>667</v>
+        <v>901</v>
       </c>
       <c r="B112" t="str">
         <v>2026-06-01</v>
@@ -33477,7 +33477,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>668</v>
+        <v>902</v>
       </c>
       <c r="B113" t="str">
         <v>2026-06-06</v>

--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -468,7 +468,7 @@
         <v>Gitai.xlsx</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-31T17:48:11.991Z</v>
+        <v>2026-07-31T18:48:06.348Z</v>
       </c>
       <c r="E2">
         <v>928</v>
@@ -477,10 +477,10 @@
         <v>5008700</v>
       </c>
       <c r="G2">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="H2">
-        <v>1053910</v>
+        <v>2280962</v>
       </c>
       <c r="I2">
         <v>60</v>
@@ -30897,7 +30897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G234"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -31062,10 +31062,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="B8" t="str">
-        <v>2023-02-26</v>
+        <v>2023-01-17</v>
       </c>
       <c r="C8" t="str">
         <v>Diesel</v>
@@ -31074,136 +31074,136 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E8" t="str">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>398</v>
+        <v>339</v>
       </c>
       <c r="B9" t="str">
-        <v>2023-04-12</v>
+        <v>2023-01-19</v>
       </c>
       <c r="C9" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D9" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E9" t="str">
-        <v>3440</v>
+        <v>3500</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>419</v>
+        <v>341</v>
       </c>
       <c r="B10" t="str">
-        <v>2023-05-15</v>
+        <v>2023-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D10" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E10" t="str">
-        <v>4975</v>
+        <v>4500</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>420</v>
+        <v>343</v>
       </c>
       <c r="B11" t="str">
-        <v>2023-05-30</v>
+        <v>2023-01-21</v>
       </c>
       <c r="C11" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D11" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E11" t="str">
-        <v>7975</v>
+        <v>4500</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>421</v>
+        <v>345</v>
       </c>
       <c r="B12" t="str">
-        <v>2023-06-18</v>
+        <v>2023-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D12" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E12" t="str">
-        <v>20000</v>
+        <v>4500</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>422</v>
+        <v>347</v>
       </c>
       <c r="B13" t="str">
-        <v>2023-06-21</v>
+        <v>2023-01-24</v>
       </c>
       <c r="C13" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D13" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E13" t="str">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>written 24-01-23 | p1 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="B14" t="str">
-        <v>2023-10-03</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C14" t="str">
         <v>Diesel</v>
@@ -31212,159 +31212,159 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E14" t="str">
-        <v>4500</v>
+        <v>3700</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>432</v>
+        <v>350</v>
       </c>
       <c r="B15" t="str">
-        <v>2023-10-17</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C15" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D15" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E15" t="str">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर खर्च | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>433</v>
+        <v>351</v>
       </c>
       <c r="B16" t="str">
-        <v>2023-10-25</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C16" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D16" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E16" t="str">
-        <v>4950</v>
+        <v>1200</v>
       </c>
       <c r="F16" t="str">
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>ऑईल फिल्टर | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>434</v>
+        <v>352</v>
       </c>
       <c r="B17" t="str">
-        <v>2023-10-26</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C17" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D17" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E17" t="str">
-        <v>4950</v>
+        <v>31000</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>मेन हब काम | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>435</v>
+        <v>353</v>
       </c>
       <c r="B18" t="str">
-        <v>2023-10-29</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C18" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D18" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E18" t="str">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F18" t="str">
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>मजुरी | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>436</v>
+        <v>354</v>
       </c>
       <c r="B19" t="str">
-        <v>2023-10-30</v>
+        <v>2023-01-25</v>
       </c>
       <c r="C19" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D19" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E19" t="str">
-        <v>1048</v>
+        <v>2500</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>एअर फिल्टर | p2 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="B20" t="str">
-        <v>2023-11-02</v>
+        <v>2023-02-09</v>
       </c>
       <c r="C20" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D20" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E20" t="str">
-        <v>4900</v>
+        <v>3500</v>
       </c>
       <c r="F20" t="str">
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>circled 0025; amount reconciled to page total 28950 | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>439</v>
+        <v>368</v>
       </c>
       <c r="B21" t="str">
-        <v>2023-11-03</v>
+        <v>2023-02-10</v>
       </c>
       <c r="C21" t="str">
         <v>Diesel</v>
@@ -31373,21 +31373,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E21" t="str">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>50 लीटर | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="B22" t="str">
-        <v>2023-11-11</v>
+        <v>2023-02-11</v>
       </c>
       <c r="C22" t="str">
         <v>Diesel</v>
@@ -31396,21 +31396,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E22" t="str">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F22" t="str">
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>50 लीटर | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="B23" t="str">
-        <v>2023-11-25</v>
+        <v>2023-02-14</v>
       </c>
       <c r="C23" t="str">
         <v>Diesel</v>
@@ -31419,182 +31419,182 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E23" t="str">
-        <v>4900</v>
+        <v>7000</v>
       </c>
       <c r="F23" t="str">
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>70 ली. | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="B24" t="str">
-        <v>2023-11-28</v>
+        <v>2023-02-14</v>
       </c>
       <c r="C24" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D24" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E24" t="str">
-        <v>4950</v>
+        <v>2000</v>
       </c>
       <c r="F24" t="str">
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>कारखाना खर्च | date carried | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>454</v>
+        <v>378</v>
       </c>
       <c r="B25" t="str">
-        <v>2023-12-10</v>
+        <v>2023-02-14</v>
       </c>
       <c r="C25" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D25" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E25" t="str">
-        <v>20000</v>
+        <v>700</v>
       </c>
       <c r="F25" t="str">
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>मशीन वाशिंग | date carried | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>466</v>
+        <v>382</v>
       </c>
       <c r="B26" t="str">
-        <v>2023-12-19</v>
+        <v>2023-02-16</v>
       </c>
       <c r="C26" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D26" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E26" t="str">
-        <v>13036</v>
+        <v>5750</v>
       </c>
       <c r="F26" t="str">
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>faint illegible text | p3 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>467</v>
+        <v>387</v>
       </c>
       <c r="B27" t="str">
-        <v>2023-12-20</v>
+        <v>2023-02-20</v>
       </c>
       <c r="C27" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D27" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E27" t="str">
-        <v>3259</v>
+        <v>10000</v>
       </c>
       <c r="F27" t="str">
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>कॅश आसावरीकडे | p4 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>468</v>
+        <v>388</v>
       </c>
       <c r="B28" t="str">
-        <v>2023-12-21</v>
+        <v>2023-02-20</v>
       </c>
       <c r="C28" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D28" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E28" t="str">
-        <v>2900</v>
+        <v>12714</v>
       </c>
       <c r="F28" t="str">
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>सर्व्हीसिंग | date carried | p4 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>469</v>
+        <v>389</v>
       </c>
       <c r="B29" t="str">
-        <v>2023-12-22</v>
+        <v>2023-02-20</v>
       </c>
       <c r="C29" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D29" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E29" t="str">
-        <v>4900</v>
+        <v>1500</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>Decoration | date carried | p4 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>470</v>
+        <v>395</v>
       </c>
       <c r="B30" t="str">
-        <v>2023-12-22</v>
+        <v>2023-02-25</v>
       </c>
       <c r="C30" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D30" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E30" t="str">
-        <v>3200</v>
+        <v>4500</v>
       </c>
       <c r="F30" t="str">
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>written 25-02-23 | p4 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>484</v>
+        <v>396</v>
       </c>
       <c r="B31" t="str">
-        <v>2024-01-12</v>
+        <v>2023-02-26</v>
       </c>
       <c r="C31" t="str">
         <v>Diesel</v>
@@ -31603,67 +31603,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E31" t="str">
-        <v>4900</v>
+        <v>650</v>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>485</v>
+        <v>397</v>
       </c>
       <c r="B32" t="str">
-        <v>2024-01-15</v>
+        <v>2023-03-05</v>
       </c>
       <c r="C32" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D32" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E32" t="str">
-        <v>4900</v>
+        <v>3500</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>पगार | p5 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>486</v>
+        <v>402</v>
       </c>
       <c r="B33" t="str">
-        <v>2024-01-16</v>
+        <v>2023-03-12</v>
       </c>
       <c r="C33" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D33" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E33" t="str">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>पगार | ditto | p5 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>514</v>
+        <v>403</v>
       </c>
       <c r="B34" t="str">
-        <v>2024-02-12</v>
+        <v>2023-03-14</v>
       </c>
       <c r="C34" t="str">
         <v>Diesel</v>
@@ -31672,21 +31672,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E34" t="str">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p6 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>522</v>
+        <v>406</v>
       </c>
       <c r="B35" t="str">
-        <v>2024-02-18</v>
+        <v>2023-03-15</v>
       </c>
       <c r="C35" t="str">
         <v>Diesel</v>
@@ -31695,205 +31695,205 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E35" t="str">
-        <v>3460</v>
+        <v>3500</v>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p6 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>524</v>
+        <v>409</v>
       </c>
       <c r="B36" t="str">
-        <v>2024-02-24</v>
+        <v>2023-03-18</v>
       </c>
       <c r="C36" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D36" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E36" t="str">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>पवन डोलारे पगार | p7 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>527</v>
+        <v>410</v>
       </c>
       <c r="B37" t="str">
-        <v>2024-02-26</v>
+        <v>2023-03-21</v>
       </c>
       <c r="C37" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D37" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E37" t="str">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="F37" t="str">
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>पवन डोलारे पगार | p7 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>528</v>
+        <v>413</v>
       </c>
       <c r="B38" t="str">
-        <v>2024-02-27</v>
+        <v>2023-03-24</v>
       </c>
       <c r="C38" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D38" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E38" t="str">
-        <v>2400</v>
+        <v>3700</v>
       </c>
       <c r="F38" t="str">
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>p3 | imported from Diesel expenses M2.pdf</v>
+        <v>पवन डोलारे पगार | p7 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>531</v>
+        <v>414</v>
       </c>
       <c r="B39" t="str">
-        <v>2024-02-29</v>
+        <v>2023-03-25</v>
       </c>
       <c r="C39" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D39" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E39" t="str">
-        <v>4900</v>
+        <v>3700</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>पवन डोलारे पगार | p7 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>533</v>
+        <v>416</v>
       </c>
       <c r="B40" t="str">
-        <v>2024-03-01</v>
+        <v>2023-03-27</v>
       </c>
       <c r="C40" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D40" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E40" t="str">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="F40" t="str">
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>p8 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>541</v>
+        <v>418</v>
       </c>
       <c r="B41" t="str">
-        <v>2024-03-06</v>
+        <v>2023-03-28</v>
       </c>
       <c r="C41" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D41" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E41" t="str">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>p8 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>543</v>
+        <v>421</v>
       </c>
       <c r="B42" t="str">
-        <v>2024-03-12</v>
+        <v>2023-04-02</v>
       </c>
       <c r="C42" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D42" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E42" t="str">
-        <v>5323</v>
+        <v>4000</v>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>written दि. 2-4. | p8 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>544</v>
+        <v>424</v>
       </c>
       <c r="B43" t="str">
-        <v>2024-03-13</v>
+        <v>2023-04-05</v>
       </c>
       <c r="C43" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D43" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E43" t="str">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="F43" t="str">
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>p8 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>545</v>
+        <v>427</v>
       </c>
       <c r="B44" t="str">
-        <v>2024-03-13</v>
+        <v>2023-04-07</v>
       </c>
       <c r="C44" t="str">
         <v>Diesel</v>
@@ -31902,21 +31902,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E44" t="str">
-        <v>4900</v>
+        <v>3600</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | sole clear entry; page mostly bleed-through | p4 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>554</v>
+        <v>434</v>
       </c>
       <c r="B45" t="str">
-        <v>2024-03-17</v>
+        <v>2023-04-12</v>
       </c>
       <c r="C45" t="str">
         <v>Diesel</v>
@@ -31925,21 +31925,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E45" t="str">
-        <v>4900</v>
+        <v>3440</v>
       </c>
       <c r="F45" t="str">
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>555</v>
+        <v>436</v>
       </c>
       <c r="B46" t="str">
-        <v>2024-03-18</v>
+        <v>2023-04-13</v>
       </c>
       <c r="C46" t="str">
         <v>Diesel</v>
@@ -31948,21 +31948,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E46" t="str">
-        <v>14500</v>
+        <v>5000</v>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p11 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>556</v>
+        <v>440</v>
       </c>
       <c r="B47" t="str">
-        <v>2024-03-23</v>
+        <v>2023-04-17</v>
       </c>
       <c r="C47" t="str">
         <v>Diesel</v>
@@ -31971,21 +31971,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E47" t="str">
-        <v>4900</v>
+        <v>3800</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p9 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>557</v>
+        <v>442</v>
       </c>
       <c r="B48" t="str">
-        <v>2024-03-24</v>
+        <v>2023-04-18</v>
       </c>
       <c r="C48" t="str">
         <v>Diesel</v>
@@ -31994,21 +31994,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E48" t="str">
-        <v>5000</v>
+        <v>20100</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p9 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>558</v>
+        <v>443</v>
       </c>
       <c r="B49" t="str">
-        <v>2024-03-25</v>
+        <v>2023-04-18</v>
       </c>
       <c r="C49" t="str">
         <v>Diesel</v>
@@ -32017,21 +32017,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E49" t="str">
-        <v>15300</v>
+        <v>2300</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p11 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>559</v>
+        <v>459</v>
       </c>
       <c r="B50" t="str">
-        <v>2024-03-28</v>
+        <v>2023-04-19</v>
       </c>
       <c r="C50" t="str">
         <v>Diesel</v>
@@ -32040,44 +32040,44 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E50" t="str">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F50" t="str">
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p9 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="B51" t="str">
-        <v>2024-03-28</v>
+        <v>2023-04-21</v>
       </c>
       <c r="C51" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D51" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E51" t="str">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="F51" t="str">
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p10 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>562</v>
+        <v>461</v>
       </c>
       <c r="B52" t="str">
-        <v>2024-04-01</v>
+        <v>2023-04-23</v>
       </c>
       <c r="C52" t="str">
         <v>Diesel</v>
@@ -32086,67 +32086,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E52" t="str">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p11 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>566</v>
+        <v>462</v>
       </c>
       <c r="B53" t="str">
-        <v>2024-04-02</v>
+        <v>2023-04-24</v>
       </c>
       <c r="C53" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D53" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E53" t="str">
-        <v>17000</v>
+        <v>20300</v>
       </c>
       <c r="F53" t="str">
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>p10 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>567</v>
+        <v>463</v>
       </c>
       <c r="B54" t="str">
-        <v>2024-04-02</v>
+        <v>2023-04-26</v>
       </c>
       <c r="C54" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D54" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E54" t="str">
-        <v>3000</v>
+        <v>20300</v>
       </c>
       <c r="F54" t="str">
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p10 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>569</v>
+        <v>464</v>
       </c>
       <c r="B55" t="str">
-        <v>2024-04-04</v>
+        <v>2023-04-27</v>
       </c>
       <c r="C55" t="str">
         <v>Diesel</v>
@@ -32155,44 +32155,44 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E55" t="str">
-        <v>19700</v>
+        <v>8000</v>
       </c>
       <c r="F55" t="str">
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>corrected from struck 19/5/24 | p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल | p11 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>573</v>
+        <v>465</v>
       </c>
       <c r="B56" t="str">
-        <v>2024-04-06</v>
+        <v>2023-05-06</v>
       </c>
       <c r="C56" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D56" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E56" t="str">
-        <v>20000</v>
+        <v>20300</v>
       </c>
       <c r="F56" t="str">
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>p12 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>579</v>
+        <v>466</v>
       </c>
       <c r="B57" t="str">
-        <v>2024-04-09</v>
+        <v>2023-05-11</v>
       </c>
       <c r="C57" t="str">
         <v>Diesel</v>
@@ -32201,21 +32201,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E57" t="str">
-        <v>37600</v>
+        <v>20000</v>
       </c>
       <c r="F57" t="str">
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>बकीट आणली | p4 | imported from Diesel expenses M2.pdf</v>
+        <v>सी.एस. खा डीझेल दादा | p13 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>582</v>
+        <v>467</v>
       </c>
       <c r="B58" t="str">
-        <v>2024-04-10</v>
+        <v>2023-05-12</v>
       </c>
       <c r="C58" t="str">
         <v>Diesel</v>
@@ -32224,21 +32224,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E58" t="str">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F58" t="str">
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>कॅश दिली डिझेलला | p14 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>584</v>
+        <v>468</v>
       </c>
       <c r="B59" t="str">
-        <v>2024-04-12</v>
+        <v>2023-05-15</v>
       </c>
       <c r="C59" t="str">
         <v>Diesel</v>
@@ -32247,21 +32247,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E59" t="str">
-        <v>19700</v>
+        <v>4975</v>
       </c>
       <c r="F59" t="str">
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>585</v>
+        <v>469</v>
       </c>
       <c r="B60" t="str">
-        <v>2024-04-13</v>
+        <v>2023-05-15</v>
       </c>
       <c r="C60" t="str">
         <v>Diesel</v>
@@ -32270,21 +32270,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E60" t="str">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F60" t="str">
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>कॅश दिली डिझेलला | p14 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>587</v>
+        <v>470</v>
       </c>
       <c r="B61" t="str">
-        <v>2024-04-17</v>
+        <v>2023-05-17</v>
       </c>
       <c r="C61" t="str">
         <v>Diesel</v>
@@ -32293,21 +32293,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E61" t="str">
-        <v>20000</v>
+        <v>20300</v>
       </c>
       <c r="F61" t="str">
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>कॅश दिली डिझेलला | p14 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>589</v>
+        <v>471</v>
       </c>
       <c r="B62" t="str">
-        <v>2024-04-19</v>
+        <v>2023-05-20</v>
       </c>
       <c r="C62" t="str">
         <v>Diesel</v>
@@ -32316,21 +32316,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E62" t="str">
-        <v>17300</v>
+        <v>20300</v>
       </c>
       <c r="F62" t="str">
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>p2 | imported from Diesel expenses M2.pdf</v>
+        <v>कॅश दिली डिझेलला | p14 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>599</v>
+        <v>472</v>
       </c>
       <c r="B63" t="str">
-        <v>2024-04-24</v>
+        <v>2023-05-23</v>
       </c>
       <c r="C63" t="str">
         <v>Diesel</v>
@@ -32339,21 +32339,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E63" t="str">
-        <v>20000</v>
+        <v>20400</v>
       </c>
       <c r="F63" t="str">
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल ८५ लि | बाळासाहेब हस्ते | p15 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>613</v>
+        <v>473</v>
       </c>
       <c r="B64" t="str">
-        <v>2024-05-04</v>
+        <v>2023-05-25</v>
       </c>
       <c r="C64" t="str">
         <v>Diesel</v>
@@ -32362,21 +32362,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E64" t="str">
-        <v>20000</v>
+        <v>20300</v>
       </c>
       <c r="F64" t="str">
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल ८३ लि | बाळासाहेब हस्ते | p15 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>618</v>
+        <v>474</v>
       </c>
       <c r="B65" t="str">
-        <v>2024-05-08</v>
+        <v>2023-05-27</v>
       </c>
       <c r="C65" t="str">
         <v>Diesel</v>
@@ -32385,21 +32385,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E65" t="str">
-        <v>20000</v>
+        <v>20300</v>
       </c>
       <c r="F65" t="str">
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल ८३ लि | बाळासाहेब हस्ते | p15 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>632</v>
+        <v>475</v>
       </c>
       <c r="B66" t="str">
-        <v>2024-05-14</v>
+        <v>2023-05-29</v>
       </c>
       <c r="C66" t="str">
         <v>Diesel</v>
@@ -32408,21 +32408,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E66" t="str">
-        <v>20000</v>
+        <v>20300</v>
       </c>
       <c r="F66" t="str">
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल ८३ लि | बाळासाहेब हस्ते | p15 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>648</v>
+        <v>476</v>
       </c>
       <c r="B67" t="str">
-        <v>2024-05-20</v>
+        <v>2023-05-30</v>
       </c>
       <c r="C67" t="str">
         <v>Diesel</v>
@@ -32431,182 +32431,182 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E67" t="str">
-        <v>20000</v>
+        <v>7975</v>
       </c>
       <c r="F67" t="str">
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>676</v>
+        <v>477</v>
       </c>
       <c r="B68" t="str">
-        <v>2024-05-31</v>
+        <v>2023-06-01</v>
       </c>
       <c r="C68" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D68" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E68" t="str">
-        <v>5000</v>
+        <v>20300</v>
       </c>
       <c r="F68" t="str">
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | दि. २७. ५/२३ | p16 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>687</v>
+        <v>478</v>
       </c>
       <c r="B69" t="str">
-        <v>2024-06-02</v>
+        <v>2023-06-03</v>
       </c>
       <c r="C69" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D69" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E69" t="str">
-        <v>3300</v>
+        <v>20300</v>
       </c>
       <c r="F69" t="str">
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | दि. २८. ५/२३ | p16 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>690</v>
+        <v>479</v>
       </c>
       <c r="B70" t="str">
-        <v>2024-06-04</v>
+        <v>2023-06-06</v>
       </c>
       <c r="C70" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D70" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E70" t="str">
-        <v>5000</v>
+        <v>20300</v>
       </c>
       <c r="F70" t="str">
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | दि. २९. ५/२३ | p16 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>721</v>
+        <v>480</v>
       </c>
       <c r="B71" t="str">
-        <v>2024-06-24</v>
+        <v>2023-06-09</v>
       </c>
       <c r="C71" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D71" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E71" t="str">
-        <v>3000</v>
+        <v>20300</v>
       </c>
       <c r="F71" t="str">
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>p1 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | दि. ३०. ५/२३ | p16 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>730</v>
+        <v>481</v>
       </c>
       <c r="B72" t="str">
-        <v>2024-09-13</v>
+        <v>2023-06-11</v>
       </c>
       <c r="C72" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D72" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E72" t="str">
-        <v>6200</v>
+        <v>24060</v>
       </c>
       <c r="F72" t="str">
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>बॅटरी मशीन | p4 | imported from Diesel expenses M2.pdf</v>
+        <v>p17 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>738</v>
+        <v>482</v>
       </c>
       <c r="B73" t="str">
-        <v>2024-10-08</v>
+        <v>2023-06-14</v>
       </c>
       <c r="C73" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D73" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E73" t="str">
-        <v>3300</v>
+        <v>20300</v>
       </c>
       <c r="F73" t="str">
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>p17 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>739</v>
+        <v>483</v>
       </c>
       <c r="B74" t="str">
-        <v>2024-10-10</v>
+        <v>2023-06-17</v>
       </c>
       <c r="C74" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D74" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E74" t="str">
-        <v>3300</v>
+        <v>20300</v>
       </c>
       <c r="F74" t="str">
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>p17 | imported from M2_expences_book1.pdf</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>740</v>
+        <v>484</v>
       </c>
       <c r="B75" t="str">
-        <v>2024-10-10</v>
+        <v>2023-06-18</v>
       </c>
       <c r="C75" t="str">
         <v>Diesel</v>
@@ -32615,21 +32615,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E75" t="str">
-        <v>3300</v>
+        <v>20000</v>
       </c>
       <c r="F75" t="str">
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>741</v>
+        <v>485</v>
       </c>
       <c r="B76" t="str">
-        <v>2024-10-11</v>
+        <v>2023-06-21</v>
       </c>
       <c r="C76" t="str">
         <v>Diesel</v>
@@ -32638,228 +32638,228 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E76" t="str">
-        <v>3300</v>
+        <v>20000</v>
       </c>
       <c r="F76" t="str">
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>date corrected (struck first digit of day) | p4 | imported from Diesel expenses M2.pdf</v>
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>742</v>
+        <v>486</v>
       </c>
       <c r="B77" t="str">
-        <v>2024-10-23</v>
+        <v>2023-06-21</v>
       </c>
       <c r="C77" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D77" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E77" t="str">
-        <v>3300</v>
+        <v>20300</v>
       </c>
       <c r="F77" t="str">
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>1/2 पगार | p1 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>743</v>
+        <v>487</v>
       </c>
       <c r="B78" t="str">
-        <v>2024-10-23</v>
+        <v>2023-06-22</v>
       </c>
       <c r="C78" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D78" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E78" t="str">
-        <v>3300</v>
+        <v>20300</v>
       </c>
       <c r="F78" t="str">
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>1/2 पगार | p1 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>744</v>
+        <v>488</v>
       </c>
       <c r="B79" t="str">
-        <v>2024-11-11</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C79" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D79" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E79" t="str">
-        <v>3300</v>
+        <v>5400</v>
       </c>
       <c r="F79" t="str">
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>कटर कीट | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>747</v>
+        <v>489</v>
       </c>
       <c r="B80" t="str">
-        <v>2024-11-27</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C80" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D80" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E80" t="str">
-        <v>2000</v>
+        <v>560</v>
       </c>
       <c r="F80" t="str">
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>बेल्ट | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>748</v>
+        <v>490</v>
       </c>
       <c r="B81" t="str">
-        <v>2024-11-30</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C81" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D81" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E81" t="str">
-        <v>3300</v>
+        <v>1300</v>
       </c>
       <c r="F81" t="str">
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>कुलंट | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>749</v>
+        <v>491</v>
       </c>
       <c r="B82" t="str">
-        <v>2024-12-01</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C82" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D82" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E82" t="str">
-        <v>3300</v>
+        <v>350</v>
       </c>
       <c r="F82" t="str">
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>पाईप | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>761</v>
+        <v>492</v>
       </c>
       <c r="B83" t="str">
-        <v>2024-12-29</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C83" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D83" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E83" t="str">
-        <v>3459</v>
+        <v>1600</v>
       </c>
       <c r="F83" t="str">
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>वाशिंग | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>772</v>
+        <v>493</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-02-21</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C84" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D84" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E84" t="str">
-        <v>2930</v>
+        <v>4000</v>
       </c>
       <c r="F84" t="str">
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>मशीन काचे काच | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>773</v>
+        <v>494</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-02-22</v>
+        <v>2023-06-30</v>
       </c>
       <c r="C85" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D85" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E85" t="str">
-        <v>20000</v>
+        <v>8500</v>
       </c>
       <c r="F85" t="str">
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>स्पीकर | p5 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>774</v>
+        <v>495</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-03-01</v>
+        <v>2023-07-01</v>
       </c>
       <c r="C86" t="str">
         <v>Diesel</v>
@@ -32868,67 +32868,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E86" t="str">
-        <v>20000</v>
+        <v>24900</v>
       </c>
       <c r="F86" t="str">
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल पांगरा | undated line above 1-7-23 header | p3 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>780</v>
+        <v>496</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-03-10</v>
+        <v>2023-07-01</v>
       </c>
       <c r="C87" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D87" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E87" t="str">
-        <v>5400</v>
+        <v>24300</v>
       </c>
       <c r="F87" t="str">
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>Servecing | p3 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>814</v>
+        <v>497</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-04-01</v>
+        <v>2023-07-01</v>
       </c>
       <c r="C88" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D88" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E88" t="str">
-        <v>7000</v>
+        <v>2300</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>date corrected (month digit overwritten) | p6 | imported from Diesel expenses M2.pdf</v>
+        <v>सर्व्हीसिंग | p3 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>836</v>
+        <v>498</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-04-24</v>
+        <v>2023-07-09</v>
       </c>
       <c r="C89" t="str">
         <v>Diesel</v>
@@ -32937,67 +32937,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E89" t="str">
-        <v>3600</v>
+        <v>4850</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल 50 लि | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>837</v>
+        <v>499</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-04-26</v>
+        <v>2023-07-09</v>
       </c>
       <c r="C90" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D90" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E90" t="str">
-        <v>3400</v>
+        <v>400</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>जेवण | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>841</v>
+        <v>500</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-04-29</v>
+        <v>2023-07-09</v>
       </c>
       <c r="C91" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D91" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E91" t="str">
-        <v>720</v>
+        <v>2500</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>846</v>
+        <v>501</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-05-01</v>
+        <v>2023-07-12</v>
       </c>
       <c r="C92" t="str">
         <v>Diesel</v>
@@ -33006,67 +33006,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E92" t="str">
-        <v>3500</v>
+        <v>4850</v>
       </c>
       <c r="F92" t="str">
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल 50 लि | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>849</v>
+        <v>502</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-05-05</v>
+        <v>2023-07-12</v>
       </c>
       <c r="C93" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D93" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E93" t="str">
-        <v>3300</v>
+        <v>500</v>
       </c>
       <c r="F93" t="str">
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>p4 | imported from Diesel expenses M2.pdf</v>
+        <v>हातखर्ची | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>850</v>
+        <v>503</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-05-05</v>
+        <v>2023-07-12</v>
       </c>
       <c r="C94" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D94" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E94" t="str">
-        <v>3700</v>
+        <v>400</v>
       </c>
       <c r="F94" t="str">
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>जेवण | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>851</v>
+        <v>504</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-05-05</v>
+        <v>2023-07-15</v>
       </c>
       <c r="C95" t="str">
         <v>Diesel</v>
@@ -33075,67 +33075,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E95" t="str">
-        <v>7200</v>
+        <v>4850</v>
       </c>
       <c r="F95" t="str">
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल 50 लि | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>854</v>
+        <v>505</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-05-08</v>
+        <v>2023-07-15</v>
       </c>
       <c r="C96" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D96" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E96" t="str">
-        <v>3050</v>
+        <v>400</v>
       </c>
       <c r="F96" t="str">
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>जेवण | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>855</v>
+        <v>506</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-05-09</v>
+        <v>2023-07-15</v>
       </c>
       <c r="C97" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D97" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E97" t="str">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="F97" t="str">
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>date corrected (day 4 struck, written as 9) | p6 | imported from Diesel expenses M2.pdf</v>
+        <v>पगार | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>856</v>
+        <v>507</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-05-10</v>
+        <v>2023-07-18</v>
       </c>
       <c r="C98" t="str">
         <v>Diesel</v>
@@ -33144,67 +33144,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E98" t="str">
-        <v>5400</v>
+        <v>4850</v>
       </c>
       <c r="F98" t="str">
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल 50 लि | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>859</v>
+        <v>508</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-05-13</v>
+        <v>2023-07-18</v>
       </c>
       <c r="C99" t="str">
-        <v>Diesel</v>
+        <v>Misc</v>
       </c>
       <c r="D99" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E99" t="str">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="F99" t="str">
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>हातखर्ची | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>889</v>
+        <v>509</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-07-04</v>
+        <v>2023-07-18</v>
       </c>
       <c r="C100" t="str">
-        <v>Diesel</v>
+        <v>Maintenance</v>
       </c>
       <c r="D100" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E100" t="str">
-        <v>3700</v>
+        <v>1450</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>ग्रीस ऑईल | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>890</v>
+        <v>510</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-09-01</v>
+        <v>2023-07-21</v>
       </c>
       <c r="C101" t="str">
         <v>Diesel</v>
@@ -33213,67 +33213,67 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E101" t="str">
-        <v>3700</v>
+        <v>4850</v>
       </c>
       <c r="F101" t="str">
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>डिझेल 50 लि | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>891</v>
+        <v>511</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-09-28</v>
+        <v>2023-07-21</v>
       </c>
       <c r="C102" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D102" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E102" t="str">
-        <v>3600</v>
+        <v>1500</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>892</v>
+        <v>512</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-11-15</v>
+        <v>2023-07-31</v>
       </c>
       <c r="C103" t="str">
-        <v>Diesel</v>
+        <v>Salary</v>
       </c>
       <c r="D103" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E103" t="str">
-        <v>10419</v>
+        <v>1750</v>
       </c>
       <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>ड्रायव्हर पगार | p2 | imported from M2_expences_book2 2.pdf</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>893</v>
+        <v>519</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-11-17</v>
+        <v>2023-10-03</v>
       </c>
       <c r="C104" t="str">
         <v>Diesel</v>
@@ -33282,21 +33282,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E104" t="str">
-        <v>3550</v>
+        <v>4500</v>
       </c>
       <c r="F104" t="str">
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>894</v>
+        <v>522</v>
       </c>
       <c r="B105" t="str">
-        <v>2026-02-16</v>
+        <v>2023-10-17</v>
       </c>
       <c r="C105" t="str">
         <v>Diesel</v>
@@ -33305,21 +33305,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E105" t="str">
-        <v>40000</v>
+        <v>3500</v>
       </c>
       <c r="F105" t="str">
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>895</v>
+        <v>523</v>
       </c>
       <c r="B106" t="str">
-        <v>2026-02-16</v>
+        <v>2023-10-25</v>
       </c>
       <c r="C106" t="str">
         <v>Diesel</v>
@@ -33328,21 +33328,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E106" t="str">
-        <v>60000</v>
+        <v>4950</v>
       </c>
       <c r="F106" t="str">
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>896</v>
+        <v>524</v>
       </c>
       <c r="B107" t="str">
-        <v>2026-03-25</v>
+        <v>2023-10-26</v>
       </c>
       <c r="C107" t="str">
         <v>Diesel</v>
@@ -33351,21 +33351,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E107" t="str">
-        <v>34700</v>
+        <v>4950</v>
       </c>
       <c r="F107" t="str">
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>897</v>
+        <v>525</v>
       </c>
       <c r="B108" t="str">
-        <v>2026-05-03</v>
+        <v>2023-10-29</v>
       </c>
       <c r="C108" t="str">
         <v>Diesel</v>
@@ -33374,21 +33374,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E108" t="str">
-        <v>30000</v>
+        <v>3500</v>
       </c>
       <c r="F108" t="str">
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>898</v>
+        <v>526</v>
       </c>
       <c r="B109" t="str">
-        <v>2026-05-06</v>
+        <v>2023-10-30</v>
       </c>
       <c r="C109" t="str">
         <v>Diesel</v>
@@ -33397,21 +33397,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E109" t="str">
-        <v>3559</v>
+        <v>1048</v>
       </c>
       <c r="F109" t="str">
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>899</v>
+        <v>528</v>
       </c>
       <c r="B110" t="str">
-        <v>2026-05-06</v>
+        <v>2023-11-02</v>
       </c>
       <c r="C110" t="str">
         <v>Diesel</v>
@@ -33420,21 +33420,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E110" t="str">
-        <v>5426</v>
+        <v>4900</v>
       </c>
       <c r="F110" t="str">
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>p5 | imported from Diesel expenses M2.pdf</v>
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>900</v>
+        <v>529</v>
       </c>
       <c r="B111" t="str">
-        <v>2026-05-23</v>
+        <v>2023-11-03</v>
       </c>
       <c r="C111" t="str">
         <v>Diesel</v>
@@ -33443,21 +33443,21 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E111" t="str">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="F111" t="str">
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>p7 | imported from Diesel expenses M2.pdf</v>
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>901</v>
+        <v>530</v>
       </c>
       <c r="B112" t="str">
-        <v>2026-06-01</v>
+        <v>2023-11-11</v>
       </c>
       <c r="C112" t="str">
         <v>Diesel</v>
@@ -33466,41 +33466,2824 @@
         <v>M2-Mahindra earthmaster sx iv 2023</v>
       </c>
       <c r="E112" t="str">
-        <v>90000</v>
+        <v>3500</v>
       </c>
       <c r="F112" t="str">
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>p6 | imported from Diesel expenses M2.pdf</v>
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>902</v>
+        <v>531</v>
       </c>
       <c r="B113" t="str">
+        <v>2023-11-13</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D113" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E113" t="str">
+        <v>6000</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>राहुल वसमत operator | p6 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>532</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2023-11-13</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D114" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E114" t="str">
+        <v>15600</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v>विजय कोंडेगाव operator | p6 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>534</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2023-11-25</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D115" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E115" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>536</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2023-11-28</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D116" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E116" t="str">
+        <v>4950</v>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>546</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2023-12-10</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D117" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E117" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>558</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2023-12-19</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D118" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E118" t="str">
+        <v>13036</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>559</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2023-12-20</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D119" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E119" t="str">
+        <v>3259</v>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>560</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2023-12-21</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D120" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E120" t="str">
+        <v>2900</v>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>561</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2023-12-22</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D121" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E121" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>562</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2023-12-22</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D122" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E122" t="str">
+        <v>3200</v>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>576</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2024-01-12</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D123" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E123" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>577</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D124" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E124" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>578</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2024-01-16</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D125" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E125" t="str">
+        <v>3200</v>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>606</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2024-02-12</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D126" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E126" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>614</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2024-02-18</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D127" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E127" t="str">
+        <v>3460</v>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>616</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2024-02-24</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D128" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E128" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>619</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2024-02-26</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D129" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E129" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>620</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2024-02-27</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D130" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2400</v>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v>p3 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>623</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2024-02-29</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D131" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E131" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>625</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D132" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E132" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>633</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D133" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E133" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>635</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2024-03-12</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D134" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E134" t="str">
+        <v>5323</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>636</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2024-03-12</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D135" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E135" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v>p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>637</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D136" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E136" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>638</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D137" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E137" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>639</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D138" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E138" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v>डिझेल | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>640</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2024-03-13</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D139" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E139" t="str">
+        <v>15300</v>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v>p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>649</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2024-03-17</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D140" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E140" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>650</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2024-03-18</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D141" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E141" t="str">
+        <v>14500</v>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>651</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2024-03-18</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D142" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E142" t="str">
+        <v>15300</v>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v>p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>652</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2024-03-19</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D143" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E143" t="str">
+        <v>17300</v>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v>p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>653</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2024-03-21</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D144" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E144" t="str">
+        <v>8000</v>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v>p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>654</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2024-03-23</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D145" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E145" t="str">
+        <v>4900</v>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>655</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2024-03-24</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D146" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E146" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>656</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2024-03-25</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D147" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E147" t="str">
+        <v>15300</v>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>657</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2024-03-25</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D148" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E148" t="str">
+        <v>7650</v>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>658</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2024-03-28</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D149" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E149" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>659</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2024-03-28</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D150" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E150" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>661</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2024-04-01</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D151" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E151" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>665</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2024-04-02</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D152" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E152" t="str">
+        <v>17000</v>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>666</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2024-04-02</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D153" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E153" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>668</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2024-04-04</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D154" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E154" t="str">
+        <v>19700</v>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v>corrected from struck 19/5/24 | p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>672</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2024-04-06</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D155" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E155" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>673</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2024-04-06</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D156" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E156" t="str">
+        <v>20300</v>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>679</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2024-04-09</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D157" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E157" t="str">
+        <v>37600</v>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v>बकीट आणली | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>682</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2024-04-10</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D158" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E158" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>684</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2024-04-12</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D159" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E159" t="str">
+        <v>19700</v>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>685</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2024-04-12</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D160" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E160" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>686</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2024-04-13</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D161" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E161" t="str">
+        <v>15000</v>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>688</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2024-04-17</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D162" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E162" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>690</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2024-04-19</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D163" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E163" t="str">
+        <v>17300</v>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v>p2 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>700</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2024-04-24</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D164" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E164" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>705</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2024-04-29</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D165" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E165" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>715</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2024-05-04</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D166" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E166" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>720</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2024-05-07</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D167" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E167" t="str">
+        <v>20300</v>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>721</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2024-05-08</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D168" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E168" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>735</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2024-05-14</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D169" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E169" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>740</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2024-05-17</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D170" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E170" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>752</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2024-05-20</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D171" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E171" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>763</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2024-05-24</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D172" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E172" t="str">
+        <v>6000</v>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v>year 2024 from prior entries | p7 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>769</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2024-05-26</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D173" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E173" t="str">
+        <v>20300</v>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v>बापू डिझेल | p8 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>782</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2024-05-31</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D174" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E174" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>792</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2024-06-01</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D175" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E175" t="str">
+        <v>5500</v>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v>बापू डिझेल | p8 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>794</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2024-06-02</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D176" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E176" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>797</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2024-06-04</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D177" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E177" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>798</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2024-06-04</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D178" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E178" t="str">
+        <v>5300</v>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v>बापू डिझेल | p8 | imported from M2_expences_book2 2.pdf</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>829</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2024-06-24</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D179" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E179" t="str">
+        <v>3000</v>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v>p1 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>838</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2024-09-13</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D180" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E180" t="str">
+        <v>6200</v>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v>बॅटरी मशीन | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>846</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2024-10-08</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D181" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E181" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>847</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2024-10-10</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D182" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E182" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>848</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2024-10-10</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D183" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E183" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>849</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2024-10-11</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D184" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E184" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v>date corrected (struck first digit of day) | p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>850</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2024-10-23</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D185" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E185" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>851</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2024-10-23</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D186" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E186" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>852</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2024-11-11</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D187" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E187" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>855</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2024-11-27</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D188" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E188" t="str">
+        <v>2000</v>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>856</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2024-11-30</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D189" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E189" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>857</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2024-12-01</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D190" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E190" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>869</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2024-12-29</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D191" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E191" t="str">
+        <v>3459</v>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>880</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2025-02-21</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D192" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E192" t="str">
+        <v>2930</v>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>881</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2025-02-22</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D193" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E193" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>882</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D194" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E194" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>888</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2025-03-10</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D195" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E195" t="str">
+        <v>5400</v>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>922</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2025-04-01</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D196" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E196" t="str">
+        <v>7000</v>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v>date corrected (month digit overwritten) | p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>944</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2025-04-24</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D197" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E197" t="str">
+        <v>3600</v>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>945</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2025-04-26</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D198" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E198" t="str">
+        <v>3400</v>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>949</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2025-04-29</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D199" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E199" t="str">
+        <v>720</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>954</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2025-05-01</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D200" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E200" t="str">
+        <v>3500</v>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>957</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D201" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E201" t="str">
+        <v>3300</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v>p4 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>958</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D202" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E202" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>959</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2025-05-05</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D203" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E203" t="str">
+        <v>7200</v>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>962</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2025-05-08</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D204" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E204" t="str">
+        <v>3050</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>963</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2025-05-09</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D205" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E205" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v>date corrected (day 4 struck, written as 9) | p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>964</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2025-05-10</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D206" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E206" t="str">
+        <v>5400</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>967</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2025-05-13</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D207" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E207" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>997</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2025-07-04</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D208" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E208" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>998</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D209" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E209" t="str">
+        <v>3700</v>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>999</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2025-09-28</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D210" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E210" t="str">
+        <v>3600</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>1000</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2025-11-15</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D211" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E211" t="str">
+        <v>10419</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>1001</v>
+      </c>
+      <c r="B212" t="str">
+        <v>2025-11-17</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D212" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E212" t="str">
+        <v>3550</v>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>1002</v>
+      </c>
+      <c r="B213" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D213" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E213" t="str">
+        <v>40000</v>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>1003</v>
+      </c>
+      <c r="B214" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D214" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E214" t="str">
+        <v>60000</v>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>1004</v>
+      </c>
+      <c r="B215" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D215" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E215" t="str">
+        <v>34700</v>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>1005</v>
+      </c>
+      <c r="B216" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D216" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E216" t="str">
+        <v>1670</v>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v>photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>1006</v>
+      </c>
+      <c r="B217" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D217" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E217" t="str">
+        <v>30000</v>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>1007</v>
+      </c>
+      <c r="B218" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D218" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E218" t="str">
+        <v>649</v>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v>photo IMG_4097 | date carried from line above (undated amount) | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>1008</v>
+      </c>
+      <c r="B219" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D219" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E219" t="str">
+        <v>3559</v>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>1009</v>
+      </c>
+      <c r="B220" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D220" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E220" t="str">
+        <v>5426</v>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v>p5 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>1010</v>
+      </c>
+      <c r="B221" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D221" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E221" t="str">
+        <v>15000</v>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v>photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>1011</v>
+      </c>
+      <c r="B222" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D222" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E222" t="str">
+        <v>24999</v>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v>खंडगाव | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>1012</v>
+      </c>
+      <c r="B223" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D223" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E223" t="str">
+        <v>8000</v>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>1013</v>
+      </c>
+      <c r="B224" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D224" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E224" t="str">
+        <v>11132</v>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v>खंडेगाव | photo IMG_4098 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>1014</v>
+      </c>
+      <c r="B225" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D225" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E225" t="str">
+        <v>7868</v>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v>खंडेगाव | photo IMG_4098 | date carried | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>1015</v>
+      </c>
+      <c r="B226" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="D226" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E226" t="str">
+        <v>90000</v>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v>p6 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>1016</v>
+      </c>
+      <c r="B227" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D227" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E227" t="str">
+        <v>12000</v>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v>वसमत | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>1017</v>
+      </c>
+      <c r="B228" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="C113" t="str">
+      <c r="C228" t="str">
         <v>Diesel</v>
       </c>
-      <c r="D113" t="str">
-        <v>M2-Mahindra earthmaster sx iv 2023</v>
-      </c>
-      <c r="E113" t="str">
+      <c r="D228" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E228" t="str">
         <v>12000</v>
       </c>
-      <c r="F113" t="str">
-        <v/>
-      </c>
-      <c r="G113" t="str">
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
         <v>p7 | imported from Diesel expenses M2.pdf</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>1018</v>
+      </c>
+      <c r="B229" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D229" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E229" t="str">
+        <v>5000</v>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v>वसमत | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>1019</v>
+      </c>
+      <c r="B230" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D230" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E230" t="str">
+        <v>8000</v>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v>वसमत | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>1020</v>
+      </c>
+      <c r="B231" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D231" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E231" t="str">
+        <v>14300</v>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v>वसमत | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>1021</v>
+      </c>
+      <c r="B232" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Misc</v>
+      </c>
+      <c r="D232" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E232" t="str">
+        <v>20000</v>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v>निळा | photo IMG_4097 | ditto निळा | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>1022</v>
+      </c>
+      <c r="B233" t="str">
+        <v>2026-07-25</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="D233" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E233" t="str">
+        <v>6500</v>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v>निळा पंप | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>1023</v>
+      </c>
+      <c r="B234" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="D234" t="str">
+        <v>M2-Mahindra earthmaster sx iv 2023</v>
+      </c>
+      <c r="E234" t="str">
+        <v>86000</v>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v>वसमत पंप | photo IMG_4097 | imported from IMG_4097-4098 (M2 expenses photos)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G234"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -6343,10 +6343,10 @@
         <v>54400</v>
       </c>
       <c r="H170">
-        <v>34500</v>
+        <v>54400</v>
       </c>
       <c r="I170">
-        <v>19900</v>
+        <v>0</v>
       </c>
       <c r="J170" t="str">
         <v>320 पाईप | जमा 34500 बाकी 19900 | भगवान मुकदम | p16 | imported from Newmachine2.pdf</v>
@@ -9543,10 +9543,10 @@
         <v>75000</v>
       </c>
       <c r="H270">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="I270">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J270" t="str">
         <v>10000 बाकी | 498 @150 | p8 | imported from Newmachinevook2.pdf</v>
@@ -9607,10 +9607,10 @@
         <v>47700</v>
       </c>
       <c r="H272">
-        <v>23850</v>
+        <v>41700</v>
       </c>
       <c r="I272">
-        <v>23850</v>
+        <v>6000</v>
       </c>
       <c r="J272" t="str">
         <v>23850 बाकी | 298 ट्रीप @160 | p8 | imported from Newmachinevook2.pdf</v>
@@ -9639,10 +9639,10 @@
         <v>34000</v>
       </c>
       <c r="H273">
-        <v>10000</v>
+        <v>34000</v>
       </c>
       <c r="I273">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="J273" t="str">
         <v>24000 बाकी | 200 ट्रीप @170 | p8 | imported from Newmachinevook2.pdf</v>
@@ -9703,10 +9703,10 @@
         <v>49500</v>
       </c>
       <c r="H275">
-        <v>37000</v>
+        <v>49500</v>
       </c>
       <c r="I275">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="J275" t="str">
         <v>12500 बाकी | 330 @150 | p8 | imported from Newmachinevook2.pdf</v>
@@ -9767,10 +9767,10 @@
         <v>42625</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>42625</v>
       </c>
       <c r="I277">
-        <v>42625</v>
+        <v>0</v>
       </c>
       <c r="J277" t="str">
         <v>42625 बाकी - fully pending | 341 @125 | p8 | imported from Newmachinevook2.pdf</v>
@@ -38405,7 +38405,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38441,10 +38441,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-31T21:15:10.444Z</v>
+        <v>2026-07-31T21:57:46.558Z</v>
       </c>
       <c r="C2" t="str">
         <v>Administrator</v>
@@ -38453,16 +38453,16 @@
         <v>income</v>
       </c>
       <c r="E2" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F2">
-        <v>1767</v>
+        <v>1431</v>
       </c>
       <c r="G2" t="str">
-        <v>{"ID":1767,"Date":"2025-03-25","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.3,"BillAmount":3000,"ReceivedAmount":3000,"PendingAmount":0,"Remarks":"-||- | date assumed from spread/neighbor | 2.30 | p2 | imported from M1_book3_2.pdf"}</v>
+        <v>{"ID":1431,"Date":"2024-05-20","Customer":"Nagorao Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":2520,"ReceivedAmount":0,"PendingAmount":2520,"Remarks":"-||- | date assumed from spread/neighbor | 14 पा | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H2" t="str">
-        <v>{"ID":1767,"Date":"2025-03-25","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.3,"BillAmount":3000,"ReceivedAmount":3000,"PendingAmount":0,"Remarks":"-||- | date assumed from spread/neighbor | 2.30 | p2 | imported from M1_book3_2.pdf"}</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>client-side</v>
@@ -38473,10 +38473,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-07-31T21:15:00.639Z</v>
+        <v>2026-07-31T21:57:25.955Z</v>
       </c>
       <c r="C3" t="str">
         <v>Administrator</v>
@@ -38485,16 +38485,16 @@
         <v>income</v>
       </c>
       <c r="E3" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F3">
-        <v>1766</v>
+        <v>1430</v>
       </c>
       <c r="G3" t="str">
-        <v>{"ID":1766,"Date":"2025-03-25","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":38.3,"BillAmount":41800,"ReceivedAmount":0,"PendingAmount":41800,"Remarks":"date assumed from spread/neighbor | 38.30 | p2 | imported from M1_book3_2.pdf"}</v>
+        <v>{"ID":1430,"Date":"2024-05-20","Customer":"Nagorao Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.5,"BillAmount":3000,"ReceivedAmount":0,"PendingAmount":3000,"Remarks":"date assumed from spread/neighbor | 2.30 मि | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H3" t="str">
-        <v>{"ID":1766,"Date":"2025-03-25","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":38.3,"BillAmount":41800,"ReceivedAmount":41800,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 38.30 | p2 | imported from M1_book3_2.pdf"}</v>
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>client-side</v>
@@ -38505,10 +38505,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-31T21:14:34.743Z</v>
+        <v>2026-07-31T21:56:56.991Z</v>
       </c>
       <c r="C4" t="str">
         <v>Administrator</v>
@@ -38517,16 +38517,16 @@
         <v>income</v>
       </c>
       <c r="E4" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F4">
-        <v>1763</v>
+        <v>1429</v>
       </c>
       <c r="G4" t="str">
-        <v>{"ID":1763,"Date":"2025-03-13","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":34,"BillAmount":37400,"ReceivedAmount":0,"PendingAmount":37400,"Remarks":"date assumed from spread/neighbor | 34 तास | p1 | imported from M1_book3_2.pdf"}</v>
+        <v>{"ID":1429,"Date":"2024-05-20","Customer":"Vitthal Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":2520,"ReceivedAmount":0,"PendingAmount":2520,"Remarks":"-||- | date assumed from spread/neighbor | 14 पा | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H4" t="str">
-        <v>{"ID":1763,"Date":"2025-03-13","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":34,"BillAmount":37400,"ReceivedAmount":37400,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 34 तास | p1 | imported from M1_book3_2.pdf"}</v>
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>client-side</v>
@@ -38537,10 +38537,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-07-31T21:13:12.244Z</v>
+        <v>2026-07-31T21:56:45.800Z</v>
       </c>
       <c r="C5" t="str">
         <v>Administrator</v>
@@ -38549,16 +38549,16 @@
         <v>income</v>
       </c>
       <c r="E5" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F5">
-        <v>1761</v>
+        <v>1428</v>
       </c>
       <c r="G5" t="str">
-        <v>{"ID":1761,"Date":"2025-03-13","Customer":"सरपंच रोडे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":76.12,"BillAmount":85600,"ReceivedAmount":0,"PendingAmount":85600,"Remarks":"date assumed from spread/neighbor | 76.12 | p1 | imported from M1_book3_2.pdf"}</v>
+        <v>{"ID":1428,"Date":"2024-05-20","Customer":"Vitthal Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":1.5,"BillAmount":1800,"ReceivedAmount":0,"PendingAmount":1800,"Remarks":"-||- | date assumed from spread/neighbor | 1.30 | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H5" t="str">
-        <v>{"ID":1761,"Date":"2025-03-13","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":76.12,"BillAmount":85600,"ReceivedAmount":85600,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 76.12 | p1 | imported from M1_book3_2.pdf"}</v>
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>client-side</v>
@@ -38569,10 +38569,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-31T21:11:19.388Z</v>
+        <v>2026-07-31T21:56:38.143Z</v>
       </c>
       <c r="C6" t="str">
         <v>Administrator</v>
@@ -38581,16 +38581,16 @@
         <v>income</v>
       </c>
       <c r="E6" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F6">
-        <v>518</v>
+        <v>1427</v>
       </c>
       <c r="G6" t="str">
-        <v>{"ID":518,"Date":"2023-04-26","Customer":"Ramakant Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":30400,"ReceivedAmount":10000,"PendingAmount":20400,"Remarks":"190 पाईप | जमा 10000 बाकी 20400 | p10 | imported from Newmachine2.pdf"}</v>
+        <v>{"ID":1427,"Date":"2024-05-20","Customer":"Vitthal Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":1.5,"BillAmount":1800,"ReceivedAmount":0,"PendingAmount":1800,"Remarks":"date assumed from spread/neighbor | 1.30 | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H6" t="str">
-        <v>{"ID":518,"Date":"2023-04-26","Customer":"Ramakant Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":30400,"ReceivedAmount":30400,"PendingAmount":0,"Remarks":"190 पाईप | जमा 10000 बाकी 20400 | p10 | imported from Newmachine2.pdf"}</v>
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>client-side</v>
@@ -38601,10 +38601,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-07-31T21:08:42.748Z</v>
+        <v>2026-07-31T21:56:23.449Z</v>
       </c>
       <c r="C7" t="str">
         <v>Administrator</v>
@@ -38613,16 +38613,16 @@
         <v>income</v>
       </c>
       <c r="E7" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F7">
-        <v>507</v>
+        <v>1426</v>
       </c>
       <c r="G7" t="str">
-        <v>{"ID":507,"Date":"2023-04-22","Customer":"Shahaji Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":2800,"ReceivedAmount":1800,"PendingAmount":1000,"Remarks":"16 पाईप | 1000 बाकी | p10 | imported from Newmachine2.pdf"}</v>
+        <v>{"ID":1426,"Date":"2024-05-20","Customer":"Rukmaji Barve","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":2520,"ReceivedAmount":0,"PendingAmount":2520,"Remarks":"date assumed from spread/neighbor | 14 पा | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H7" t="str">
-        <v>{"ID":507,"Date":"2023-04-22","Customer":"Shahaji Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":2800,"ReceivedAmount":2800,"PendingAmount":0,"Remarks":"16 पाईप | 1000 बाकी | p10 | imported from Newmachine2.pdf"}</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>client-side</v>
@@ -38633,10 +38633,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-31T21:07:23.915Z</v>
+        <v>2026-07-31T21:55:48.044Z</v>
       </c>
       <c r="C8" t="str">
         <v>Administrator</v>
@@ -38648,13 +38648,13 @@
         <v>UPDATE</v>
       </c>
       <c r="F8">
-        <v>372</v>
+        <v>1436</v>
       </c>
       <c r="G8" t="str">
-        <v>{"ID":372,"Date":"2023-02-10","Customer":"Jankiram Tole","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":43,"BillAmount":43000,"ReceivedAmount":8000,"PendingAmount":35000,"Remarks":"43 तास | जमा 8000 बाकी | p3 | imported from Newmachine2.pdf"}</v>
+        <v>{"ID":1436,"Date":"2024-05-20","Customer":"Rambhaji + Hivara Nimbani","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":3000,"ReceivedAmount":0,"PendingAmount":3000,"Remarks":"date assumed from spread/neighbor | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H8" t="str">
-        <v>{"ID":372,"Date":"2023-02-10","Customer":"Jankiram Tole","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":43,"BillAmount":43000,"ReceivedAmount":43000,"PendingAmount":0,"Remarks":"43 तास | जमा 8000 बाकी | p3 | imported from Newmachine2.pdf"}</v>
+        <v>{"ID":1436,"Date":"2024-05-20","Customer":"Rukhmaji","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":3000,"ReceivedAmount":0,"PendingAmount":3000,"Remarks":"date assumed from spread/neighbor | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="I8" t="str">
         <v>client-side</v>
@@ -38665,10 +38665,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-31T21:05:59.816Z</v>
+        <v>2026-07-31T21:55:12.757Z</v>
       </c>
       <c r="C9" t="str">
         <v>Administrator</v>
@@ -38677,16 +38677,16 @@
         <v>income</v>
       </c>
       <c r="E9" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F9">
-        <v>231</v>
+        <v>1425</v>
       </c>
       <c r="G9" t="str">
-        <v>{"ID":231,"Date":"2022-08-17","Customer":"Dhore pralahda &amp; baburao","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Work hrs","HoursWorked":"","BillAmount":1300,"ReceivedAmount":0,"PendingAmount":1300,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+        <v>{"ID":1425,"Date":"2024-05-20","Customer":"Balubhau Amaik","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.5,"BillAmount":3000,"ReceivedAmount":0,"PendingAmount":3000,"Remarks":"-||- | date assumed from spread/neighbor | 2.30 मि | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H9" t="str">
-        <v>{"ID":231,"Date":"2022-08-17","Customer":"Dhore pralahda &amp; baburao","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Work hrs","HoursWorked":"","BillAmount":2600,"ReceivedAmount":2600,"PendingAmount":0,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>client-side</v>
@@ -38697,10 +38697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-31T21:03:10.905Z</v>
+        <v>2026-07-31T21:54:39.622Z</v>
       </c>
       <c r="C10" t="str">
         <v>Administrator</v>
@@ -38709,16 +38709,16 @@
         <v>income</v>
       </c>
       <c r="E10" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>1424</v>
       </c>
       <c r="G10" t="str">
-        <v>{"ID":66,"Date":"2022-03-01","Customer":"baban bepari","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Trip","HoursWorked":"","BillAmount":4200,"ReceivedAmount":0,"PendingAmount":4200,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+        <v>{"ID":1424,"Date":"2024-05-20","Customer":"Balubhau Amaik","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":1,"BillAmount":1200,"ReceivedAmount":0,"PendingAmount":1200,"Remarks":"-||- | date assumed from spread/neighbor | 1 ता | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H10" t="str">
-        <v>{"ID":66,"Date":"2022-03-01","Customer":"baban bepari","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Trip","HoursWorked":"","BillAmount":4200,"ReceivedAmount":4200,"PendingAmount":0,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>client-side</v>
@@ -38729,10 +38729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-07-31T21:01:59.833Z</v>
+        <v>2026-07-31T21:54:26.958Z</v>
       </c>
       <c r="C11" t="str">
         <v>Administrator</v>
@@ -38741,16 +38741,16 @@
         <v>income</v>
       </c>
       <c r="E11" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F11">
-        <v>818</v>
+        <v>1423</v>
       </c>
       <c r="G11" t="str">
-        <v>{"ID":818,"Date":"2023-12-07","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":0,"PendingAmount":9900,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1423,"Date":"2024-05-20","Customer":"Balubhau Amaik","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":1.5,"BillAmount":1800,"ReceivedAmount":0,"PendingAmount":1800,"Remarks":"-||- | date assumed from spread/neighbor | 1.30 मि | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H11" t="str">
-        <v>{"ID":818,"Date":"2023-12-07","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":9900,"PendingAmount":0,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>client-side</v>
@@ -38761,10 +38761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-07-31T21:01:52.442Z</v>
+        <v>2026-07-31T21:54:10.291Z</v>
       </c>
       <c r="C12" t="str">
         <v>Administrator</v>
@@ -38773,16 +38773,16 @@
         <v>income</v>
       </c>
       <c r="E12" t="str">
-        <v>UPDATE</v>
+        <v>DELETE</v>
       </c>
       <c r="F12">
-        <v>821</v>
+        <v>1422</v>
       </c>
       <c r="G12" t="str">
-        <v>{"ID":821,"Date":"2023-12-08","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.3,"BillAmount":10000,"ReceivedAmount":0,"PendingAmount":10000,"Remarks":"9 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1422,"Date":"2024-05-20","Customer":"Balubhau Amaik","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":19,"BillAmount":22800,"ReceivedAmount":0,"PendingAmount":22800,"Remarks":"date assumed from spread/neighbor | 19 तास | p17 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H12" t="str">
-        <v>{"ID":821,"Date":"2023-12-08","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.3,"BillAmount":10000,"ReceivedAmount":10000,"PendingAmount":0,"Remarks":"9 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>client-side</v>
@@ -38793,10 +38793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-31T21:01:44.216Z</v>
+        <v>2026-07-31T21:46:45.780Z</v>
       </c>
       <c r="C13" t="str">
         <v>Administrator</v>
@@ -38808,13 +38808,13 @@
         <v>UPDATE</v>
       </c>
       <c r="F13">
-        <v>823</v>
+        <v>1014</v>
       </c>
       <c r="G13" t="str">
-        <v>{"ID":823,"Date":"2023-12-09","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":10.5,"BillAmount":11500,"ReceivedAmount":0,"PendingAmount":11500,"Remarks":"10 तास 30 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1014,"Date":"2024-03-14","Customer":"नान्नाजी ठौरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":49500,"ReceivedAmount":37000,"PendingAmount":12500,"Remarks":"12500 बाकी | 330 @150 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="H13" t="str">
-        <v>{"ID":823,"Date":"2023-12-09","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":10.5,"BillAmount":11500,"ReceivedAmount":11500,"PendingAmount":0,"Remarks":"10 तास 30 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1014,"Date":"2024-03-14","Customer":"नान्नाजी ठौरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":49500,"ReceivedAmount":49500,"PendingAmount":0,"Remarks":"12500 बाकी | 330 @150 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="I13" t="str">
         <v>client-side</v>
@@ -38825,10 +38825,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-07-31T21:01:34.108Z</v>
+        <v>2026-07-31T21:46:08.013Z</v>
       </c>
       <c r="C14" t="str">
         <v>Administrator</v>
@@ -38840,13 +38840,13 @@
         <v>UPDATE</v>
       </c>
       <c r="F14">
-        <v>825</v>
+        <v>1009</v>
       </c>
       <c r="G14" t="str">
-        <v>{"ID":825,"Date":"2023-12-10","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":0,"PendingAmount":9900,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1009,"Date":"2024-03-14","Customer":"वामन ठौरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":75000,"ReceivedAmount":65000,"PendingAmount":10000,"Remarks":"10000 बाकी | 498 @150 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="H14" t="str">
-        <v>{"ID":825,"Date":"2023-12-10","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":9900,"PendingAmount":0,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1009,"Date":"2024-03-14","Customer":"वामन ठौरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":75000,"ReceivedAmount":75000,"PendingAmount":0,"Remarks":"10000 बाकी | 498 @150 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="I14" t="str">
         <v>client-side</v>
@@ -38857,10 +38857,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-31T21:01:01.499Z</v>
+        <v>2026-07-31T21:45:57.705Z</v>
       </c>
       <c r="C15" t="str">
         <v>Administrator</v>
@@ -38872,13 +38872,13 @@
         <v>UPDATE</v>
       </c>
       <c r="F15">
-        <v>816</v>
+        <v>1011</v>
       </c>
       <c r="G15" t="str">
-        <v>{"ID":816,"Date":"2023-12-06","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":8.3,"BillAmount":9000,"ReceivedAmount":0,"PendingAmount":9000,"Remarks":"8 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1011,"Date":"2024-03-14","Customer":"रंगनाथ अंभोरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":47700,"ReceivedAmount":23850,"PendingAmount":23850,"Remarks":"23850 बाकी | 298 ट्रीप @160 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="H15" t="str">
-        <v>{"ID":816,"Date":"2023-12-06","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":8.3,"BillAmount":9000,"ReceivedAmount":9000,"PendingAmount":0,"Remarks":"8 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+        <v>{"ID":1011,"Date":"2024-03-14","Customer":"रंगनाथ अंभोरे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":47700,"ReceivedAmount":41700,"PendingAmount":6000,"Remarks":"23850 बाकी | 298 ट्रीप @160 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="I15" t="str">
         <v>client-side</v>
@@ -38889,28 +38889,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-13T11:17:08.408Z</v>
+        <v>2026-07-31T21:45:37.855Z</v>
       </c>
       <c r="C16" t="str">
         <v>Administrator</v>
       </c>
       <c r="D16" t="str">
-        <v>partners</v>
+        <v>income</v>
       </c>
       <c r="E16" t="str">
         <v>UPDATE</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>636</v>
       </c>
       <c r="G16" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"Baliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+        <v>{"ID":636,"Date":"2023-05-23","Customer":"Bhagwan Mukadam","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":54400,"ReceivedAmount":34500,"PendingAmount":19900,"Remarks":"320 पाईप | जमा 34500 बाकी 19900 | भगवान मुकदम | p16 | imported from Newmachine2.pdf"}</v>
       </c>
       <c r="H16" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"Baliram Barve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+        <v>{"ID":636,"Date":"2023-05-23","Customer":"Bhagwan Mukadam","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":54400,"ReceivedAmount":54400,"PendingAmount":0,"Remarks":"320 पाईप | जमा 34500 बाकी 19900 | भगवान मुकदम | p16 | imported from Newmachine2.pdf"}</v>
       </c>
       <c r="I16" t="str">
         <v>client-side</v>
@@ -38921,28 +38921,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-13T11:17:01.666Z</v>
+        <v>2026-07-31T21:45:22.685Z</v>
       </c>
       <c r="C17" t="str">
         <v>Administrator</v>
       </c>
       <c r="D17" t="str">
-        <v>partners</v>
+        <v>income</v>
       </c>
       <c r="E17" t="str">
         <v>UPDATE</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1012</v>
       </c>
       <c r="G17" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"BAliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+        <v>{"ID":1012,"Date":"2024-03-14","Customer":"श्यामा शिंदे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":34000,"ReceivedAmount":10000,"PendingAmount":24000,"Remarks":"24000 बाकी | 200 ट्रीप @170 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="H17" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"Baliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+        <v>{"ID":1012,"Date":"2024-03-14","Customer":"श्यामा शिंदे","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":34000,"ReceivedAmount":34000,"PendingAmount":0,"Remarks":"24000 बाकी | 200 ट्रीप @170 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="I17" t="str">
         <v>client-side</v>
@@ -38953,28 +38953,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-13T11:16:38.529Z</v>
+        <v>2026-07-31T21:45:07.647Z</v>
       </c>
       <c r="C18" t="str">
         <v>Administrator</v>
       </c>
       <c r="D18" t="str">
-        <v>partners</v>
+        <v>income</v>
       </c>
       <c r="E18" t="str">
-        <v>CREATE</v>
+        <v>UPDATE</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1016</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>{"ID":1016,"Date":"2024-03-14","Customer":"शिवा आबा","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":42625,"ReceivedAmount":0,"PendingAmount":42625,"Remarks":"42625 बाकी - fully pending | 341 @125 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="H18" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"Vijay Barve","TransactionType":"Investment","Amount":200000,"Remarks":"Deposite 2","ID":5}</v>
+        <v>{"ID":1016,"Date":"2024-03-14","Customer":"शिवा आबा","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":42625,"ReceivedAmount":42625,"PendingAmount":0,"Remarks":"42625 बाकी - fully pending | 341 @125 | p8 | imported from Newmachinevook2.pdf"}</v>
       </c>
       <c r="I18" t="str">
         <v>client-side</v>
@@ -38985,28 +38985,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-13T11:16:14.363Z</v>
+        <v>2026-07-31T21:44:29.263Z</v>
       </c>
       <c r="C19" t="str">
         <v>Administrator</v>
       </c>
       <c r="D19" t="str">
-        <v>partners</v>
+        <v>income</v>
       </c>
       <c r="E19" t="str">
-        <v>CREATE</v>
+        <v>UPDATE</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1061</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>{"ID":1061,"Date":"2024-04-01","Customer":"ग्राम पंचायत","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":56000,"ReceivedAmount":25000,"PendingAmount":31000,"Remarks":"जमा 25000 बाकी 31000 | पाईपलाईन 250 B (+ विरार) | p7 | imported from M1_book3_1.pdf"}</v>
       </c>
       <c r="H19" t="str">
-        <v>{"Date":"2022-01-14","PartnerName":"Vijay Barve","TransactionType":"Investment","Amount":250000,"Remarks":"Deposite 1","ID":4}</v>
+        <v>{"ID":1061,"Date":"2024-04-01","Customer":"ग्राम पंचायत","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":0,"BillAmount":56000,"ReceivedAmount":56000,"PendingAmount":0,"Remarks":"जमा 25000 बाकी 31000 | पाईपलाईन 250 B (+ विरार) | p7 | imported from M1_book3_1.pdf"}</v>
       </c>
       <c r="I19" t="str">
         <v>client-side</v>
@@ -39017,28 +39017,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-13T11:15:30.651Z</v>
+        <v>2026-07-31T21:15:10.444Z</v>
       </c>
       <c r="C20" t="str">
         <v>Administrator</v>
       </c>
       <c r="D20" t="str">
-        <v>partners</v>
+        <v>income</v>
       </c>
       <c r="E20" t="str">
-        <v>CREATE</v>
+        <v>UPDATE</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>1767</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>{"ID":1767,"Date":"2025-03-25","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.3,"BillAmount":3000,"ReceivedAmount":3000,"PendingAmount":0,"Remarks":"-||- | date assumed from spread/neighbor | 2.30 | p2 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="H20" t="str">
-        <v>{"Date":"2023-01-14","PartnerName":"BAliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+        <v>{"ID":1767,"Date":"2025-03-25","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":2.3,"BillAmount":3000,"ReceivedAmount":3000,"PendingAmount":0,"Remarks":"-||- | date assumed from spread/neighbor | 2.30 | p2 | imported from M1_book3_2.pdf"}</v>
       </c>
       <c r="I20" t="str">
         <v>client-side</v>
@@ -39047,9 +39047,585 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-07-31T21:15:00.639Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D21" t="str">
+        <v>income</v>
+      </c>
+      <c r="E21" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F21">
+        <v>1766</v>
+      </c>
+      <c r="G21" t="str">
+        <v>{"ID":1766,"Date":"2025-03-25","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":38.3,"BillAmount":41800,"ReceivedAmount":0,"PendingAmount":41800,"Remarks":"date assumed from spread/neighbor | 38.30 | p2 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="H21" t="str">
+        <v>{"ID":1766,"Date":"2025-03-25","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":38.3,"BillAmount":41800,"ReceivedAmount":41800,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 38.30 | p2 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="I21" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>17</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-07-31T21:14:34.743Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D22" t="str">
+        <v>income</v>
+      </c>
+      <c r="E22" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F22">
+        <v>1763</v>
+      </c>
+      <c r="G22" t="str">
+        <v>{"ID":1763,"Date":"2025-03-13","Customer":"सरपंच ढोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":34,"BillAmount":37400,"ReceivedAmount":0,"PendingAmount":37400,"Remarks":"date assumed from spread/neighbor | 34 तास | p1 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="H22" t="str">
+        <v>{"ID":1763,"Date":"2025-03-13","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":34,"BillAmount":37400,"ReceivedAmount":37400,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 34 तास | p1 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="I22" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>16</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-07-31T21:13:12.244Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D23" t="str">
+        <v>income</v>
+      </c>
+      <c r="E23" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F23">
+        <v>1761</v>
+      </c>
+      <c r="G23" t="str">
+        <v>{"ID":1761,"Date":"2025-03-13","Customer":"सरपंच रोडे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":76.12,"BillAmount":85600,"ReceivedAmount":0,"PendingAmount":85600,"Remarks":"date assumed from spread/neighbor | 76.12 | p1 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="H23" t="str">
+        <v>{"ID":1761,"Date":"2025-03-13","Customer":"Gajanan Nannaji Dhore","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":76.12,"BillAmount":85600,"ReceivedAmount":85600,"PendingAmount":0,"Remarks":"date assumed from spread/neighbor | 76.12 | p1 | imported from M1_book3_2.pdf"}</v>
+      </c>
+      <c r="I23" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>15</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-07-31T21:11:19.388Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D24" t="str">
+        <v>income</v>
+      </c>
+      <c r="E24" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F24">
+        <v>518</v>
+      </c>
+      <c r="G24" t="str">
+        <v>{"ID":518,"Date":"2023-04-26","Customer":"Ramakant Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":30400,"ReceivedAmount":10000,"PendingAmount":20400,"Remarks":"190 पाईप | जमा 10000 बाकी 20400 | p10 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="H24" t="str">
+        <v>{"ID":518,"Date":"2023-04-26","Customer":"Ramakant Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":30400,"ReceivedAmount":30400,"PendingAmount":0,"Remarks":"190 पाईप | जमा 10000 बाकी 20400 | p10 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="I24" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>14</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-07-31T21:08:42.748Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D25" t="str">
+        <v>income</v>
+      </c>
+      <c r="E25" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F25">
+        <v>507</v>
+      </c>
+      <c r="G25" t="str">
+        <v>{"ID":507,"Date":"2023-04-22","Customer":"Shahaji Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":2800,"ReceivedAmount":1800,"PendingAmount":1000,"Remarks":"16 पाईप | 1000 बाकी | p10 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="H25" t="str">
+        <v>{"ID":507,"Date":"2023-04-22","Customer":"Shahaji Barve","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":0,"BillAmount":2800,"ReceivedAmount":2800,"PendingAmount":0,"Remarks":"16 पाईप | 1000 बाकी | p10 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="I25" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>13</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-07-31T21:07:23.915Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D26" t="str">
+        <v>income</v>
+      </c>
+      <c r="E26" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F26">
+        <v>372</v>
+      </c>
+      <c r="G26" t="str">
+        <v>{"ID":372,"Date":"2023-02-10","Customer":"Jankiram Tole","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":43,"BillAmount":43000,"ReceivedAmount":8000,"PendingAmount":35000,"Remarks":"43 तास | जमा 8000 बाकी | p3 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="H26" t="str">
+        <v>{"ID":372,"Date":"2023-02-10","Customer":"Jankiram Tole","Machine":"M2-Mahindra earthmaster sx iv 2023","Site":"","HoursWorked":43,"BillAmount":43000,"ReceivedAmount":43000,"PendingAmount":0,"Remarks":"43 तास | जमा 8000 बाकी | p3 | imported from Newmachine2.pdf"}</v>
+      </c>
+      <c r="I26" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>12</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-07-31T21:05:59.816Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D27" t="str">
+        <v>income</v>
+      </c>
+      <c r="E27" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F27">
+        <v>231</v>
+      </c>
+      <c r="G27" t="str">
+        <v>{"ID":231,"Date":"2022-08-17","Customer":"Dhore pralahda &amp; baburao","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Work hrs","HoursWorked":"","BillAmount":1300,"ReceivedAmount":0,"PendingAmount":1300,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+      </c>
+      <c r="H27" t="str">
+        <v>{"ID":231,"Date":"2022-08-17","Customer":"Dhore pralahda &amp; baburao","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Work hrs","HoursWorked":"","BillAmount":2600,"ReceivedAmount":2600,"PendingAmount":0,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+      </c>
+      <c r="I27" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>11</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-07-31T21:03:10.905Z</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D28" t="str">
+        <v>income</v>
+      </c>
+      <c r="E28" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F28">
+        <v>66</v>
+      </c>
+      <c r="G28" t="str">
+        <v>{"ID":66,"Date":"2022-03-01","Customer":"baban bepari","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Trip","HoursWorked":"","BillAmount":4200,"ReceivedAmount":0,"PendingAmount":4200,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+      </c>
+      <c r="H28" t="str">
+        <v>{"ID":66,"Date":"2022-03-01","Customer":"baban bepari","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"Trip","HoursWorked":"","BillAmount":4200,"ReceivedAmount":4200,"PendingAmount":0,"Remarks":"Imported from Gitai_Earthmovers_income-expense-worksheet.xlsx"}</v>
+      </c>
+      <c r="I28" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>10</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-07-31T21:01:59.833Z</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D29" t="str">
+        <v>income</v>
+      </c>
+      <c r="E29" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F29">
+        <v>818</v>
+      </c>
+      <c r="G29" t="str">
+        <v>{"ID":818,"Date":"2023-12-07","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":0,"PendingAmount":9900,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="H29" t="str">
+        <v>{"ID":818,"Date":"2023-12-07","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":9900,"PendingAmount":0,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="I29" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>9</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-07-31T21:01:52.442Z</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D30" t="str">
+        <v>income</v>
+      </c>
+      <c r="E30" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F30">
+        <v>821</v>
+      </c>
+      <c r="G30" t="str">
+        <v>{"ID":821,"Date":"2023-12-08","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.3,"BillAmount":10000,"ReceivedAmount":0,"PendingAmount":10000,"Remarks":"9 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="H30" t="str">
+        <v>{"ID":821,"Date":"2023-12-08","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.3,"BillAmount":10000,"ReceivedAmount":10000,"PendingAmount":0,"Remarks":"9 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="I30" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>8</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-07-31T21:01:44.216Z</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D31" t="str">
+        <v>income</v>
+      </c>
+      <c r="E31" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F31">
+        <v>823</v>
+      </c>
+      <c r="G31" t="str">
+        <v>{"ID":823,"Date":"2023-12-09","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":10.5,"BillAmount":11500,"ReceivedAmount":0,"PendingAmount":11500,"Remarks":"10 तास 30 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="H31" t="str">
+        <v>{"ID":823,"Date":"2023-12-09","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":10.5,"BillAmount":11500,"ReceivedAmount":11500,"PendingAmount":0,"Remarks":"10 तास 30 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="I31" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>7</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-07-31T21:01:34.108Z</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D32" t="str">
+        <v>income</v>
+      </c>
+      <c r="E32" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F32">
+        <v>825</v>
+      </c>
+      <c r="G32" t="str">
+        <v>{"ID":825,"Date":"2023-12-10","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":0,"PendingAmount":9900,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="H32" t="str">
+        <v>{"ID":825,"Date":"2023-12-10","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":9.2,"BillAmount":9900,"ReceivedAmount":9900,"PendingAmount":0,"Remarks":"9 तास 12 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="I32" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>6</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-07-31T21:01:01.499Z</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D33" t="str">
+        <v>income</v>
+      </c>
+      <c r="E33" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F33">
+        <v>816</v>
+      </c>
+      <c r="G33" t="str">
+        <v>{"ID":816,"Date":"2023-12-06","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":8.3,"BillAmount":9000,"ReceivedAmount":0,"PendingAmount":9000,"Remarks":"8 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="H33" t="str">
+        <v>{"ID":816,"Date":"2023-12-06","Customer":"आदिनाथ जवन दोरे","Machine":"M1- Mahindra earthmaster sx iv 2022","Site":"","HoursWorked":8.3,"BillAmount":9000,"ReceivedAmount":9000,"PendingAmount":0,"Remarks":"8 तास 18 मि | बाकी | p2 | imported from M1_book3_1.pdf"}</v>
+      </c>
+      <c r="I33" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>5</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-06-13T11:17:08.408Z</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D34" t="str">
+        <v>partners</v>
+      </c>
+      <c r="E34" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"Baliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+      </c>
+      <c r="H34" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"Baliram Barve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+      </c>
+      <c r="I34" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>4</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-06-13T11:17:01.666Z</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D35" t="str">
+        <v>partners</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"BAliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+      </c>
+      <c r="H35" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"Baliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+      </c>
+      <c r="I35" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>3</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-06-13T11:16:38.529Z</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D36" t="str">
+        <v>partners</v>
+      </c>
+      <c r="E36" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"Vijay Barve","TransactionType":"Investment","Amount":200000,"Remarks":"Deposite 2","ID":5}</v>
+      </c>
+      <c r="I36" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-06-13T11:16:14.363Z</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D37" t="str">
+        <v>partners</v>
+      </c>
+      <c r="E37" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>{"Date":"2022-01-14","PartnerName":"Vijay Barve","TransactionType":"Investment","Amount":250000,"Remarks":"Deposite 1","ID":4}</v>
+      </c>
+      <c r="I37" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-06-13T11:15:30.651Z</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="D38" t="str">
+        <v>partners</v>
+      </c>
+      <c r="E38" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>{"Date":"2023-01-14","PartnerName":"BAliram BArve","TransactionType":"Investment","Amount":100000,"Remarks":"Deposite 2","ID":3}</v>
+      </c>
+      <c r="I38" t="str">
+        <v>client-side</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -7864,7 +7864,7 @@
         <v>2023-06-16</v>
       </c>
       <c r="C218" t="str">
-        <v>Gajanan Dhore</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D218" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -11512,7 +11512,7 @@
         <v>2024-04-16</v>
       </c>
       <c r="C332" t="str">
-        <v>गजानन सरपंच</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D332" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>

--- a/Gitai-M2.xlsx
+++ b/Gitai-M2.xlsx
@@ -8248,7 +8248,7 @@
         <v>2023-11-03</v>
       </c>
       <c r="C230" t="str">
-        <v>केशव ठोरे</v>
+        <v>केशव ढोरे</v>
       </c>
       <c r="D230" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -8568,7 +8568,7 @@
         <v>2023-12-05</v>
       </c>
       <c r="C240" t="str">
-        <v>गजू ठोरे सरपंच</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D240" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -8600,7 +8600,7 @@
         <v>2023-12-06</v>
       </c>
       <c r="C241" t="str">
-        <v>गजू ठोरे सरपंच</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D241" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -8632,7 +8632,7 @@
         <v>2023-12-07</v>
       </c>
       <c r="C242" t="str">
-        <v>गजू ठोरे सरपंच</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D242" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -8664,7 +8664,7 @@
         <v>2023-12-07</v>
       </c>
       <c r="C243" t="str">
-        <v>जबन ठोरे</v>
+        <v>जबन ढोरे</v>
       </c>
       <c r="D243" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -8696,7 +8696,7 @@
         <v>2023-12-08</v>
       </c>
       <c r="C244" t="str">
-        <v>गजू ठोरे</v>
+        <v>गजू ढोरे</v>
       </c>
       <c r="D244" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -9528,7 +9528,7 @@
         <v>2024-03-14</v>
       </c>
       <c r="C270" t="str">
-        <v>वामन ठौरे</v>
+        <v>वामन ढोरे</v>
       </c>
       <c r="D270" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -9560,7 +9560,7 @@
         <v>2024-03-14</v>
       </c>
       <c r="C271" t="str">
-        <v>राजू ठौरे</v>
+        <v>राजू ढोरे</v>
       </c>
       <c r="D271" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -9656,7 +9656,7 @@
         <v>2024-03-14</v>
       </c>
       <c r="C274" t="str">
-        <v>आसम ठौरे</v>
+        <v>आसम ढोरे</v>
       </c>
       <c r="D274" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -9688,7 +9688,7 @@
         <v>2024-03-14</v>
       </c>
       <c r="C275" t="str">
-        <v>नान्नाजी ठौरे</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D275" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20408,7 +20408,7 @@
         <v>2024-06-28</v>
       </c>
       <c r="C610" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D610" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20504,7 +20504,7 @@
         <v>2024-06-29</v>
       </c>
       <c r="C613" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D613" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20568,7 +20568,7 @@
         <v>2024-06-30</v>
       </c>
       <c r="C615" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D615" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20600,7 +20600,7 @@
         <v>2024-07-01</v>
       </c>
       <c r="C616" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D616" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20632,7 +20632,7 @@
         <v>2024-07-02</v>
       </c>
       <c r="C617" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D617" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20664,7 +20664,7 @@
         <v>2024-07-03</v>
       </c>
       <c r="C618" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D618" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20696,7 +20696,7 @@
         <v>2024-07-04</v>
       </c>
       <c r="C619" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D619" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20728,7 +20728,7 @@
         <v>2024-07-04</v>
       </c>
       <c r="C620" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D620" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -20760,7 +20760,7 @@
         <v>2024-07-04</v>
       </c>
       <c r="C621" t="str">
-        <v>Gaju Sarpanch Degav Wat</v>
+        <v>Gajanan Nannaji Dhore</v>
       </c>
       <c r="D621" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -24888,7 +24888,7 @@
         <v>2025-04-27</v>
       </c>
       <c r="C750" t="str">
-        <v>गना ठोरे</v>
+        <v>गना ढोरे</v>
       </c>
       <c r="D750" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -25208,7 +25208,7 @@
         <v>2025-05-07</v>
       </c>
       <c r="C760" t="str">
-        <v>हरिभाऊ ठोरे</v>
+        <v>हरिभाऊ ढोरे</v>
       </c>
       <c r="D760" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
@@ -25880,7 +25880,7 @@
         <v>2025-05-15</v>
       </c>
       <c r="C781" t="str">
-        <v>देवीदास ठोरे</v>
+        <v>देवीदास ढोरे</v>
       </c>
       <c r="D781" t="str">
         <v>M2-Mahindra earthmaster sx iv 2023</v>
